--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE255"/>
+  <dimension ref="A1:AE254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46108</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45698</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55173-2023</t>
+          <t>A 62418-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45237</v>
+        <v>46007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1688,248 +1688,248 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 60033-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 55173-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45237</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Brunklöver</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 62418-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 60033-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48890-2021</t>
+          <t>A 49644-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,14 +2162,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44452</v>
+        <v>44454</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49644-2021</t>
+          <t>A 14222-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44454</v>
+        <v>44651</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2298,7 +2298,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14222-2022</t>
+          <t>A 427-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44651</v>
+        <v>44565</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 427-2022</t>
+          <t>A 67534-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44565</v>
+        <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 67534-2021</t>
+          <t>A 47772-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44524</v>
+        <v>44854</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47772-2022</t>
+          <t>A 429-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44854</v>
+        <v>44565</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 429-2022</t>
+          <t>A 8399-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44565</v>
+        <v>44610</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8399-2022</t>
+          <t>A 67514-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44610</v>
+        <v>44524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 67514-2021</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44524</v>
+        <v>45229</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>45532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44816</v>
+        <v>45532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44846</v>
+        <v>45411</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3038,14 +3038,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45748</v>
+        <v>44571</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45390</v>
+        <v>44747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44929</v>
+        <v>45127</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3257,14 +3257,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45517</v>
+        <v>45055</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3276,13 +3276,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3325,7 +3320,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 23567-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3339,10 +3334,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45503</v>
+        <v>45792</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,13 +3349,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3403,7 +3393,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3417,10 +3407,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45504</v>
+        <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3432,13 +3422,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3481,7 +3466,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3495,10 +3480,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45884</v>
+        <v>45793</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3511,7 +3496,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3554,7 +3539,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3568,10 +3553,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46066</v>
+        <v>45792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3583,8 +3568,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3627,7 +3617,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3641,10 +3631,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46065</v>
+        <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3657,7 +3647,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3700,7 +3690,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3714,10 +3704,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44970</v>
+        <v>45797</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3730,7 +3720,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3773,7 +3763,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3783,14 +3773,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45827</v>
+        <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3803,7 +3793,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3846,7 +3836,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3860,10 +3850,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46070</v>
+        <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3876,7 +3866,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3919,7 +3909,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3933,10 +3923,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45835</v>
+        <v>45799</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3949,7 +3939,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3992,7 +3982,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4006,10 +3996,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46071</v>
+        <v>45799</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4022,7 +4012,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4065,7 +4055,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4079,10 +4069,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44565</v>
+        <v>45799</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4095,7 +4085,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4138,7 +4128,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4148,14 +4138,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45908</v>
+        <v>45799</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4168,7 +4158,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4211,7 +4201,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4225,10 +4215,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45905</v>
+        <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4241,7 +4231,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4284,7 +4274,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4298,10 +4288,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45909</v>
+        <v>45800</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4314,7 +4304,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4357,7 +4347,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4371,10 +4361,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45909</v>
+        <v>45503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4392,7 +4382,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4435,7 +4425,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4449,10 +4439,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45356</v>
+        <v>45504</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4464,8 +4454,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4508,7 +4503,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4522,10 +4517,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45912</v>
+        <v>45800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4538,7 +4533,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4581,7 +4576,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4595,10 +4590,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45581</v>
+        <v>46010</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4611,7 +4606,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4654,7 +4649,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4668,10 +4663,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45246</v>
+        <v>46013</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4683,8 +4678,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>21.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45730</v>
+        <v>44691</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45918</v>
+        <v>45516</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45918</v>
+        <v>45884</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45918</v>
+        <v>46030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45462</v>
+        <v>44565</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5102,14 +5102,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45516</v>
+        <v>45146</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45516</v>
+        <v>46034</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5238,7 +5238,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45103</v>
+        <v>46034</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>9.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45937</v>
+        <v>46036</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5384,7 +5384,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45937</v>
+        <v>45103</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5457,7 +5457,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45177</v>
+        <v>46042</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5530,7 +5530,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45939</v>
+        <v>45905</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5613,14 +5613,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45669</v>
+        <v>45827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45713</v>
+        <v>46042</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5749,7 +5749,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5759,14 +5759,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45951</v>
+        <v>45908</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5822,7 +5822,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5832,14 +5832,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45951</v>
+        <v>46044</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5895,7 +5895,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45951</v>
+        <v>45909</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5968,7 +5968,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45950</v>
+        <v>45909</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5997,8 +5997,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6041,7 +6046,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6055,10 +6060,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45957</v>
+        <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6071,7 +6076,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6114,7 +6119,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6124,14 +6129,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45957</v>
+        <v>46044</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6144,7 +6149,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6187,7 +6192,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6197,14 +6202,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45644</v>
+        <v>46048</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6216,13 +6221,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6265,7 +6265,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44853</v>
+        <v>46048</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45957</v>
+        <v>45246</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6411,7 +6411,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6425,10 +6425,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45957</v>
+        <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6484,7 +6484,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44509</v>
+        <v>45835</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6557,7 +6557,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45183</v>
+        <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45680</v>
+        <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6703,7 +6703,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45964</v>
+        <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.7</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6776,7 +6776,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45965</v>
+        <v>46065</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6849,7 +6849,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45965</v>
+        <v>46066</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45974</v>
+        <v>46070</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6995,7 +6995,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45974</v>
+        <v>46071</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7078,14 +7078,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45055</v>
+        <v>45680</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45975</v>
+        <v>45937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7214,7 +7214,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45975</v>
+        <v>45937</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45978</v>
+        <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7360,7 +7360,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45978</v>
+        <v>45099</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7433,7 +7433,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45978</v>
+        <v>45462</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45975</v>
+        <v>45950</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7593,10 +7593,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45509</v>
+        <v>45951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7608,13 +7608,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7657,7 +7652,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7671,10 +7666,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45978</v>
+        <v>45951</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7687,7 +7682,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7730,7 +7725,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7744,10 +7739,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46121</v>
+        <v>44854</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7760,7 +7755,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7803,7 +7798,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7817,10 +7812,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45980</v>
+        <v>45951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7833,7 +7828,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7876,7 +7871,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7890,10 +7885,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45980</v>
+        <v>45356</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7905,13 +7900,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7954,7 +7944,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7964,14 +7954,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45980</v>
+        <v>45177</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7983,13 +7973,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8032,7 +8017,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8046,10 +8031,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45106</v>
+        <v>45257</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8062,7 +8047,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8105,7 +8090,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8119,10 +8104,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45106</v>
+        <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8135,7 +8120,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8178,7 +8163,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8192,10 +8177,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45986</v>
+        <v>45957</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8208,7 +8193,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8251,7 +8236,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8265,10 +8250,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46126</v>
+        <v>45957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8281,7 +8266,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8324,7 +8309,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8334,14 +8319,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45992</v>
+        <v>45957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8354,7 +8339,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8397,7 +8382,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19357-2026</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8411,10 +8396,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46133</v>
+        <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8427,7 +8412,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8470,7 +8455,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8484,10 +8469,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45995</v>
+        <v>45532</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8500,7 +8485,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8543,7 +8528,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8557,10 +8542,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45996</v>
+        <v>45517</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8572,8 +8557,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8616,7 +8606,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8630,10 +8620,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46000</v>
+        <v>45672</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8645,8 +8635,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8689,7 +8684,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8703,10 +8698,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46000</v>
+        <v>45672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8718,8 +8713,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8762,7 +8762,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46000</v>
+        <v>45730</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8835,7 +8835,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46000</v>
+        <v>45965</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46000</v>
+        <v>45964</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8981,7 +8981,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46000</v>
+        <v>45965</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9054,7 +9054,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9064,14 +9064,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46000</v>
+        <v>46121</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9141,10 +9141,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46000</v>
+        <v>46126</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9200,7 +9200,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 19357-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46000</v>
+        <v>46133</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9273,7 +9273,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45103</v>
+        <v>44929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9346,7 +9346,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46000</v>
+        <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9419,7 +9419,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45146</v>
+        <v>45975</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.4</v>
+        <v>8.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9492,7 +9492,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45356</v>
+        <v>45975</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9565,7 +9565,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46010</v>
+        <v>45975</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9638,7 +9638,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45229</v>
+        <v>45974</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9711,7 +9711,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46013</v>
+        <v>45978</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9740,13 +9740,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9789,7 +9784,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9803,10 +9798,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46030</v>
+        <v>45978</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9819,7 +9814,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9862,7 +9857,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9876,10 +9871,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46034</v>
+        <v>45978</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9892,7 +9887,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9935,7 +9930,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9949,10 +9944,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46034</v>
+        <v>45978</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9965,7 +9960,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10008,7 +10003,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10022,10 +10017,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46036</v>
+        <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10037,8 +10032,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10081,7 +10081,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45807</v>
+        <v>45980</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10154,7 +10154,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46042</v>
+        <v>45980</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10183,8 +10183,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10227,7 +10232,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10241,10 +10246,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46042</v>
+        <v>45669</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10257,7 +10262,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10300,7 +10305,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10314,10 +10319,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45799</v>
+        <v>45357</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10330,7 +10335,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10373,7 +10378,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10383,14 +10388,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46044</v>
+        <v>45986</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10403,7 +10408,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10446,7 +10451,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10460,10 +10465,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46044</v>
+        <v>45582</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10476,7 +10481,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10519,7 +10524,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10529,14 +10534,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46044</v>
+        <v>45581</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10549,7 +10554,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10592,7 +10597,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10602,14 +10607,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46048</v>
+        <v>45992</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10622,7 +10627,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10665,7 +10670,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10679,10 +10684,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46048</v>
+        <v>45608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10695,7 +10700,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10738,7 +10743,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10752,10 +10757,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46044</v>
+        <v>45807</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10768,7 +10773,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10811,7 +10816,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10825,10 +10830,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45175</v>
+        <v>45995</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10841,7 +10846,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10884,7 +10889,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10898,10 +10903,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45713</v>
+        <v>45996</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10914,7 +10919,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10957,7 +10962,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10971,10 +10976,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45581</v>
+        <v>46000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10987,7 +10992,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11030,7 +11035,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11040,14 +11045,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45146</v>
+        <v>46000</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11060,7 +11065,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11103,7 +11108,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11117,10 +11122,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45582</v>
+        <v>46000</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11133,7 +11138,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11176,7 +11181,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11190,10 +11195,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45118</v>
+        <v>46000</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11206,7 +11211,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11249,7 +11254,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11263,10 +11268,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45127</v>
+        <v>46000</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11279,7 +11284,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11322,7 +11327,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11336,10 +11341,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45580</v>
+        <v>46000</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11351,13 +11356,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11400,7 +11400,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 21204-2026</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46146</v>
+        <v>46000</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11473,7 +11473,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45509</v>
+        <v>46000</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46148</v>
+        <v>46000</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11619,7 +11619,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11633,10 +11633,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45609</v>
+        <v>46000</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45609</v>
+        <v>45103</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11765,7 +11765,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46149</v>
+        <v>45146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11838,7 +11838,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45713</v>
+        <v>45175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46149</v>
+        <v>45713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11984,7 +11984,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11998,10 +11998,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45439</v>
+        <v>45713</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12057,7 +12057,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45737</v>
+        <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12130,7 +12130,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12144,10 +12144,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45098</v>
+        <v>45587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12203,7 +12203,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46162</v>
+        <v>44970</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12232,13 +12232,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12281,7 +12276,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12295,10 +12290,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46078</v>
+        <v>45799</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12311,7 +12306,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12354,7 +12349,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12368,10 +12363,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46161</v>
+        <v>45463</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12384,7 +12379,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12427,7 +12422,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12441,10 +12436,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45440</v>
+        <v>44935</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12456,13 +12451,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12505,7 +12495,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 21204-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12519,10 +12509,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45231</v>
+        <v>46146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12535,7 +12525,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12578,7 +12568,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12592,10 +12582,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44581</v>
+        <v>46149</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12608,7 +12598,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12651,7 +12641,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12665,10 +12655,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46170</v>
+        <v>46149</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12681,7 +12671,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12724,7 +12714,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12738,10 +12728,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45188</v>
+        <v>45748</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12754,7 +12744,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12797,7 +12787,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12811,10 +12801,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12826,13 +12816,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12875,7 +12860,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12889,10 +12874,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46175</v>
+        <v>45615</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12904,13 +12889,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12953,7 +12933,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12967,10 +12947,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46175</v>
+        <v>46161</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12982,13 +12962,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13031,7 +13006,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13045,10 +13020,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46175</v>
+        <v>46078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13060,13 +13035,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13109,7 +13079,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13123,10 +13093,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46175</v>
+        <v>46162</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13144,7 +13114,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13187,7 +13157,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13201,10 +13171,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45099</v>
+        <v>46170</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13217,7 +13187,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13260,7 +13230,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13274,10 +13244,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13289,8 +13259,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13333,7 +13308,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13347,10 +13322,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45257</v>
+        <v>46175</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13362,8 +13337,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13406,7 +13386,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13420,10 +13400,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13435,8 +13415,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13479,7 +13464,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13493,10 +13478,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44854</v>
+        <v>46175</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13508,8 +13493,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13552,7 +13542,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13566,10 +13556,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45357</v>
+        <v>46176</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13582,7 +13572,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13625,7 +13615,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13639,10 +13629,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45771</v>
+        <v>46175</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13660,7 +13650,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13703,7 +13693,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13717,10 +13707,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44747</v>
+        <v>46176</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13733,7 +13723,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13776,7 +13766,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13790,10 +13780,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44747</v>
+        <v>44581</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13806,7 +13796,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13849,7 +13839,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13863,10 +13853,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45259</v>
+        <v>45218</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13879,7 +13869,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13922,7 +13912,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13936,10 +13926,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45549</v>
+        <v>46198</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13952,7 +13942,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13995,7 +13985,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14009,10 +13999,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46198</v>
+        <v>45146</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14068,7 +14058,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14082,10 +14072,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44691</v>
+        <v>46245</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14098,7 +14088,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14141,7 +14131,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14155,10 +14145,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45069</v>
+        <v>46253</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14171,7 +14161,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14214,7 +14204,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14224,14 +14214,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44571</v>
+        <v>46253</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14244,7 +14234,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14287,7 +14277,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14297,14 +14287,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14317,7 +14307,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14360,7 +14350,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14374,10 +14364,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45411</v>
+        <v>46210</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14390,7 +14380,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14433,7 +14423,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14447,10 +14437,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44935</v>
+        <v>45609</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14463,7 +14453,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14506,7 +14496,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14520,10 +14510,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45118</v>
+        <v>45730</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14536,7 +14526,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14579,7 +14569,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14593,10 +14583,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14609,7 +14599,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14652,7 +14642,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14666,10 +14656,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46210</v>
+        <v>46260</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14682,7 +14672,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14725,7 +14715,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14735,14 +14725,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46253</v>
+        <v>46267</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14755,7 +14745,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14798,7 +14788,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14808,14 +14798,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46253</v>
+        <v>46140</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14828,7 +14818,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14871,7 +14861,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14885,10 +14875,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45508</v>
+        <v>45139</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14900,13 +14890,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14949,7 +14934,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14963,10 +14948,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45730</v>
+        <v>44509</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14979,7 +14964,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15022,7 +15007,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15032,14 +15017,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15051,8 +15036,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15095,7 +15085,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15109,10 +15099,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45624</v>
+        <v>46268</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15125,7 +15115,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15168,7 +15158,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15182,10 +15172,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44501</v>
+        <v>45275</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15198,7 +15188,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>10.2</v>
+        <v>6.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15241,7 +15231,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15255,10 +15245,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46260</v>
+        <v>46273</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15271,7 +15261,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15314,7 +15304,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15328,10 +15318,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45463</v>
+        <v>45549</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15344,7 +15334,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15387,7 +15377,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15401,10 +15391,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45608</v>
+        <v>45748</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15417,7 +15407,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15460,7 +15450,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15474,10 +15464,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45275</v>
+        <v>46273</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15490,7 +15480,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15533,7 +15523,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15547,10 +15537,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45713</v>
+        <v>46274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15563,7 +15553,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15606,7 +15596,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15620,10 +15610,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45713</v>
+        <v>45106</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15636,7 +15626,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15679,7 +15669,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15689,14 +15679,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45146</v>
+        <v>46274</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15709,7 +15699,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15752,7 +15742,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15766,10 +15756,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44987</v>
+        <v>44953</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15782,7 +15772,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15825,7 +15815,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15839,10 +15829,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45139</v>
+        <v>45737</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15855,7 +15845,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15898,7 +15888,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15912,10 +15902,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45615</v>
+        <v>45439</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15928,7 +15918,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15971,7 +15961,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15985,10 +15975,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44987</v>
+        <v>44501</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16001,7 +15991,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.7</v>
+        <v>10.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16044,7 +16034,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16058,10 +16048,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45757</v>
+        <v>45624</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16074,7 +16064,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16117,7 +16107,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16131,10 +16121,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45775</v>
+        <v>45609</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16147,7 +16137,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16190,7 +16180,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16204,10 +16194,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46140</v>
+        <v>45609</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16220,7 +16210,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16263,7 +16253,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16277,10 +16267,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45532</v>
+        <v>45098</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16293,7 +16283,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16336,7 +16326,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16350,10 +16340,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45532</v>
+        <v>44747</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16366,7 +16356,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16409,7 +16399,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16423,10 +16413,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45532</v>
+        <v>45509</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16438,8 +16428,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16482,7 +16477,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16496,10 +16491,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44509</v>
+        <v>45771</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16511,8 +16506,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16555,7 +16555,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16569,10 +16569,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46267</v>
+        <v>44987</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16628,7 +16628,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16642,10 +16642,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46268</v>
+        <v>45231</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16701,7 +16701,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16715,10 +16715,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45474</v>
+        <v>45509</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16730,13 +16730,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16779,7 +16774,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16793,10 +16788,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44979</v>
+        <v>45508</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16808,8 +16803,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16852,7 +16852,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16862,14 +16862,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46269</v>
+        <v>44509</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16881,13 +16881,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16930,7 +16925,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16944,10 +16939,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46274</v>
+        <v>45106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16960,7 +16955,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17003,7 +16998,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17017,10 +17012,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46274</v>
+        <v>45118</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17033,7 +17028,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17076,7 +17071,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17090,10 +17085,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44953</v>
+        <v>45118</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17106,7 +17101,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17149,7 +17144,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17163,10 +17158,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46273</v>
+        <v>44979</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17179,7 +17174,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17222,7 +17217,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17232,14 +17227,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44747</v>
+        <v>45069</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17252,7 +17247,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17295,7 +17290,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17309,10 +17304,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46273</v>
+        <v>44987</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17325,7 +17320,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>7.9</v>
+        <v>3.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17368,7 +17363,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17382,10 +17377,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45587</v>
+        <v>45580</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17397,8 +17392,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17441,7 +17441,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17455,10 +17455,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45748</v>
+        <v>45440</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17470,8 +17470,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17514,7 +17519,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17528,10 +17533,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45672</v>
+        <v>45390</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17543,13 +17548,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17592,7 +17592,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17606,10 +17606,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45672</v>
+        <v>45713</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17621,13 +17621,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17670,7 +17665,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17684,10 +17679,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45609</v>
+        <v>45516</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17700,7 +17695,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17743,7 +17738,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17757,10 +17752,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45118</v>
+        <v>45581</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17773,7 +17768,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17816,7 +17811,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17826,14 +17821,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45782</v>
+        <v>45644</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17845,8 +17840,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17903,10 +17903,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45782</v>
+        <v>45259</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17962,7 +17962,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17976,10 +17976,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45790</v>
+        <v>45474</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18040,7 +18040,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18054,10 +18054,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45791</v>
+        <v>45188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18069,13 +18069,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18118,7 +18113,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18132,10 +18127,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45791</v>
+        <v>44747</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18147,13 +18142,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>8.199999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18196,7 +18186,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 23567-2025</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18210,10 +18200,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45792</v>
+        <v>45775</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18226,7 +18216,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18269,7 +18259,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18283,10 +18273,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45187</v>
+        <v>44816</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18299,7 +18289,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18342,7 +18332,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18356,10 +18346,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45792</v>
+        <v>45713</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18371,13 +18361,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18420,7 +18405,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18434,10 +18419,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45792</v>
+        <v>45356</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18450,7 +18435,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18493,7 +18478,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18507,10 +18492,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45793</v>
+        <v>45183</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18508,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18566,7 +18551,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18580,10 +18565,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45797</v>
+        <v>45713</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18596,7 +18581,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18639,7 +18624,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18653,10 +18638,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45797</v>
+        <v>45118</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18669,7 +18654,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18712,7 +18697,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18726,10 +18711,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45800</v>
+        <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18742,7 +18727,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18785,7 +18770,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18799,10 +18784,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45799</v>
+        <v>45782</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18815,7 +18800,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18858,7 +18843,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18872,10 +18857,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45800</v>
+        <v>45187</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18888,7 +18873,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18931,7 +18916,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18945,10 +18930,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45799</v>
+        <v>45791</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18960,8 +18945,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19004,7 +18994,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19018,10 +19008,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45799</v>
+        <v>45791</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19033,8 +19023,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19077,7 +19072,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19091,10 +19086,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45799</v>
+        <v>45790</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19106,8 +19101,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19150,24 +19150,24 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45799</v>
+        <v>45250</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19179,8 +19179,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>1.9</v>
+        <v>31.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19240,7 +19245,7 @@
         <v>44559</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19318,7 +19323,7 @@
         <v>44645</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19374,7 +19379,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 1362-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19388,10 +19393,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45250</v>
+        <v>45775</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19403,13 +19408,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>31.7</v>
+        <v>63.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>S 1362-2025</t>
+          <t>S 2703-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19466,10 +19466,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45775</v>
+        <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>63.6</v>
+        <v>61.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19525,7 +19525,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>S 2703-2025</t>
+          <t>S 425-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19539,10 +19539,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45929</v>
+        <v>46070</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19554,8 +19554,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>61.2</v>
+        <v>17.3</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19598,7 +19603,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>S 425-2026</t>
+          <t>S 470-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19612,10 +19617,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19627,13 +19632,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>17.3</v>
+        <v>31.7</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19673,10 +19673,10 @@
       </c>
       <c r="V253" s="2" t="inlineStr"/>
     </row>
-    <row r="254" ht="15" customHeight="1">
+    <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S 470-2026</t>
+          <t>S 964-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19686,14 +19686,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46073</v>
+        <v>46114</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19705,8 +19705,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>31.7</v>
+        <v>0.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19745,84 +19750,6 @@
         <v>0</v>
       </c>
       <c r="V254" s="2" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>S 964-2026</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D255" s="1" t="n">
-        <v>46114</v>
-      </c>
-      <c r="E255" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I255" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J255" t="n">
-        <v>0</v>
-      </c>
-      <c r="K255" t="n">
-        <v>0</v>
-      </c>
-      <c r="L255" t="n">
-        <v>0</v>
-      </c>
-      <c r="M255" t="n">
-        <v>0</v>
-      </c>
-      <c r="N255" t="n">
-        <v>0</v>
-      </c>
-      <c r="O255" t="n">
-        <v>0</v>
-      </c>
-      <c r="P255" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0</v>
-      </c>
-      <c r="S255" t="n">
-        <v>0</v>
-      </c>
-      <c r="T255" t="n">
-        <v>0</v>
-      </c>
-      <c r="U255" t="n">
-        <v>0</v>
-      </c>
-      <c r="V255" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46108</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45698</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>46007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60033-2024</t>
+          <t>A 55173-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45642</v>
+        <v>45237</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1753,17 +1753,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1793,143 +1793,143 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 60033-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 55173-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45237</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49644-2021</t>
+          <t>A 14222-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44454</v>
+        <v>44651</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14222-2022</t>
+          <t>A 427-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44651</v>
+        <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2298,7 +2298,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 427-2022</t>
+          <t>A 67534-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44565</v>
+        <v>44524</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 67534-2021</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44524</v>
+        <v>45218</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 47772-2022</t>
+          <t>A 8399-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44854</v>
+        <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 429-2022</t>
+          <t>A 47772-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44565</v>
+        <v>44854</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8399-2022</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44610</v>
+        <v>44816</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 67514-2021</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44524</v>
+        <v>45188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 429-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45229</v>
+        <v>44565</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45532</v>
+        <v>45099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45532</v>
+        <v>45257</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45411</v>
+        <v>44846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 67514-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3038,14 +3038,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44571</v>
+        <v>44524</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44747</v>
+        <v>45462</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45127</v>
+        <v>45748</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3257,14 +3257,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45055</v>
+        <v>44854</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23567-2025</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45792</v>
+        <v>45390</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45757</v>
+        <v>45357</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45793</v>
+        <v>45771</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3495,8 +3495,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3539,7 +3544,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3553,10 +3558,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45792</v>
+        <v>44747</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3568,13 +3573,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45792</v>
+        <v>44747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45797</v>
+        <v>45884</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45797</v>
+        <v>45503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3792,8 +3792,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3836,7 +3841,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3850,10 +3855,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45799</v>
+        <v>45504</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3865,8 +3870,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3909,7 +3919,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3923,10 +3933,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45799</v>
+        <v>44929</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3939,7 +3949,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3982,7 +3992,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3996,10 +4006,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45799</v>
+        <v>44565</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4012,7 +4022,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4055,7 +4065,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4069,10 +4079,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45799</v>
+        <v>45259</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4085,7 +4095,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4128,7 +4138,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45799</v>
+        <v>45549</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4158,7 +4168,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4201,7 +4211,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,14 +4221,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44853</v>
+        <v>45908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4231,7 +4241,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4274,7 +4284,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4288,10 +4298,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45800</v>
+        <v>45905</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4304,7 +4314,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4347,7 +4357,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4361,10 +4371,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45503</v>
+        <v>45909</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4374,11 +4384,6 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -4425,7 +4430,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4439,10 +4444,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45504</v>
+        <v>45517</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4460,7 +4465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4503,7 +4508,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4517,10 +4522,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45800</v>
+        <v>45909</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,8 +4537,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4576,7 +4586,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4590,10 +4600,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46010</v>
+        <v>45912</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4606,7 +4616,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4649,7 +4659,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4663,10 +4673,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46013</v>
+        <v>45918</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,13 +4688,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>21.4</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4727,7 +4732,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4741,10 +4746,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44691</v>
+        <v>45918</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4757,7 +4762,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4800,7 +4805,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4814,10 +4819,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45516</v>
+        <v>45918</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4830,7 +4835,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4873,7 +4878,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4887,10 +4892,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45884</v>
+        <v>46121</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4903,7 +4908,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4946,7 +4951,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4960,10 +4965,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46030</v>
+        <v>46126</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4976,7 +4981,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5019,7 +5024,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5033,10 +5038,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44565</v>
+        <v>44970</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5049,7 +5054,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5092,7 +5097,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5102,14 +5107,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45146</v>
+        <v>45937</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5122,7 +5127,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5165,7 +5170,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5179,10 +5184,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46034</v>
+        <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5195,7 +5200,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5238,7 +5243,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 19357-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5252,10 +5257,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46034</v>
+        <v>46133</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5268,7 +5273,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9.1</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5311,7 +5316,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5325,10 +5330,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46036</v>
+        <v>45939</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5341,7 +5346,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5384,7 +5389,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5398,10 +5403,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45103</v>
+        <v>45951</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5414,7 +5419,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5457,7 +5462,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5471,10 +5476,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46042</v>
+        <v>45951</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5487,7 +5492,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5530,7 +5535,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5544,10 +5549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45905</v>
+        <v>45951</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5560,7 +5565,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5603,7 +5608,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5613,14 +5618,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45827</v>
+        <v>45950</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5633,7 +5638,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5676,7 +5681,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5690,10 +5695,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46042</v>
+        <v>45957</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5706,7 +5711,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5749,7 +5754,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5759,14 +5764,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45908</v>
+        <v>45957</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5779,7 +5784,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5822,7 +5827,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5832,14 +5837,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46044</v>
+        <v>45957</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5852,7 +5857,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5895,7 +5900,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5909,10 +5914,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45909</v>
+        <v>45957</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5925,7 +5930,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5968,7 +5973,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45909</v>
+        <v>45356</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5997,13 +6002,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6046,7 +6046,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46044</v>
+        <v>45581</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6119,7 +6119,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6129,14 +6129,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46044</v>
+        <v>45246</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>4.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6192,7 +6192,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46048</v>
+        <v>45964</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6265,7 +6265,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46048</v>
+        <v>45730</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45246</v>
+        <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6411,7 +6411,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6425,10 +6425,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45912</v>
+        <v>45965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6484,7 +6484,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45835</v>
+        <v>45807</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6557,7 +6557,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45918</v>
+        <v>45799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45918</v>
+        <v>45974</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6703,7 +6703,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45918</v>
+        <v>45974</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6776,7 +6776,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46065</v>
+        <v>45975</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6849,7 +6849,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46066</v>
+        <v>45975</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>8.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46070</v>
+        <v>46044</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6995,7 +6995,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46071</v>
+        <v>45978</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45680</v>
+        <v>45978</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45937</v>
+        <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7214,7 +7214,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45937</v>
+        <v>45975</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45939</v>
+        <v>45978</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7360,7 +7360,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45099</v>
+        <v>45175</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7433,7 +7433,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45462</v>
+        <v>45980</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45950</v>
+        <v>45980</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7535,8 +7535,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7579,7 +7584,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7593,10 +7598,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45951</v>
+        <v>45980</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7608,8 +7613,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7652,7 +7662,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7666,10 +7676,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45951</v>
+        <v>44691</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7682,7 +7692,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7725,7 +7735,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7735,14 +7745,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44854</v>
+        <v>45069</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7755,7 +7765,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7798,7 +7808,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7808,14 +7818,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45951</v>
+        <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7828,7 +7838,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7871,7 +7881,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7885,10 +7895,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45356</v>
+        <v>45581</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7901,7 +7911,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7944,7 +7954,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7954,14 +7964,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45177</v>
+        <v>45516</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7974,7 +7984,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8017,7 +8027,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8031,10 +8041,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45257</v>
+        <v>45516</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8047,7 +8057,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8090,7 +8100,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8104,10 +8114,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44846</v>
+        <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8120,7 +8130,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8163,7 +8173,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8177,10 +8187,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45957</v>
+        <v>45986</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8193,7 +8203,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8236,7 +8246,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8246,14 +8256,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45957</v>
+        <v>45177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8266,7 +8276,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8309,7 +8319,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8323,10 +8333,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45957</v>
+        <v>45669</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8339,7 +8349,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8382,7 +8392,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8392,14 +8402,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45957</v>
+        <v>45992</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8412,7 +8422,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8455,7 +8465,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 21204-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8469,10 +8479,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45532</v>
+        <v>46146</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8485,7 +8495,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8528,7 +8538,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8542,10 +8552,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45517</v>
+        <v>45995</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8557,13 +8567,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8606,7 +8611,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8620,10 +8625,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45672</v>
+        <v>45713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8635,13 +8640,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8684,7 +8684,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45672</v>
+        <v>45996</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8713,13 +8713,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8762,7 +8757,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8776,10 +8771,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45730</v>
+        <v>46000</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8792,7 +8787,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8835,7 +8830,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8849,10 +8844,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45965</v>
+        <v>46000</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8865,7 +8860,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8908,7 +8903,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8922,10 +8917,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45964</v>
+        <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8938,7 +8933,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8981,7 +8976,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8995,10 +8990,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45965</v>
+        <v>45411</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9011,7 +9006,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9054,7 +9049,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9068,10 +9063,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46121</v>
+        <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9127,7 +9122,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9141,10 +9136,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9157,7 +9152,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9200,7 +9195,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 19357-2026</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9214,10 +9209,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46133</v>
+        <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9230,7 +9225,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9273,7 +9268,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9287,10 +9282,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44929</v>
+        <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9303,7 +9298,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9346,7 +9341,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9356,14 +9351,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45974</v>
+        <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9376,7 +9371,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9419,7 +9414,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9433,10 +9428,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45975</v>
+        <v>46000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9449,7 +9444,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9492,7 +9487,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9506,10 +9501,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45975</v>
+        <v>46000</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9522,7 +9517,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9565,7 +9560,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9579,10 +9574,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45975</v>
+        <v>46149</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9595,7 +9590,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9638,7 +9633,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9652,10 +9647,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45974</v>
+        <v>45103</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9668,7 +9663,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9711,7 +9706,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9725,10 +9720,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45978</v>
+        <v>46149</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9741,7 +9736,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9784,7 +9779,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9798,10 +9793,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45978</v>
+        <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9814,7 +9809,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9857,7 +9852,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9871,10 +9866,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45978</v>
+        <v>45146</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9887,7 +9882,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9930,7 +9925,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9940,14 +9935,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45978</v>
+        <v>45644</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9959,8 +9954,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10003,7 +10003,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45980</v>
+        <v>44853</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10032,13 +10032,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10081,7 +10076,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10095,10 +10090,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45980</v>
+        <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10111,7 +10106,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10154,7 +10149,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10168,10 +10163,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45980</v>
+        <v>45183</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10183,13 +10178,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10232,7 +10222,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10246,10 +10236,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45669</v>
+        <v>45680</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10262,7 +10252,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10305,7 +10295,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10319,10 +10309,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45357</v>
+        <v>46010</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10335,7 +10325,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10378,7 +10368,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10392,10 +10382,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45986</v>
+        <v>46013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10407,8 +10397,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>4.4</v>
+        <v>21.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10451,7 +10446,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10461,14 +10456,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45582</v>
+        <v>45055</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10481,7 +10476,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10524,7 +10519,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10538,10 +10533,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45581</v>
+        <v>46162</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10553,8 +10548,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10597,7 +10597,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45992</v>
+        <v>46078</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45608</v>
+        <v>45509</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10699,8 +10699,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10743,7 +10748,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10757,10 +10762,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45807</v>
+        <v>46161</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10773,7 +10778,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10816,7 +10821,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10830,10 +10835,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10846,7 +10851,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10889,7 +10894,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10903,10 +10908,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45996</v>
+        <v>46034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10919,7 +10924,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10962,7 +10967,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10976,10 +10981,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46000</v>
+        <v>46034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10992,7 +10997,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11035,7 +11040,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11045,14 +11050,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46000</v>
+        <v>45106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11065,7 +11070,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11108,7 +11113,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11122,10 +11127,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46000</v>
+        <v>45106</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11138,7 +11143,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11181,7 +11186,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11195,10 +11200,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46000</v>
+        <v>46036</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11211,7 +11216,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11254,7 +11259,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11268,10 +11273,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46000</v>
+        <v>46042</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11284,7 +11289,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11327,7 +11332,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11341,10 +11346,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46000</v>
+        <v>46042</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11357,7 +11362,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11400,7 +11405,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11414,10 +11419,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46000</v>
+        <v>46170</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11430,7 +11435,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11473,7 +11478,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11487,10 +11492,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46000</v>
+        <v>44935</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11503,7 +11508,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11546,7 +11551,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11556,14 +11561,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11576,7 +11581,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11619,7 +11624,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11633,10 +11638,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11649,7 +11654,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11692,7 +11697,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11706,10 +11711,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45103</v>
+        <v>46175</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11721,8 +11726,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11765,7 +11775,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11775,14 +11785,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45146</v>
+        <v>46044</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11795,7 +11805,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11838,7 +11848,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11852,10 +11862,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45175</v>
+        <v>46175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11867,8 +11877,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11911,7 +11926,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11925,10 +11940,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45713</v>
+        <v>46048</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11941,7 +11956,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11984,7 +11999,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11998,10 +12013,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45713</v>
+        <v>46048</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12014,7 +12029,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12057,7 +12072,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12071,10 +12086,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46044</v>
+        <v>46175</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12086,8 +12101,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12130,7 +12150,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12144,10 +12164,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45587</v>
+        <v>45118</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12160,7 +12180,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12203,7 +12223,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12217,10 +12237,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44970</v>
+        <v>46175</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12232,8 +12252,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12276,7 +12301,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12290,10 +12315,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45799</v>
+        <v>46175</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12305,8 +12330,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12349,7 +12379,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12363,10 +12393,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45463</v>
+        <v>45356</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12379,7 +12409,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12422,7 +12452,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12436,10 +12466,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44935</v>
+        <v>46176</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12452,7 +12482,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12495,7 +12525,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21204-2026</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12509,10 +12539,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46146</v>
+        <v>46176</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12568,7 +12598,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12582,10 +12612,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46149</v>
+        <v>45229</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12598,7 +12628,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12641,7 +12671,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12655,10 +12685,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46149</v>
+        <v>46066</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12714,7 +12744,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12728,10 +12758,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45748</v>
+        <v>46065</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12744,7 +12774,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12787,7 +12817,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12801,10 +12831,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46148</v>
+        <v>46070</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12817,7 +12847,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12860,7 +12890,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12874,10 +12904,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45615</v>
+        <v>46071</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12890,7 +12920,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12933,7 +12963,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12947,10 +12977,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46161</v>
+        <v>45508</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12962,8 +12992,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13006,7 +13041,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13020,10 +13055,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46078</v>
+        <v>45730</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13036,7 +13071,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13079,7 +13114,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13093,10 +13128,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46162</v>
+        <v>45624</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13108,13 +13143,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13157,7 +13187,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13171,10 +13201,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46170</v>
+        <v>44501</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13187,7 +13217,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13230,7 +13260,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13244,10 +13274,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46175</v>
+        <v>45463</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13259,13 +13289,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13308,7 +13333,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13322,10 +13347,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46175</v>
+        <v>45608</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13337,13 +13362,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13386,7 +13406,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13400,10 +13420,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46175</v>
+        <v>46198</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13415,13 +13435,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13464,7 +13479,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13478,10 +13493,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46175</v>
+        <v>45713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13493,13 +13508,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13542,7 +13552,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13556,10 +13566,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46176</v>
+        <v>45146</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13572,7 +13582,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13615,7 +13625,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13629,10 +13639,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46175</v>
+        <v>46245</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13644,13 +13654,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13693,7 +13698,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13707,10 +13712,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46176</v>
+        <v>45582</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13723,7 +13728,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13766,7 +13771,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13780,10 +13785,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44581</v>
+        <v>45118</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13796,7 +13801,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13839,7 +13844,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13853,10 +13858,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45218</v>
+        <v>45127</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13869,7 +13874,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13912,7 +13917,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13926,10 +13931,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46198</v>
+        <v>45580</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13941,8 +13946,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13985,7 +13995,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13999,10 +14009,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45146</v>
+        <v>45509</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14015,7 +14025,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14058,7 +14068,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14072,10 +14082,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46245</v>
+        <v>45609</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14088,7 +14098,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14131,7 +14141,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14141,14 +14151,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46253</v>
+        <v>45609</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14161,7 +14171,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14204,7 +14214,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14218,10 +14228,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46253</v>
+        <v>45713</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14234,7 +14244,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14277,7 +14287,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14287,14 +14297,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46253</v>
+        <v>45439</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14307,7 +14317,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14350,7 +14360,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14364,10 +14374,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46210</v>
+        <v>45275</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14380,7 +14390,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.6</v>
+        <v>6.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14423,7 +14433,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14437,10 +14447,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45609</v>
+        <v>46253</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14453,7 +14463,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14496,7 +14506,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14510,10 +14520,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45730</v>
+        <v>46210</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14526,7 +14536,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14569,7 +14579,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14579,14 +14589,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14599,7 +14609,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14642,7 +14652,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14656,10 +14666,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46260</v>
+        <v>45713</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14672,7 +14682,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14715,7 +14725,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14729,10 +14739,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46267</v>
+        <v>45713</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14745,7 +14755,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14788,7 +14798,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14798,14 +14808,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46140</v>
+        <v>45146</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14818,7 +14828,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14861,7 +14871,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14871,14 +14881,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45139</v>
+        <v>46253</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14891,7 +14901,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14934,7 +14944,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14948,10 +14958,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44509</v>
+        <v>45737</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14964,7 +14974,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15007,7 +15017,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15017,14 +15027,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46269</v>
+        <v>45098</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15036,13 +15046,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15085,7 +15090,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15099,10 +15104,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46268</v>
+        <v>44987</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15115,7 +15120,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15158,7 +15163,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15172,10 +15177,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45275</v>
+        <v>45139</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15188,7 +15193,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15231,7 +15236,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15245,10 +15250,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46273</v>
+        <v>45615</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15261,7 +15266,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15304,7 +15309,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15318,10 +15323,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45549</v>
+        <v>46255</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15334,7 +15339,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15377,7 +15382,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15391,10 +15396,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45748</v>
+        <v>45440</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15406,8 +15411,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15450,7 +15460,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15464,10 +15474,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46273</v>
+        <v>45231</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15480,7 +15490,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15523,7 +15533,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15537,10 +15547,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15553,7 +15563,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15596,7 +15606,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15610,10 +15620,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45106</v>
+        <v>44987</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15626,7 +15636,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15669,7 +15679,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15683,10 +15693,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46274</v>
+        <v>45757</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15699,7 +15709,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15742,7 +15752,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15756,10 +15766,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44953</v>
+        <v>45775</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15772,7 +15782,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15815,7 +15825,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15829,10 +15839,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45737</v>
+        <v>44581</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15845,7 +15855,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15888,7 +15898,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15902,10 +15912,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45439</v>
+        <v>45532</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15918,7 +15928,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15961,7 +15971,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15975,10 +15985,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44501</v>
+        <v>45532</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15991,7 +16001,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16034,7 +16044,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16048,10 +16058,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45624</v>
+        <v>45532</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16064,7 +16074,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16107,7 +16117,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16121,10 +16131,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45609</v>
+        <v>45474</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16136,8 +16146,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16180,7 +16195,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16194,10 +16209,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45609</v>
+        <v>44979</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16210,7 +16225,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16253,7 +16268,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16267,10 +16282,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45098</v>
+        <v>46140</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16283,7 +16298,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16326,7 +16341,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16340,10 +16355,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44747</v>
+        <v>44509</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16356,7 +16371,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16399,7 +16414,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16413,10 +16428,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45509</v>
+        <v>46267</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16428,13 +16443,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16477,7 +16487,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16491,10 +16501,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45771</v>
+        <v>46268</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16506,13 +16516,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16555,7 +16560,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16565,14 +16570,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44987</v>
+        <v>46269</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16582,6 +16587,11 @@
       <c r="G212" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I212" t="n">
@@ -16628,7 +16638,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16642,10 +16652,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45231</v>
+        <v>44953</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16658,7 +16668,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16701,7 +16711,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16715,10 +16725,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45509</v>
+        <v>44747</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16731,7 +16741,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16774,7 +16784,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16788,10 +16798,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45508</v>
+        <v>46274</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16803,13 +16813,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16852,7 +16857,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16866,10 +16871,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44509</v>
+        <v>46274</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16882,7 +16887,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16925,7 +16930,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16939,10 +16944,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45106</v>
+        <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16955,7 +16960,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16998,7 +17003,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17012,10 +17017,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45118</v>
+        <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17028,7 +17033,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17071,7 +17076,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17085,10 +17090,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45118</v>
+        <v>46273</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17101,7 +17106,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17144,7 +17149,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17158,10 +17163,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44979</v>
+        <v>45748</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17174,7 +17179,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17217,7 +17222,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17227,14 +17232,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45069</v>
+        <v>45672</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17246,8 +17251,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17290,7 +17300,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17304,10 +17314,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44987</v>
+        <v>45672</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17319,8 +17329,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17363,7 +17378,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17377,10 +17392,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45580</v>
+        <v>45609</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17392,13 +17407,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17441,7 +17451,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17455,10 +17465,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45440</v>
+        <v>45118</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17470,13 +17480,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17519,7 +17524,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17533,10 +17538,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45390</v>
+        <v>46280</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17549,7 +17554,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17592,7 +17597,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17606,10 +17611,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45713</v>
+        <v>45782</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17622,7 +17627,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17665,7 +17670,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17679,10 +17684,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45516</v>
+        <v>45782</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17695,7 +17700,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17738,7 +17743,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17752,10 +17757,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45581</v>
+        <v>45790</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17767,8 +17772,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17811,7 +17821,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17821,14 +17831,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45644</v>
+        <v>45791</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17846,7 +17856,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17889,7 +17899,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17903,10 +17913,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45259</v>
+        <v>45791</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17918,8 +17928,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17962,7 +17977,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 23567-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17976,10 +17991,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45474</v>
+        <v>45792</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17991,13 +18006,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18040,7 +18050,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18054,10 +18064,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45188</v>
+        <v>45187</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18070,7 +18080,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18113,7 +18123,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18127,10 +18137,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44747</v>
+        <v>45792</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18142,8 +18152,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18186,7 +18201,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18200,10 +18215,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45775</v>
+        <v>45792</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18216,7 +18231,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18259,7 +18274,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18273,10 +18288,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44816</v>
+        <v>45793</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18289,7 +18304,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18332,7 +18347,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18346,10 +18361,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45713</v>
+        <v>45797</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18362,7 +18377,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18405,7 +18420,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18419,10 +18434,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45356</v>
+        <v>45797</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18435,7 +18450,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18478,7 +18493,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18492,10 +18507,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45183</v>
+        <v>45800</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18508,7 +18523,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18551,7 +18566,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18565,10 +18580,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45713</v>
+        <v>45799</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18581,7 +18596,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18624,7 +18639,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18638,10 +18653,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45118</v>
+        <v>45800</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18654,7 +18669,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18697,7 +18712,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18711,10 +18726,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45782</v>
+        <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18727,7 +18742,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18770,7 +18785,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18784,10 +18799,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45782</v>
+        <v>45799</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18800,7 +18815,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18843,7 +18858,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18857,10 +18872,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45187</v>
+        <v>45799</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18873,7 +18888,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18916,7 +18931,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18930,10 +18945,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45791</v>
+        <v>45799</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18945,13 +18960,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -18994,7 +19004,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19004,14 +19014,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45791</v>
+        <v>45827</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19023,13 +19033,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19072,7 +19077,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19086,10 +19091,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45790</v>
+        <v>45835</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19101,13 +19106,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19150,7 +19150,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19164,10 +19164,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45250</v>
+        <v>44559</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>31.7</v>
+        <v>60.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19228,7 +19228,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19242,10 +19242,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44559</v>
+        <v>44645</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19257,13 +19257,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>60.7</v>
+        <v>15.8</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19306,7 +19301,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19320,10 +19315,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44645</v>
+        <v>45250</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19335,8 +19330,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>15.8</v>
+        <v>31.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19396,7 +19396,7 @@
         <v>45775</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46070</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>46073</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46114</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46108</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45698</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>46007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55173-2023</t>
+          <t>A 60033-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45237</v>
+        <v>45642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1777,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1793,143 +1793,143 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 55173-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45237</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Brunklöver</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 60033-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44651</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44524</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 47772-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45218</v>
+        <v>44854</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8399-2022</t>
+          <t>A 429-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44610</v>
+        <v>44565</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47772-2022</t>
+          <t>A 8399-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44854</v>
+        <v>44610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 67514-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44816</v>
+        <v>44524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45188</v>
+        <v>45229</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 429-2022</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44565</v>
+        <v>45411</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45099</v>
+        <v>45532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45257</v>
+        <v>45532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2965,14 +2965,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44846</v>
+        <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 67514-2021</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44524</v>
+        <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45462</v>
+        <v>44747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3184,14 +3184,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45748</v>
+        <v>45055</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44854</v>
+        <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45390</v>
+        <v>44853</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45357</v>
+        <v>45503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3422,8 +3422,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3466,7 +3471,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3480,10 +3485,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45771</v>
+        <v>45504</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3501,7 +3506,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3544,7 +3549,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3558,10 +3563,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44747</v>
+        <v>44691</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3574,7 +3579,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3617,7 +3622,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3631,10 +3636,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44747</v>
+        <v>45516</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3647,7 +3652,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3690,7 +3695,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45884</v>
+        <v>45799</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3720,7 +3725,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3763,7 +3768,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45503</v>
+        <v>45799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3792,13 +3797,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45504</v>
+        <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3870,13 +3870,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3919,7 +3914,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3933,10 +3928,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44929</v>
+        <v>45799</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3949,7 +3944,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3992,7 +3987,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44565</v>
+        <v>45799</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4022,7 +4017,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4065,7 +4060,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4075,14 +4070,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45259</v>
+        <v>45146</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4095,7 +4090,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4138,7 +4133,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4152,10 +4147,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45549</v>
+        <v>45800</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4168,7 +4163,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4211,7 +4206,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4221,14 +4216,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45908</v>
+        <v>45800</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4241,7 +4236,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4284,7 +4279,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4298,10 +4293,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45905</v>
+        <v>45103</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4314,7 +4309,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4357,7 +4352,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4371,10 +4366,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45909</v>
+        <v>46030</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4387,7 +4382,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4430,7 +4425,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45517</v>
+        <v>45884</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4459,13 +4454,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4508,7 +4498,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4522,10 +4512,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45909</v>
+        <v>44565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4537,13 +4527,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4586,7 +4571,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4600,10 +4585,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45912</v>
+        <v>45246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4616,7 +4601,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4659,7 +4644,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4673,10 +4658,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45918</v>
+        <v>46034</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4689,7 +4674,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4732,7 +4717,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4742,14 +4727,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45918</v>
+        <v>45827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4762,7 +4747,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4805,7 +4790,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4819,10 +4804,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45918</v>
+        <v>45905</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4835,7 +4820,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4878,7 +4863,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4892,10 +4877,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46121</v>
+        <v>46034</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4908,7 +4893,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>9.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4951,7 +4936,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4961,14 +4946,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46126</v>
+        <v>45908</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4981,7 +4966,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5024,7 +5009,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5038,10 +5023,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44970</v>
+        <v>45909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5054,7 +5039,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5097,7 +5082,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5111,10 +5096,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45937</v>
+        <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5126,8 +5111,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5170,7 +5160,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5184,10 +5174,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45937</v>
+        <v>46036</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5200,7 +5190,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5243,7 +5233,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19357-2026</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5257,10 +5247,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46133</v>
+        <v>45835</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5273,7 +5263,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5316,7 +5306,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5330,10 +5320,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45939</v>
+        <v>45912</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5346,7 +5336,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5389,7 +5379,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5403,10 +5393,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45951</v>
+        <v>45680</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5419,7 +5409,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5462,7 +5452,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5476,10 +5466,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45951</v>
+        <v>45918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5492,7 +5482,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5535,7 +5525,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5549,10 +5539,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45951</v>
+        <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5565,7 +5555,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5608,7 +5598,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5622,10 +5612,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45950</v>
+        <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5638,7 +5628,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5681,7 +5671,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5695,10 +5685,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45957</v>
+        <v>45099</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5711,7 +5701,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5754,7 +5744,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5768,10 +5758,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45957</v>
+        <v>44854</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5784,7 +5774,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5827,7 +5817,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5841,10 +5831,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45957</v>
+        <v>45356</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5857,7 +5847,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5900,7 +5890,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5914,10 +5904,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45957</v>
+        <v>46042</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5930,7 +5920,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5973,7 +5963,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5983,14 +5973,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45356</v>
+        <v>45177</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6003,7 +5993,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6046,7 +6036,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6060,10 +6050,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45581</v>
+        <v>45937</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6076,7 +6066,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6119,7 +6109,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6133,10 +6123,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45246</v>
+        <v>46042</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6149,7 +6139,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6192,7 +6182,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6206,10 +6196,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45964</v>
+        <v>45937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6222,7 +6212,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6265,7 +6255,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6279,10 +6269,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45730</v>
+        <v>45939</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6295,7 +6285,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6338,7 +6328,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6348,14 +6338,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45965</v>
+        <v>46044</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6368,7 +6358,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6411,7 +6401,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6425,10 +6415,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45965</v>
+        <v>46044</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6441,7 +6431,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6484,7 +6474,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6498,10 +6488,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45807</v>
+        <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6514,7 +6504,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6557,7 +6547,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6567,14 +6557,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45799</v>
+        <v>46044</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6587,7 +6577,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6630,7 +6620,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6644,10 +6634,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45974</v>
+        <v>44846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6660,7 +6650,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6703,7 +6693,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6717,10 +6707,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45974</v>
+        <v>45462</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6733,7 +6723,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6776,7 +6766,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6790,10 +6780,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45975</v>
+        <v>46048</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6806,7 +6796,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6849,7 +6839,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6863,10 +6853,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45975</v>
+        <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6879,7 +6869,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>8.5</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6922,7 +6912,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6936,10 +6926,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46044</v>
+        <v>45950</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6952,7 +6942,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6995,7 +6985,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7009,10 +6999,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45978</v>
+        <v>45951</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7025,7 +7015,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7068,7 +7058,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7082,10 +7072,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45978</v>
+        <v>45951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7098,7 +7088,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7141,7 +7131,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7155,10 +7145,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45978</v>
+        <v>45951</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7171,7 +7161,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7214,7 +7204,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7228,10 +7218,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45975</v>
+        <v>45957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7244,7 +7234,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7287,7 +7277,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7301,10 +7291,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45978</v>
+        <v>45957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7360,7 +7350,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7374,10 +7364,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45175</v>
+        <v>45957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7390,7 +7380,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7433,7 +7423,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7447,10 +7437,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45980</v>
+        <v>45957</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7463,7 +7453,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7506,7 +7496,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7520,10 +7510,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45980</v>
+        <v>45532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7535,13 +7525,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7584,7 +7569,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7598,10 +7583,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45980</v>
+        <v>45517</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7615,11 +7600,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7662,7 +7647,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7676,10 +7661,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44691</v>
+        <v>45672</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7691,8 +7676,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7735,7 +7725,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7745,14 +7735,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45069</v>
+        <v>45672</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7764,8 +7754,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7808,7 +7803,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7818,14 +7813,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44571</v>
+        <v>45730</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7838,7 +7833,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7881,7 +7876,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7895,10 +7890,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45581</v>
+        <v>45965</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7954,7 +7949,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7968,10 +7963,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45516</v>
+        <v>45964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7984,7 +7979,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8027,7 +8022,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8041,10 +8036,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45516</v>
+        <v>45965</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8057,7 +8052,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8100,7 +8095,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8114,10 +8109,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45103</v>
+        <v>46065</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8130,7 +8125,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8173,7 +8168,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8187,10 +8182,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45986</v>
+        <v>44929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8203,7 +8198,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8246,7 +8241,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8256,14 +8251,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45177</v>
+        <v>45974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8276,7 +8271,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8319,7 +8314,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8333,10 +8328,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45669</v>
+        <v>46066</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8349,7 +8344,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8392,7 +8387,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8402,14 +8397,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45992</v>
+        <v>45975</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8422,7 +8417,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.3</v>
+        <v>8.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8465,7 +8460,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21204-2026</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8479,10 +8474,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46146</v>
+        <v>45975</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8495,7 +8490,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8538,7 +8533,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8552,10 +8547,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45995</v>
+        <v>45975</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8568,7 +8563,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8611,7 +8606,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8625,10 +8620,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45713</v>
+        <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8641,7 +8636,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8684,7 +8679,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8698,10 +8693,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45996</v>
+        <v>45978</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8714,7 +8709,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8757,7 +8752,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8771,10 +8766,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46000</v>
+        <v>45669</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8787,7 +8782,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8830,7 +8825,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8844,10 +8839,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46000</v>
+        <v>46070</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8860,7 +8855,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8903,7 +8898,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8917,10 +8912,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46000</v>
+        <v>45357</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8933,7 +8928,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8976,7 +8971,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8990,10 +8985,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45411</v>
+        <v>46071</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9006,7 +9001,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9049,7 +9044,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9063,10 +9058,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46000</v>
+        <v>45978</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9079,7 +9074,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9122,7 +9117,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9136,10 +9131,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46148</v>
+        <v>45978</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9152,7 +9147,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9195,7 +9190,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9209,10 +9204,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46000</v>
+        <v>45978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9225,7 +9220,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9268,7 +9263,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9282,10 +9277,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46000</v>
+        <v>45582</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9298,7 +9293,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9341,7 +9336,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9351,14 +9346,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46000</v>
+        <v>45980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9370,8 +9365,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46000</v>
+        <v>45980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9487,7 +9487,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46000</v>
+        <v>45980</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9516,8 +9516,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9560,7 +9565,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9574,10 +9579,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46149</v>
+        <v>45608</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9590,7 +9595,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9633,7 +9638,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9647,10 +9652,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45103</v>
+        <v>45986</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9663,7 +9668,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9706,7 +9711,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9716,14 +9721,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46149</v>
+        <v>45992</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9736,7 +9741,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9779,7 +9784,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9793,10 +9798,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46000</v>
+        <v>45995</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9852,7 +9857,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9866,10 +9871,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45146</v>
+        <v>45713</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9882,7 +9887,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.4</v>
+        <v>0.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9925,7 +9930,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9935,14 +9940,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45644</v>
+        <v>45713</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9954,13 +9959,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10003,7 +10003,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44853</v>
+        <v>45996</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10076,7 +10076,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10090,10 +10090,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44509</v>
+        <v>46000</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45183</v>
+        <v>46000</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10222,7 +10222,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45680</v>
+        <v>46000</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10295,7 +10295,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10309,10 +10309,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10382,10 +10382,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10397,13 +10397,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>21.4</v>
+        <v>2.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10446,7 +10441,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10456,14 +10451,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45055</v>
+        <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10476,7 +10471,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10519,7 +10514,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10533,10 +10528,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46162</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10548,13 +10543,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10597,7 +10587,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10611,10 +10601,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46078</v>
+        <v>46000</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10627,7 +10617,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10670,7 +10660,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10684,10 +10674,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45509</v>
+        <v>46000</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10699,13 +10689,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10748,7 +10733,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10762,10 +10747,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46161</v>
+        <v>46000</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10778,7 +10763,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10821,7 +10806,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10835,10 +10820,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46030</v>
+        <v>45587</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10851,7 +10836,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10894,7 +10879,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10908,10 +10893,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46034</v>
+        <v>44970</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10924,7 +10909,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10967,7 +10952,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10981,10 +10966,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46034</v>
+        <v>45103</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10997,7 +10982,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>9.1</v>
+        <v>4.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11040,7 +11025,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11054,10 +11039,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45106</v>
+        <v>45146</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11070,7 +11055,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11113,7 +11098,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11127,10 +11112,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45106</v>
+        <v>46010</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11143,7 +11128,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11186,7 +11171,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11200,10 +11185,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46036</v>
+        <v>46013</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11215,8 +11200,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>21.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11259,7 +11249,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11273,10 +11263,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46042</v>
+        <v>45463</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11289,7 +11279,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11332,7 +11322,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11346,10 +11336,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46042</v>
+        <v>44935</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11362,7 +11352,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11405,7 +11395,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11419,10 +11409,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46170</v>
+        <v>45748</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11435,7 +11425,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11478,7 +11468,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11492,10 +11482,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44935</v>
+        <v>45615</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11508,7 +11498,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11551,7 +11541,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11561,14 +11551,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46044</v>
+        <v>46121</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11581,7 +11571,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11624,7 +11614,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11638,10 +11628,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46044</v>
+        <v>46126</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11654,7 +11644,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11697,7 +11687,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11711,10 +11701,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46175</v>
+        <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11726,13 +11716,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11775,7 +11760,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11785,14 +11770,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46044</v>
+        <v>45218</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11805,7 +11790,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11848,7 +11833,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 19357-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11862,10 +11847,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46175</v>
+        <v>46133</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11877,13 +11862,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11926,7 +11906,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11940,10 +11920,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46048</v>
+        <v>45146</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11956,7 +11936,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11999,7 +11979,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12013,10 +11993,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46048</v>
+        <v>45609</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12029,7 +12009,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12072,7 +12052,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12086,10 +12066,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46175</v>
+        <v>45730</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12101,13 +12081,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12150,7 +12125,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12164,10 +12139,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45118</v>
+        <v>45581</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12180,7 +12155,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12223,7 +12198,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12237,10 +12212,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46175</v>
+        <v>45807</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12252,13 +12227,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12301,7 +12271,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12315,10 +12285,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46175</v>
+        <v>45139</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12330,13 +12300,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12379,7 +12344,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12393,10 +12358,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45356</v>
+        <v>45175</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12409,7 +12374,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12452,7 +12417,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12466,10 +12431,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46176</v>
+        <v>45275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12482,7 +12447,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12525,7 +12490,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12539,10 +12504,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46176</v>
+        <v>46044</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12555,7 +12520,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12598,7 +12563,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12612,10 +12577,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45229</v>
+        <v>45549</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12628,7 +12593,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12671,7 +12636,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12685,10 +12650,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46066</v>
+        <v>45748</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12701,7 +12666,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12744,7 +12709,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12758,10 +12723,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46065</v>
+        <v>45799</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12774,7 +12739,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12817,7 +12782,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12831,10 +12796,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46070</v>
+        <v>45106</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12847,7 +12812,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12890,7 +12855,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 21204-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12904,10 +12869,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46071</v>
+        <v>46146</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12920,7 +12885,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12963,7 +12928,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12977,10 +12942,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45508</v>
+        <v>46149</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12992,13 +12957,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13041,7 +13001,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13055,10 +13015,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45730</v>
+        <v>46149</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13071,7 +13031,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13114,7 +13074,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13128,10 +13088,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45624</v>
+        <v>44953</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13144,7 +13104,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13187,7 +13147,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13201,10 +13161,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44501</v>
+        <v>45737</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13217,7 +13177,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>10.2</v>
+        <v>2.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13260,7 +13220,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13274,10 +13234,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45463</v>
+        <v>46148</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13290,7 +13250,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13333,7 +13293,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13347,10 +13307,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45608</v>
+        <v>45439</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13363,7 +13323,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13406,7 +13366,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13420,10 +13380,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46198</v>
+        <v>44501</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13436,7 +13396,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13479,7 +13439,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13493,10 +13453,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45713</v>
+        <v>46161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13509,7 +13469,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13552,7 +13512,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13566,10 +13526,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45146</v>
+        <v>46078</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13582,7 +13542,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13625,7 +13585,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13639,10 +13599,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46245</v>
+        <v>45624</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13655,7 +13615,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13698,7 +13658,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13712,10 +13672,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45582</v>
+        <v>45609</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13728,7 +13688,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13771,7 +13731,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13785,10 +13745,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45118</v>
+        <v>45609</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13801,7 +13761,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13844,7 +13804,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13858,10 +13818,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45127</v>
+        <v>45098</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13874,7 +13834,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13917,7 +13877,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13931,10 +13891,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45580</v>
+        <v>46162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13952,7 +13912,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13995,7 +13955,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14009,10 +13969,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45509</v>
+        <v>44747</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14025,7 +13985,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14068,7 +14028,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14082,10 +14042,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45609</v>
+        <v>45509</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14097,8 +14057,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14141,7 +14106,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14155,10 +14120,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45609</v>
+        <v>45771</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14170,8 +14135,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14214,7 +14184,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14228,10 +14198,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45713</v>
+        <v>46170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14244,7 +14214,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14287,7 +14257,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14301,10 +14271,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45439</v>
+        <v>46175</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14316,8 +14286,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14360,7 +14335,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14374,10 +14349,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45275</v>
+        <v>46175</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14389,8 +14364,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14433,7 +14413,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14447,10 +14427,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46253</v>
+        <v>46175</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14462,8 +14442,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14506,7 +14491,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14520,10 +14505,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46210</v>
+        <v>46175</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14535,8 +14520,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14579,7 +14569,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14589,14 +14579,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46253</v>
+        <v>46176</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14609,7 +14599,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14652,7 +14642,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14666,10 +14656,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45713</v>
+        <v>46175</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14681,8 +14671,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14725,7 +14720,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14739,10 +14734,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45713</v>
+        <v>46176</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14755,7 +14750,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14798,7 +14793,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14808,14 +14803,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45146</v>
+        <v>44987</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14828,7 +14823,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14871,7 +14866,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14881,14 +14876,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46253</v>
+        <v>45231</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14901,7 +14896,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14944,7 +14939,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14958,10 +14953,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45737</v>
+        <v>45509</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14974,7 +14969,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15017,7 +15012,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15031,10 +15026,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45098</v>
+        <v>45508</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15046,8 +15041,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15090,7 +15090,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44987</v>
+        <v>44509</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15163,7 +15163,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15177,10 +15177,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45139</v>
+        <v>45106</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15236,7 +15236,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15250,10 +15250,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45615</v>
+        <v>45118</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46255</v>
+        <v>45118</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15382,7 +15382,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15396,10 +15396,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45440</v>
+        <v>44979</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15411,13 +15411,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15460,7 +15455,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15474,10 +15469,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45231</v>
+        <v>46198</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15490,7 +15485,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15533,7 +15528,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15547,10 +15542,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15563,7 +15558,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15606,7 +15601,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15616,14 +15611,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44987</v>
+        <v>45069</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15636,7 +15631,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15679,7 +15674,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15693,10 +15688,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45757</v>
+        <v>44987</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15709,7 +15704,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15752,7 +15747,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15762,14 +15757,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45775</v>
+        <v>46253</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15782,7 +15777,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15825,7 +15820,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15839,10 +15834,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44581</v>
+        <v>46253</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15855,7 +15850,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15898,7 +15893,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15912,10 +15907,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45532</v>
+        <v>45580</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15927,8 +15922,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15981,14 +15981,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45532</v>
+        <v>46253</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16044,7 +16044,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16058,10 +16058,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45532</v>
+        <v>46210</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16117,7 +16117,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16131,10 +16131,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45474</v>
+        <v>45440</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16195,7 +16195,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16209,10 +16209,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44979</v>
+        <v>45390</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16268,7 +16268,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16282,10 +16282,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46140</v>
+        <v>46255</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16355,10 +16355,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44509</v>
+        <v>45713</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16487,7 +16487,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46268</v>
+        <v>45516</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16560,7 +16560,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16570,14 +16570,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16589,13 +16589,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16638,7 +16633,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16652,10 +16647,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44953</v>
+        <v>45581</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16668,7 +16663,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16711,7 +16706,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16721,14 +16716,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44747</v>
+        <v>45644</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16740,8 +16735,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16784,7 +16784,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16798,10 +16798,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46274</v>
+        <v>46140</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16871,10 +16871,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46274</v>
+        <v>45259</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16930,7 +16930,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45587</v>
+        <v>44509</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17003,7 +17003,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17017,10 +17017,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46273</v>
+        <v>45474</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17032,8 +17032,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17076,7 +17081,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17086,14 +17091,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17105,8 +17110,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>7.9</v>
+        <v>3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17149,7 +17159,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17163,10 +17173,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45748</v>
+        <v>46268</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17179,7 +17189,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17222,7 +17232,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17236,10 +17246,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45672</v>
+        <v>45188</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17251,13 +17261,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17300,7 +17305,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17314,10 +17319,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45672</v>
+        <v>44747</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17329,13 +17334,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17378,7 +17378,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17392,10 +17392,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45609</v>
+        <v>45775</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17451,7 +17451,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17465,10 +17465,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45118</v>
+        <v>44816</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17524,7 +17524,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17538,10 +17538,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17597,7 +17597,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45782</v>
+        <v>46273</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.8</v>
+        <v>7.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17670,7 +17670,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17684,10 +17684,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45782</v>
+        <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17743,7 +17743,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17757,10 +17757,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45790</v>
+        <v>45713</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17772,13 +17772,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17821,7 +17816,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17835,10 +17830,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45791</v>
+        <v>45356</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17850,13 +17845,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17899,7 +17889,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17913,10 +17903,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45791</v>
+        <v>45183</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17928,13 +17918,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17977,7 +17962,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 23567-2025</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17991,10 +17976,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45792</v>
+        <v>45713</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18007,7 +17992,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18050,7 +18035,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18064,10 +18049,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45187</v>
+        <v>46274</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18080,7 +18065,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18123,7 +18108,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18137,10 +18122,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45792</v>
+        <v>45118</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18152,13 +18137,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18201,7 +18181,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18215,10 +18195,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45792</v>
+        <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18231,7 +18211,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18274,7 +18254,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18288,10 +18268,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45793</v>
+        <v>45782</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18304,7 +18284,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18347,7 +18327,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18361,10 +18341,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45797</v>
+        <v>46280</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18377,7 +18357,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18420,7 +18400,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18434,10 +18414,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45797</v>
+        <v>45187</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18450,7 +18430,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18493,7 +18473,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18507,10 +18487,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45800</v>
+        <v>45791</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18522,8 +18502,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18566,7 +18551,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18580,10 +18565,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45799</v>
+        <v>45791</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18595,8 +18580,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18639,7 +18629,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18653,10 +18643,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45800</v>
+        <v>45790</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18668,8 +18658,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18712,7 +18707,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 23567-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18726,10 +18721,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45799</v>
+        <v>45792</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18742,7 +18737,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18785,7 +18780,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18799,10 +18794,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45799</v>
+        <v>45793</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18815,7 +18810,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.6</v>
+        <v>8.1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18858,7 +18853,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18872,10 +18867,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45799</v>
+        <v>45792</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18887,8 +18882,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18931,7 +18931,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18945,10 +18945,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45799</v>
+        <v>45792</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19004,7 +19004,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19014,14 +19014,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45827</v>
+        <v>45797</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19077,7 +19077,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19091,10 +19091,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45835</v>
+        <v>45797</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19150,7 +19150,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19164,10 +19164,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44559</v>
+        <v>45250</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>60.7</v>
+        <v>31.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19228,7 +19228,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19242,10 +19242,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44645</v>
+        <v>44559</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19257,8 +19257,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>15.8</v>
+        <v>60.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19301,7 +19306,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19315,10 +19320,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45250</v>
+        <v>44645</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19330,13 +19335,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>31.7</v>
+        <v>15.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19396,7 +19396,7 @@
         <v>45775</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46070</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>46073</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46114</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46108</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45698</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 62418-2025</t>
+          <t>A 55173-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46007</v>
+        <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1648,17 +1648,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1688,248 +1688,248 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 62418-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 60033-2024</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45642</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>5.3</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Ögonpyrola</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 55173-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45237</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44651</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44524</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>44854</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>44565</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>44610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45229</v>
+        <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45411</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45532</v>
+        <v>45748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45532</v>
+        <v>45390</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2965,14 +2965,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44571</v>
+        <v>44816</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45127</v>
+        <v>44929</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44747</v>
+        <v>45503</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3130,8 +3130,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3174,7 +3179,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3184,14 +3189,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45055</v>
+        <v>45504</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3203,8 +3208,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3247,7 +3257,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3261,10 +3271,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45757</v>
+        <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3276,8 +3286,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3320,7 +3335,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3334,10 +3349,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44853</v>
+        <v>45884</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3350,7 +3365,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3393,7 +3408,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3407,10 +3422,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45503</v>
+        <v>46066</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3422,13 +3437,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3471,7 +3481,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3485,10 +3495,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45504</v>
+        <v>46065</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,13 +3510,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3549,7 +3554,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3563,10 +3568,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44691</v>
+        <v>46070</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3579,7 +3584,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3622,7 +3627,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3636,10 +3641,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45516</v>
+        <v>46071</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3652,7 +3657,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3695,7 +3700,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3709,10 +3714,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45799</v>
+        <v>44970</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3725,7 +3730,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3768,7 +3773,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3778,14 +3783,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45799</v>
+        <v>45827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3798,7 +3803,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3841,7 +3846,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3855,10 +3860,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45799</v>
+        <v>45835</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3871,7 +3876,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3914,7 +3919,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3928,10 +3933,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45799</v>
+        <v>45356</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3944,7 +3949,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3987,7 +3992,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45799</v>
+        <v>45581</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4017,7 +4022,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4060,7 +4065,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4070,14 +4075,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45146</v>
+        <v>45246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4090,7 +4095,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4133,7 +4138,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4147,10 +4152,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45800</v>
+        <v>45730</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4163,7 +4168,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4206,7 +4211,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45800</v>
+        <v>44565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4236,7 +4241,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4279,7 +4284,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4293,10 +4298,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45103</v>
+        <v>46121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4309,7 +4314,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4352,7 +4357,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4366,10 +4371,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46030</v>
+        <v>45516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4382,7 +4387,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4425,7 +4430,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4439,10 +4444,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45884</v>
+        <v>45516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4455,7 +4460,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4498,7 +4503,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4512,10 +4517,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44565</v>
+        <v>45462</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4528,7 +4533,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4571,7 +4576,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4585,10 +4590,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45246</v>
+        <v>45103</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4601,7 +4606,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4644,7 +4649,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4658,10 +4663,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46034</v>
+        <v>46126</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4674,7 +4679,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4717,7 +4722,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4731,10 +4736,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45827</v>
+        <v>45177</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4747,7 +4752,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4790,7 +4795,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4804,10 +4809,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45905</v>
+        <v>45669</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4820,7 +4825,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4863,7 +4868,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 19357-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4877,10 +4882,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46034</v>
+        <v>46133</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4893,7 +4898,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9.1</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4953,7 +4958,7 @@
         <v>45908</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5009,7 +5014,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5023,10 +5028,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45909</v>
+        <v>45905</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5039,7 +5044,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5082,7 +5087,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5096,10 +5101,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45909</v>
+        <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5111,13 +5116,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5160,7 +5160,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46036</v>
+        <v>45909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5233,7 +5233,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45835</v>
+        <v>45909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5262,8 +5262,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5323,7 +5328,7 @@
         <v>45912</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5379,7 +5384,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5393,10 +5398,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45680</v>
+        <v>45918</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5409,7 +5414,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5469,7 +5474,7 @@
         <v>45918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5525,7 +5530,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5542,7 +5547,7 @@
         <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5555,7 +5560,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5598,7 +5603,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5608,14 +5613,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45918</v>
+        <v>45644</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5627,8 +5632,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5671,7 +5681,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5685,10 +5695,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45099</v>
+        <v>44853</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5701,7 +5711,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5744,7 +5754,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5758,10 +5768,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44854</v>
+        <v>44509</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5774,7 +5784,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5817,7 +5827,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5831,10 +5841,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45356</v>
+        <v>45183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5847,7 +5857,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5890,7 +5900,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5904,10 +5914,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46042</v>
+        <v>45680</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5920,7 +5930,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5963,7 +5973,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5973,14 +5983,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45177</v>
+        <v>45807</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5993,7 +6003,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6036,7 +6046,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6050,10 +6060,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45937</v>
+        <v>45799</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6066,7 +6076,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6109,7 +6119,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6119,14 +6129,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46042</v>
+        <v>45055</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6139,7 +6149,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6182,7 +6192,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6196,10 +6206,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45937</v>
+        <v>45509</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6211,8 +6221,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6255,7 +6270,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6269,10 +6284,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45939</v>
+        <v>46044</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6285,7 +6300,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6328,7 +6343,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6338,14 +6353,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46044</v>
+        <v>45106</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6358,7 +6373,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6401,7 +6416,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6415,10 +6430,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46044</v>
+        <v>45106</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6431,7 +6446,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6474,7 +6489,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6488,10 +6503,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45257</v>
+        <v>45175</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6504,7 +6519,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6547,7 +6562,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6557,14 +6572,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46044</v>
+        <v>45581</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6577,7 +6592,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6620,7 +6635,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 21204-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6634,10 +6649,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44846</v>
+        <v>46146</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6650,7 +6665,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6693,7 +6708,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6707,10 +6722,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45462</v>
+        <v>45356</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6723,7 +6738,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6766,7 +6781,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6780,10 +6795,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46048</v>
+        <v>46148</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6796,7 +6811,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6839,7 +6854,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6853,10 +6868,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46048</v>
+        <v>46149</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6869,7 +6884,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6912,7 +6927,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6926,10 +6941,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45950</v>
+        <v>46149</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6942,7 +6957,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6985,7 +7000,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6999,10 +7014,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45951</v>
+        <v>45229</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7015,7 +7030,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7058,7 +7073,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7072,10 +7087,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45951</v>
+        <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7088,7 +7103,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7131,7 +7146,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7145,10 +7160,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45951</v>
+        <v>45937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7161,7 +7176,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7204,7 +7219,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7218,10 +7233,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45957</v>
+        <v>46162</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7233,8 +7248,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7277,7 +7297,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7291,10 +7311,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45957</v>
+        <v>46078</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7307,7 +7327,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7350,7 +7370,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7364,10 +7384,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45957</v>
+        <v>46161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7380,7 +7400,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7423,7 +7443,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7437,10 +7457,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45957</v>
+        <v>45939</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7453,7 +7473,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7496,7 +7516,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7510,10 +7530,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45532</v>
+        <v>46170</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7526,7 +7546,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7569,7 +7589,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7583,10 +7603,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45517</v>
+        <v>46175</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7604,7 +7624,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7647,7 +7667,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7661,10 +7681,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45672</v>
+        <v>46175</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7678,11 +7698,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7725,7 +7745,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7739,10 +7759,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45672</v>
+        <v>45713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7754,13 +7774,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7803,7 +7818,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7817,10 +7832,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45730</v>
+        <v>46175</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7832,8 +7847,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7876,7 +7896,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7890,10 +7910,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45965</v>
+        <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7905,8 +7925,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7949,7 +7974,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7963,10 +7988,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45964</v>
+        <v>46175</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7978,8 +8003,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8022,7 +8052,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8036,10 +8066,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45965</v>
+        <v>46176</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8052,7 +8082,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8095,7 +8125,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8109,10 +8139,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46065</v>
+        <v>45146</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8125,7 +8155,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8168,7 +8198,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8182,10 +8212,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44929</v>
+        <v>45951</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8198,7 +8228,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8241,7 +8271,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8255,10 +8285,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45974</v>
+        <v>46176</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8271,7 +8301,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8314,7 +8344,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8328,10 +8358,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46066</v>
+        <v>45951</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8344,7 +8374,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8387,7 +8417,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8401,10 +8431,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45975</v>
+        <v>45951</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8417,7 +8447,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8460,7 +8490,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8474,10 +8504,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45975</v>
+        <v>45950</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8490,7 +8520,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8533,7 +8563,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8547,10 +8577,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45975</v>
+        <v>45582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8563,7 +8593,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8606,7 +8636,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8620,10 +8650,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45974</v>
+        <v>45118</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8679,7 +8709,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8693,10 +8723,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45978</v>
+        <v>45127</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8709,7 +8739,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8752,7 +8782,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8766,10 +8796,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45669</v>
+        <v>45580</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8781,8 +8811,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8825,7 +8860,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8839,10 +8874,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46070</v>
+        <v>45509</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8855,7 +8890,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8898,7 +8933,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8912,10 +8947,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45357</v>
+        <v>45957</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8928,7 +8963,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8971,7 +9006,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8985,10 +9020,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46071</v>
+        <v>45957</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9001,7 +9036,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9044,7 +9079,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9058,10 +9093,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45978</v>
+        <v>45957</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9117,7 +9152,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9131,10 +9166,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45978</v>
+        <v>45609</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9147,7 +9182,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9190,7 +9225,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9204,10 +9239,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45978</v>
+        <v>45609</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9220,7 +9255,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9263,7 +9298,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9277,10 +9312,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45582</v>
+        <v>45957</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9293,7 +9328,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9336,7 +9371,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9350,10 +9385,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45980</v>
+        <v>45713</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9365,13 +9400,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9414,7 +9444,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9428,10 +9458,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45980</v>
+        <v>45439</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9444,7 +9474,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9487,7 +9517,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9501,10 +9531,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45980</v>
+        <v>45964</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9516,13 +9546,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>3.7</v>
+        <v>6.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9565,7 +9590,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9579,10 +9604,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45608</v>
+        <v>45965</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9595,7 +9620,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9638,7 +9663,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9652,10 +9677,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45986</v>
+        <v>45965</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9668,7 +9693,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9711,7 +9736,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9721,14 +9746,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45992</v>
+        <v>45974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9741,7 +9766,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9784,7 +9809,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9798,10 +9823,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45995</v>
+        <v>45737</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9814,7 +9839,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9857,7 +9882,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9871,10 +9896,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45713</v>
+        <v>45098</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9887,7 +9912,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9930,7 +9955,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9944,10 +9969,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45713</v>
+        <v>45974</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9960,7 +9985,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10003,7 +10028,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10017,10 +10042,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45996</v>
+        <v>46198</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10033,7 +10058,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10076,7 +10101,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10090,10 +10115,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46000</v>
+        <v>45975</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10106,7 +10131,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>8.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10149,7 +10174,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10159,14 +10184,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46000</v>
+        <v>45975</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10179,7 +10204,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10222,7 +10247,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10236,10 +10261,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46000</v>
+        <v>45978</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10252,7 +10277,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10295,7 +10320,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10309,10 +10334,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46000</v>
+        <v>45978</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10325,7 +10350,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10368,7 +10393,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10382,10 +10407,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46000</v>
+        <v>45978</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10398,7 +10423,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10441,7 +10466,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10455,10 +10480,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46000</v>
+        <v>45975</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10471,7 +10496,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10514,7 +10539,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10528,10 +10553,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>45978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10544,7 +10569,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10587,7 +10612,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10601,10 +10626,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46000</v>
+        <v>46245</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10617,7 +10642,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10660,7 +10685,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10674,10 +10699,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46000</v>
+        <v>45440</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10689,8 +10714,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10733,7 +10763,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10747,10 +10777,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46000</v>
+        <v>45980</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10763,7 +10793,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>6.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10806,7 +10836,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10820,10 +10850,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45587</v>
+        <v>45980</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10835,8 +10865,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10879,7 +10914,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10893,10 +10928,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44970</v>
+        <v>45980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10908,8 +10943,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10952,7 +10992,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10966,10 +11006,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45103</v>
+        <v>45231</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10982,7 +11022,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11025,7 +11065,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11039,10 +11079,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45146</v>
+        <v>44581</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11055,7 +11095,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11098,7 +11138,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11112,10 +11152,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46010</v>
+        <v>45986</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11128,7 +11168,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11171,7 +11211,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11185,10 +11225,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46013</v>
+        <v>45188</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11200,13 +11240,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>21.4</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11249,7 +11284,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11263,10 +11298,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45463</v>
+        <v>46253</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11279,7 +11314,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11322,7 +11357,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11336,10 +11371,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44935</v>
+        <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11352,7 +11387,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11395,7 +11430,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11409,10 +11444,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45748</v>
+        <v>45099</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11425,7 +11460,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11468,7 +11503,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11478,14 +11513,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45615</v>
+        <v>46253</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11498,7 +11533,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11541,7 +11576,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11555,10 +11590,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46121</v>
+        <v>45257</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11571,7 +11606,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11614,7 +11649,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11624,14 +11659,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46126</v>
+        <v>46253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11644,7 +11679,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11687,7 +11722,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11697,14 +11732,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44581</v>
+        <v>45992</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11717,7 +11752,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11760,7 +11795,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11774,10 +11809,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45218</v>
+        <v>44854</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11790,7 +11825,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11833,7 +11868,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19357-2026</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11847,10 +11882,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46133</v>
+        <v>46255</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11863,7 +11898,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11906,7 +11941,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11920,10 +11955,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45146</v>
+        <v>45357</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11936,7 +11971,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11979,7 +12014,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11993,10 +12028,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45609</v>
+        <v>46260</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12009,7 +12044,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12052,7 +12087,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12066,10 +12101,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45730</v>
+        <v>45771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12081,8 +12116,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12125,7 +12165,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12139,10 +12179,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45581</v>
+        <v>45995</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12155,7 +12195,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12198,7 +12238,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12212,10 +12252,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45807</v>
+        <v>45996</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12228,7 +12268,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12271,7 +12311,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12285,10 +12325,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45139</v>
+        <v>44747</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12301,7 +12341,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12344,7 +12384,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12358,10 +12398,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45175</v>
+        <v>44747</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12374,7 +12414,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12417,7 +12457,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12431,10 +12471,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45275</v>
+        <v>46000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12447,7 +12487,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12490,7 +12530,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12504,10 +12544,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46044</v>
+        <v>46000</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12520,7 +12560,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12563,7 +12603,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12577,10 +12617,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45549</v>
+        <v>46000</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12593,7 +12633,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12636,7 +12676,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12650,10 +12690,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45748</v>
+        <v>46000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12666,7 +12706,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12709,7 +12749,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12723,10 +12763,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45799</v>
+        <v>46000</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12739,7 +12779,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12782,7 +12822,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12796,10 +12836,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45106</v>
+        <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12812,7 +12852,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12855,7 +12895,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 21204-2026</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12865,14 +12905,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46146</v>
+        <v>46000</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12885,7 +12925,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12928,7 +12968,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12942,10 +12982,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46149</v>
+        <v>46000</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12958,7 +12998,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13001,7 +13041,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13015,10 +13055,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46149</v>
+        <v>46000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13031,7 +13071,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13074,7 +13114,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13088,10 +13128,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44953</v>
+        <v>45103</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13104,7 +13144,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13147,7 +13187,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13161,10 +13201,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45737</v>
+        <v>46000</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13177,7 +13217,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13220,7 +13260,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13234,10 +13274,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46148</v>
+        <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13250,7 +13290,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13293,7 +13333,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13307,10 +13347,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45439</v>
+        <v>46140</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13323,7 +13363,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13366,7 +13406,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13380,10 +13420,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44501</v>
+        <v>44509</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13396,7 +13436,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>10.2</v>
+        <v>2.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13439,7 +13479,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13453,10 +13493,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46161</v>
+        <v>46267</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13469,7 +13509,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13512,7 +13552,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13526,10 +13566,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46078</v>
+        <v>46268</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13542,7 +13582,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13585,7 +13625,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13599,10 +13639,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45624</v>
+        <v>45259</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13615,7 +13655,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13658,7 +13698,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13672,10 +13712,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45609</v>
+        <v>45549</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13688,7 +13728,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13731,7 +13771,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13741,14 +13781,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45609</v>
+        <v>46269</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13760,8 +13800,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13804,7 +13849,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13818,10 +13863,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45098</v>
+        <v>46010</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13834,7 +13879,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13877,7 +13922,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13891,10 +13936,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46162</v>
+        <v>46274</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13906,13 +13951,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13955,7 +13995,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13969,10 +14009,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44747</v>
+        <v>46274</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13985,7 +14025,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14028,7 +14068,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14042,10 +14082,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45509</v>
+        <v>46013</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14059,11 +14099,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>21.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14106,7 +14146,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14120,10 +14160,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45771</v>
+        <v>46273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14135,13 +14175,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14184,7 +14219,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14198,10 +14233,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46170</v>
+        <v>46273</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14214,7 +14249,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>7.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14257,7 +14292,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14271,10 +14306,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46175</v>
+        <v>46280</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14286,13 +14321,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14335,7 +14365,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14349,10 +14379,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46175</v>
+        <v>44691</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14364,13 +14394,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14413,7 +14438,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14423,14 +14448,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46175</v>
+        <v>45069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14442,13 +14467,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14491,7 +14511,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14501,14 +14521,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46175</v>
+        <v>44571</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14520,13 +14540,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14569,7 +14584,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14583,10 +14598,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46176</v>
+        <v>46030</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14599,7 +14614,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14642,7 +14657,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14656,10 +14671,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46175</v>
+        <v>46034</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14671,13 +14686,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14720,7 +14730,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14734,10 +14744,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46176</v>
+        <v>46034</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14750,7 +14760,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>5.9</v>
+        <v>9.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14793,7 +14803,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14807,10 +14817,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44987</v>
+        <v>45411</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14823,7 +14833,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14866,7 +14876,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14880,10 +14890,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45231</v>
+        <v>46036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14896,7 +14906,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14939,7 +14949,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14953,10 +14963,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45509</v>
+        <v>44935</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15012,7 +15022,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15026,10 +15036,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45508</v>
+        <v>46042</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15041,13 +15051,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15090,7 +15095,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15104,10 +15109,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44509</v>
+        <v>46042</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15120,7 +15125,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15163,7 +15168,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15177,10 +15182,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45106</v>
+        <v>45118</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15193,7 +15198,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15236,7 +15241,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15246,14 +15251,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45118</v>
+        <v>46044</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15266,7 +15271,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15309,7 +15314,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15323,10 +15328,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45118</v>
+        <v>46044</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15339,7 +15344,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15382,7 +15387,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15392,14 +15397,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44979</v>
+        <v>46044</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15412,7 +15417,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15455,7 +15460,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15469,10 +15474,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46198</v>
+        <v>46048</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15485,7 +15490,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15528,7 +15533,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15542,10 +15547,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46245</v>
+        <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15558,7 +15563,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15601,7 +15606,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15611,14 +15616,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45069</v>
+        <v>45508</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15630,8 +15635,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15674,7 +15684,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15688,10 +15698,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44987</v>
+        <v>45730</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15704,7 +15714,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15747,7 +15757,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15757,14 +15767,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46253</v>
+        <v>45624</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15777,7 +15787,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15820,7 +15830,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15834,10 +15844,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46253</v>
+        <v>44501</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15850,7 +15860,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.3</v>
+        <v>10.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15893,7 +15903,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15907,10 +15917,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45580</v>
+        <v>45463</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15922,13 +15932,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15971,7 +15976,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15981,14 +15986,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46253</v>
+        <v>45608</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16001,7 +16006,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16044,7 +16049,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16058,10 +16063,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46210</v>
+        <v>45275</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16074,7 +16079,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.6</v>
+        <v>6.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16117,7 +16122,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16131,10 +16136,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45440</v>
+        <v>45713</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16146,13 +16151,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16195,7 +16195,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16209,10 +16209,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45390</v>
+        <v>45713</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16268,7 +16268,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16278,14 +16278,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46255</v>
+        <v>45146</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16355,10 +16355,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45713</v>
+        <v>44987</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46260</v>
+        <v>45139</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16487,7 +16487,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45516</v>
+        <v>45615</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16560,7 +16560,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16574,10 +16574,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46267</v>
+        <v>44987</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16633,7 +16633,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16647,10 +16647,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45581</v>
+        <v>45757</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16706,7 +16706,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16716,14 +16716,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45644</v>
+        <v>45775</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16735,13 +16735,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16784,7 +16779,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16798,10 +16793,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46140</v>
+        <v>45532</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16814,7 +16809,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16857,7 +16852,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16871,10 +16866,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45259</v>
+        <v>45532</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16887,7 +16882,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16930,7 +16925,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16944,10 +16939,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44509</v>
+        <v>45532</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16960,7 +16955,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17020,7 +17015,7 @@
         <v>45474</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17081,7 +17076,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17091,14 +17086,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46269</v>
+        <v>44979</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17110,13 +17105,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17159,7 +17149,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17173,10 +17163,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46268</v>
+        <v>44953</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17189,7 +17179,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17232,7 +17222,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17246,10 +17236,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45188</v>
+        <v>44747</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17262,7 +17252,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17305,7 +17295,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17319,10 +17309,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44747</v>
+        <v>45587</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17335,7 +17325,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17378,7 +17368,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17392,10 +17382,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45775</v>
+        <v>45748</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17408,7 +17398,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17451,7 +17441,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17465,10 +17455,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44816</v>
+        <v>45672</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17480,8 +17470,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17524,7 +17519,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17538,10 +17533,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46273</v>
+        <v>45672</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17553,8 +17548,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17597,7 +17597,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46273</v>
+        <v>45609</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>7.9</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17670,7 +17670,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17684,10 +17684,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46274</v>
+        <v>45118</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17743,7 +17743,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17757,10 +17757,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45713</v>
+        <v>45782</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17830,10 +17830,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45356</v>
+        <v>45782</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17903,10 +17903,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45183</v>
+        <v>45790</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17918,8 +17918,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17962,7 +17967,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17976,10 +17981,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45713</v>
+        <v>45791</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17991,8 +17996,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18035,7 +18045,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18049,10 +18059,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46274</v>
+        <v>45791</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18064,8 +18074,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18108,7 +18123,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 23567-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18122,10 +18137,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45118</v>
+        <v>45792</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18138,7 +18153,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18181,7 +18196,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18195,10 +18210,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45782</v>
+        <v>45187</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18211,7 +18226,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18254,7 +18269,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18268,10 +18283,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45782</v>
+        <v>45792</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18283,8 +18298,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18327,7 +18347,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18341,10 +18361,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46280</v>
+        <v>45792</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18357,7 +18377,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18400,7 +18420,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18414,10 +18434,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45187</v>
+        <v>45793</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18430,7 +18450,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18473,7 +18493,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18487,10 +18507,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45791</v>
+        <v>45797</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18502,13 +18522,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18551,7 +18566,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18565,10 +18580,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45791</v>
+        <v>45797</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18580,13 +18595,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18629,7 +18639,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18643,10 +18653,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45790</v>
+        <v>45800</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18658,13 +18668,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18707,7 +18712,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 23567-2025</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18721,10 +18726,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45792</v>
+        <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18737,7 +18742,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18780,7 +18785,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18794,10 +18799,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45793</v>
+        <v>45800</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18810,7 +18815,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18853,7 +18858,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18867,10 +18872,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45792</v>
+        <v>45799</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18882,13 +18887,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18931,7 +18931,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18945,10 +18945,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45792</v>
+        <v>45799</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19004,7 +19004,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45797</v>
+        <v>45799</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19077,7 +19077,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19091,10 +19091,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45797</v>
+        <v>45799</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19150,7 +19150,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19164,10 +19164,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45250</v>
+        <v>44559</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>31.7</v>
+        <v>60.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19228,7 +19228,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19242,10 +19242,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44559</v>
+        <v>44645</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19257,13 +19257,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>60.7</v>
+        <v>15.8</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19306,7 +19301,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19320,10 +19315,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44645</v>
+        <v>45250</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19335,8 +19330,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>15.8</v>
+        <v>31.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19396,7 +19396,7 @@
         <v>45775</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46070</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>46073</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46114</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 16140-2026</t>
+          <t>A 6179-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46108</v>
+        <v>45698</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,13 +1436,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1469,156 +1469,156 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 6179-2025 artfynd.xlsx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 6179-2025 karta.png", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 6179-2025 georefererad karta.tif", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 6179-2025 FSC-klagomål.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 6179-2025 FSC-klagomål mail.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 6179-2025 tillsynsbegäran.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 6179-2025 tillsynsbegäran mail.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 16140-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bollvitmossa
 Utter</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 16140-2026 artfynd.xlsx", "A 16140-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 16140-2026 karta.png", "A 16140-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 16140-2026 georefererad karta.tif", "A 16140-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 16140-2026 FSC-klagomål.docx", "A 16140-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 16140-2026 FSC-klagomål mail.docx", "A 16140-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 16140-2026 tillsynsbegäran.docx", "A 16140-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 16140-2026 tillsynsbegäran mail.docx", "A 16140-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 6179-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45698</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 6179-2025 artfynd.xlsx", "A 6179-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 6179-2025 karta.png", "A 6179-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 6179-2025 georefererad karta.tif", "A 6179-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 6179-2025 FSC-klagomål.docx", "A 6179-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 6179-2025 FSC-klagomål mail.docx", "A 6179-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 6179-2025 tillsynsbegäran.docx", "A 6179-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 6179-2025 tillsynsbegäran mail.docx", "A 6179-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55173-2023</t>
+          <t>A 60033-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45237</v>
+        <v>45642</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1688,35 +1688,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
         <v>46007</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60033-2024</t>
+          <t>A 55173-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45642</v>
+        <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,17 +1858,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1898,35 +1898,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
         <v>45701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44651</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44524</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>44854</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>44565</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>44610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45218</v>
+        <v>45229</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45532</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45748</v>
+        <v>45532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45390</v>
+        <v>45411</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2965,14 +2965,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44816</v>
+        <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44929</v>
+        <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45503</v>
+        <v>44747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3130,13 +3130,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3179,7 +3174,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45504</v>
+        <v>45757</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,13 +3203,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3257,7 +3247,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3267,14 +3257,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45517</v>
+        <v>45055</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3286,13 +3276,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3335,7 +3320,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3349,10 +3334,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45884</v>
+        <v>44853</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3365,7 +3350,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3408,7 +3393,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3422,10 +3407,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46066</v>
+        <v>45503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3437,8 +3422,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3481,7 +3471,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3495,10 +3485,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46065</v>
+        <v>45504</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3510,8 +3500,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3554,7 +3549,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3568,10 +3563,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46070</v>
+        <v>44691</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3584,7 +3579,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3627,7 +3622,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46071</v>
+        <v>45516</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3657,7 +3652,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3700,7 +3695,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3710,14 +3705,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44970</v>
+        <v>45146</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3730,7 +3725,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3773,7 +3768,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3783,14 +3778,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45827</v>
+        <v>45103</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3803,7 +3798,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3846,7 +3841,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3860,10 +3855,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45835</v>
+        <v>45246</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3876,7 +3871,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3919,7 +3914,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3933,10 +3928,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45356</v>
+        <v>45680</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3949,7 +3944,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3992,7 +3987,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45581</v>
+        <v>45099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4022,7 +4017,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4065,7 +4060,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4079,10 +4074,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45246</v>
+        <v>44854</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4095,7 +4090,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4138,7 +4133,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4148,14 +4143,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45730</v>
+        <v>45177</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4168,7 +4163,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4211,7 +4206,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44565</v>
+        <v>45356</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4284,7 +4279,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4298,10 +4293,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46121</v>
+        <v>45257</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4314,7 +4309,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4357,7 +4352,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4371,10 +4366,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45516</v>
+        <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4387,7 +4382,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4430,7 +4425,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45516</v>
+        <v>45532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4460,7 +4455,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4503,7 +4498,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4517,10 +4512,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45462</v>
+        <v>45517</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4532,8 +4527,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4576,7 +4576,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45103</v>
+        <v>45672</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4605,8 +4605,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4649,7 +4654,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4663,10 +4668,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46126</v>
+        <v>45672</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4678,8 +4683,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4722,7 +4732,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4732,14 +4742,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45177</v>
+        <v>45730</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4752,7 +4762,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4795,7 +4805,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4809,10 +4819,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45669</v>
+        <v>44929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4825,7 +4835,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4868,7 +4878,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19357-2026</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4882,10 +4892,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46133</v>
+        <v>45669</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4898,7 +4908,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4941,7 +4951,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4951,14 +4961,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45908</v>
+        <v>45357</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4971,7 +4981,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5014,7 +5024,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5028,10 +5038,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45905</v>
+        <v>45582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5044,7 +5054,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5087,7 +5097,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5101,10 +5111,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45713</v>
+        <v>45581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5117,7 +5127,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5160,7 +5170,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5174,10 +5184,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45909</v>
+        <v>45884</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5190,7 +5200,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5233,7 +5243,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5247,10 +5257,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45909</v>
+        <v>45807</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5262,13 +5272,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5311,7 +5316,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5325,10 +5330,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45912</v>
+        <v>45608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5341,7 +5346,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5384,7 +5389,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5398,10 +5403,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45918</v>
+        <v>44565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5414,7 +5419,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5457,7 +5462,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5471,10 +5476,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45918</v>
+        <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5487,7 +5492,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5530,7 +5535,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5544,10 +5549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45918</v>
+        <v>45713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5560,7 +5565,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5603,7 +5608,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5613,14 +5618,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45644</v>
+        <v>45175</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5632,13 +5637,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5681,7 +5681,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44853</v>
+        <v>45587</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5754,7 +5754,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44509</v>
+        <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5827,7 +5827,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45183</v>
+        <v>46044</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5900,7 +5900,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45680</v>
+        <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5973,7 +5973,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5983,14 +5983,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45807</v>
+        <v>45908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45799</v>
+        <v>45909</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6119,7 +6119,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6129,14 +6129,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45055</v>
+        <v>45909</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6148,8 +6148,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6192,7 +6197,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6206,10 +6211,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45509</v>
+        <v>45799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6219,11 +6224,6 @@
       <c r="G71" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -6270,7 +6270,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6284,10 +6284,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46044</v>
+        <v>45912</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45106</v>
+        <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6416,7 +6416,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45106</v>
+        <v>45918</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6489,7 +6489,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45175</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45581</v>
+        <v>45463</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6635,7 +6635,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21204-2026</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6649,10 +6649,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46146</v>
+        <v>44935</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6708,7 +6708,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45356</v>
+        <v>45748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 21204-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46149</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6927,7 +6927,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46149</v>
+        <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7000,7 +7000,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45229</v>
+        <v>45939</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7073,7 +7073,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45937</v>
+        <v>45615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7146,7 +7146,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45937</v>
+        <v>46149</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7219,7 +7219,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46162</v>
+        <v>46149</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7248,13 +7248,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7297,7 +7292,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7311,10 +7306,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46078</v>
+        <v>46148</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7327,7 +7322,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7370,7 +7365,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7384,10 +7379,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46161</v>
+        <v>45950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7400,7 +7395,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7443,7 +7438,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7457,10 +7452,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7473,7 +7468,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7516,7 +7511,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7530,10 +7525,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46170</v>
+        <v>45951</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7546,7 +7541,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7589,7 +7584,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7603,10 +7598,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46175</v>
+        <v>45951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7618,13 +7613,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7667,7 +7657,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7681,10 +7671,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46175</v>
+        <v>44581</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7696,13 +7686,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7745,7 +7730,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7759,10 +7744,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45713</v>
+        <v>45218</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7775,7 +7760,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7818,7 +7803,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7832,10 +7817,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46175</v>
+        <v>45957</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7847,13 +7832,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7896,7 +7876,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7910,10 +7890,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46175</v>
+        <v>45957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7925,13 +7905,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7974,7 +7949,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7988,10 +7963,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46175</v>
+        <v>45146</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8003,13 +7978,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8052,7 +8022,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8066,10 +8036,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46176</v>
+        <v>45957</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8082,7 +8052,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8125,7 +8095,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8139,10 +8109,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45146</v>
+        <v>45957</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8155,7 +8125,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8198,7 +8168,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8212,10 +8182,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45951</v>
+        <v>45965</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8228,7 +8198,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8271,7 +8241,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8285,10 +8255,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46176</v>
+        <v>45964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8301,7 +8271,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>6.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8344,7 +8314,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8358,10 +8328,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45951</v>
+        <v>45965</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8374,7 +8344,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8417,7 +8387,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8431,10 +8401,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45951</v>
+        <v>45609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8447,7 +8417,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8490,7 +8460,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8504,10 +8474,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45950</v>
+        <v>45730</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8520,7 +8490,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8563,7 +8533,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8577,10 +8547,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45582</v>
+        <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8593,7 +8563,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8636,7 +8606,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8650,10 +8620,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45118</v>
+        <v>45975</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8666,7 +8636,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8709,7 +8679,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8723,10 +8693,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45127</v>
+        <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8739,7 +8709,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8782,7 +8752,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8796,10 +8766,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45580</v>
+        <v>45975</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8811,13 +8781,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8860,7 +8825,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8874,10 +8839,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45509</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8890,7 +8855,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8933,7 +8898,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8947,10 +8912,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45957</v>
+        <v>45978</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8963,7 +8928,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9006,7 +8971,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9020,10 +8985,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45957</v>
+        <v>45978</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9036,7 +9001,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9079,7 +9044,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9093,10 +9058,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45957</v>
+        <v>45978</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9109,7 +9074,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9152,7 +9117,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9166,10 +9131,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45609</v>
+        <v>45978</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9182,7 +9147,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9225,7 +9190,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9239,10 +9204,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45609</v>
+        <v>45980</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9252,6 +9217,11 @@
       <c r="G112" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -9298,7 +9268,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9312,10 +9282,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45957</v>
+        <v>45980</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9328,7 +9298,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9371,7 +9341,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9385,10 +9355,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45713</v>
+        <v>45139</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9444,7 +9414,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9458,10 +9428,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45439</v>
+        <v>45980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9473,8 +9443,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9517,7 +9492,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9531,10 +9506,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45964</v>
+        <v>45986</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9547,7 +9522,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9590,7 +9565,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9604,10 +9579,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45965</v>
+        <v>45275</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9620,7 +9595,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9663,7 +9638,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9673,14 +9648,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45965</v>
+        <v>45992</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9693,7 +9668,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9736,7 +9711,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9750,10 +9725,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45974</v>
+        <v>45549</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9766,7 +9741,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9809,7 +9784,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9823,10 +9798,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45737</v>
+        <v>45748</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9839,7 +9814,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9882,7 +9857,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9896,10 +9871,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45098</v>
+        <v>46161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9912,7 +9887,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9955,7 +9930,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9969,10 +9944,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45974</v>
+        <v>46078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10028,7 +10003,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10042,10 +10017,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46198</v>
+        <v>45106</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10058,7 +10033,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10101,7 +10076,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10115,10 +10090,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45975</v>
+        <v>45995</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10131,7 +10106,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10174,7 +10149,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10188,10 +10163,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45975</v>
+        <v>45996</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10204,7 +10179,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10247,7 +10222,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10261,10 +10236,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45978</v>
+        <v>46162</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10276,8 +10251,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10320,7 +10300,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10334,10 +10314,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45978</v>
+        <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10350,7 +10330,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10393,7 +10373,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10403,14 +10383,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45978</v>
+        <v>46000</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10423,7 +10403,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10466,7 +10446,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10480,10 +10460,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45975</v>
+        <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10496,7 +10476,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10539,7 +10519,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10553,10 +10533,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45978</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10569,7 +10549,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10612,7 +10592,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10626,10 +10606,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46245</v>
+        <v>46000</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10642,7 +10622,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10685,7 +10665,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10699,10 +10679,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45440</v>
+        <v>46000</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10714,13 +10694,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10763,7 +10738,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10777,10 +10752,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45980</v>
+        <v>46000</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10793,7 +10768,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10836,7 +10811,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10850,10 +10825,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45980</v>
+        <v>46000</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10865,13 +10840,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10914,7 +10884,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10928,10 +10898,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45980</v>
+        <v>46000</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10943,13 +10913,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10992,7 +10957,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11006,10 +10971,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45231</v>
+        <v>46000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11022,7 +10987,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11065,7 +11030,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11079,10 +11044,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44581</v>
+        <v>45103</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11095,7 +11060,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11138,7 +11103,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11152,10 +11117,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45986</v>
+        <v>45146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11168,7 +11133,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11211,7 +11176,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11225,10 +11190,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45188</v>
+        <v>44953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11241,7 +11206,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11284,7 +11249,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11298,10 +11263,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46253</v>
+        <v>45737</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11314,7 +11279,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11357,7 +11322,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11371,10 +11336,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46210</v>
+        <v>46010</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11387,7 +11352,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11430,7 +11395,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11444,10 +11409,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45099</v>
+        <v>46013</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11459,8 +11424,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>21.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11503,7 +11473,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11513,14 +11483,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46253</v>
+        <v>45439</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11533,7 +11503,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11576,7 +11546,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11590,10 +11560,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45257</v>
+        <v>44501</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11606,7 +11576,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11649,7 +11619,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11659,14 +11629,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46253</v>
+        <v>46030</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11679,7 +11649,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11722,7 +11692,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11732,14 +11702,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45992</v>
+        <v>46170</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11752,7 +11722,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11795,7 +11765,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11809,10 +11779,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44854</v>
+        <v>46034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11825,7 +11795,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11868,7 +11838,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11882,10 +11852,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46255</v>
+        <v>45624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11898,7 +11868,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11941,7 +11911,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11955,10 +11925,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45357</v>
+        <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11971,7 +11941,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12014,7 +11984,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12028,10 +11998,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46260</v>
+        <v>46036</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12044,7 +12014,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12087,7 +12057,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12101,10 +12071,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45771</v>
+        <v>45609</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12116,13 +12086,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12165,7 +12130,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12179,10 +12144,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45995</v>
+        <v>45609</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12195,7 +12160,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12238,7 +12203,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12252,10 +12217,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45996</v>
+        <v>45098</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12268,7 +12233,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12311,7 +12276,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12328,7 +12293,7 @@
         <v>44747</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12341,7 +12306,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12384,7 +12349,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12398,10 +12363,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44747</v>
+        <v>46042</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12457,7 +12422,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12471,10 +12436,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46000</v>
+        <v>46042</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12487,7 +12452,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12530,7 +12495,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12540,14 +12505,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12560,7 +12525,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12603,7 +12568,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12617,10 +12582,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12633,7 +12598,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12676,7 +12641,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12686,14 +12651,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12706,7 +12671,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12749,7 +12714,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12763,10 +12728,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12778,8 +12743,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12822,7 +12792,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12836,10 +12806,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12851,8 +12821,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12895,7 +12870,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12905,14 +12880,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46000</v>
+        <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12925,7 +12900,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12968,7 +12943,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12982,10 +12957,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46000</v>
+        <v>46048</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12998,7 +12973,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13041,7 +13016,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13055,10 +13030,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46000</v>
+        <v>45509</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13070,8 +13045,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13114,7 +13094,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13128,10 +13108,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45103</v>
+        <v>46175</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13143,8 +13123,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13187,7 +13172,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13201,10 +13186,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13216,8 +13201,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13260,7 +13250,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13274,10 +13264,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45146</v>
+        <v>46176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13290,7 +13280,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13333,7 +13323,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13347,10 +13337,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46140</v>
+        <v>46175</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13362,8 +13352,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13406,7 +13401,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13420,10 +13415,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44509</v>
+        <v>46176</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13436,7 +13431,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13479,7 +13474,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13493,10 +13488,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46267</v>
+        <v>45771</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13508,8 +13503,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13552,7 +13552,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13566,10 +13566,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46268</v>
+        <v>46065</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13639,10 +13639,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45259</v>
+        <v>46066</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13698,7 +13698,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45549</v>
+        <v>46070</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13771,7 +13771,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13781,14 +13781,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46269</v>
+        <v>44987</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13798,11 +13798,6 @@
       <c r="G174" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -13849,7 +13844,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13863,10 +13858,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46010</v>
+        <v>46071</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13879,7 +13874,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13922,7 +13917,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13936,10 +13931,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46274</v>
+        <v>45231</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13952,7 +13947,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13995,7 +13990,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14009,10 +14004,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46274</v>
+        <v>45509</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14025,7 +14020,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14068,7 +14063,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14082,10 +14077,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46013</v>
+        <v>45508</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14099,11 +14094,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>21.4</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14146,7 +14141,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14160,10 +14155,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46273</v>
+        <v>44509</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14176,7 +14171,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14219,7 +14214,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14233,10 +14228,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46273</v>
+        <v>45106</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14249,7 +14244,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14292,7 +14287,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14306,10 +14301,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46280</v>
+        <v>45118</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14322,7 +14317,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14365,7 +14360,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14379,10 +14374,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44691</v>
+        <v>45118</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14395,7 +14390,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14438,7 +14433,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14448,14 +14443,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45069</v>
+        <v>44979</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14468,7 +14463,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14511,7 +14506,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14521,14 +14516,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44571</v>
+        <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14541,7 +14536,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14584,7 +14579,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14594,14 +14589,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46030</v>
+        <v>45069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14614,7 +14609,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14657,7 +14652,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14671,10 +14666,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46034</v>
+        <v>46121</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14687,7 +14682,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14730,7 +14725,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14744,10 +14739,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46034</v>
+        <v>46126</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14760,7 +14755,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>9.1</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14803,7 +14798,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14817,10 +14812,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45411</v>
+        <v>46245</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14833,7 +14828,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14876,7 +14871,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14890,10 +14885,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46036</v>
+        <v>44987</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14906,7 +14901,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14949,7 +14944,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 19357-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14963,10 +14958,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44935</v>
+        <v>46133</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14979,7 +14974,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15022,7 +15017,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15036,10 +15031,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46042</v>
+        <v>45580</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15051,8 +15046,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15095,7 +15095,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15109,10 +15109,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46042</v>
+        <v>45440</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15124,8 +15124,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15168,7 +15173,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15182,10 +15187,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45118</v>
+        <v>45390</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15198,7 +15203,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15241,7 +15246,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15251,14 +15256,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46044</v>
+        <v>45713</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15271,7 +15276,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15314,7 +15319,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15324,14 +15329,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46044</v>
+        <v>46253</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15344,7 +15349,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15387,7 +15392,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15397,14 +15402,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46044</v>
+        <v>46253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15417,7 +15422,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.2</v>
+        <v>5.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15460,7 +15465,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15470,14 +15475,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46048</v>
+        <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15490,7 +15495,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15533,7 +15538,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15547,10 +15552,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46048</v>
+        <v>46210</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15563,7 +15568,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15606,7 +15611,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15620,10 +15625,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45508</v>
+        <v>45516</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15635,13 +15640,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15684,7 +15684,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15698,10 +15698,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45730</v>
+        <v>45581</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15757,7 +15757,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15767,14 +15767,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45624</v>
+        <v>45644</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15786,8 +15786,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15830,7 +15835,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15844,10 +15849,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44501</v>
+        <v>45259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15860,7 +15865,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15903,7 +15908,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15917,10 +15922,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45463</v>
+        <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15932,8 +15937,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15976,7 +15986,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15990,10 +16000,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45608</v>
+        <v>46255</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16006,7 +16016,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16049,7 +16059,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16063,10 +16073,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45275</v>
+        <v>45188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16079,7 +16089,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16122,7 +16132,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16136,10 +16146,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45713</v>
+        <v>44747</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16152,7 +16162,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16195,7 +16205,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16209,10 +16219,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45713</v>
+        <v>45775</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16225,7 +16235,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16268,7 +16278,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16278,14 +16288,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45146</v>
+        <v>44816</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16298,7 +16308,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16341,7 +16351,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16355,10 +16365,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44987</v>
+        <v>46260</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16371,7 +16381,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16414,7 +16424,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16428,10 +16438,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45139</v>
+        <v>45713</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16487,7 +16497,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16501,10 +16511,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45615</v>
+        <v>45356</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16517,7 +16527,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16560,7 +16570,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16574,10 +16584,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44987</v>
+        <v>45183</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16590,7 +16600,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16633,7 +16643,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16647,10 +16657,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45757</v>
+        <v>45713</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16663,7 +16673,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16706,7 +16716,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16720,10 +16730,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45775</v>
+        <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16736,7 +16746,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16779,7 +16789,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16793,10 +16803,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45532</v>
+        <v>46140</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16809,7 +16819,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16852,7 +16862,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16866,10 +16876,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45532</v>
+        <v>44509</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16882,7 +16892,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16925,7 +16935,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16935,14 +16945,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45532</v>
+        <v>46269</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16954,8 +16964,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16998,7 +17013,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17012,10 +17027,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45474</v>
+        <v>46268</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17027,13 +17042,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17076,7 +17086,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17090,10 +17100,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44979</v>
+        <v>45118</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17106,7 +17116,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17149,7 +17159,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17163,10 +17173,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44953</v>
+        <v>45782</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17179,7 +17189,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17222,7 +17232,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17236,10 +17246,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44747</v>
+        <v>46273</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17252,7 +17262,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17295,7 +17305,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17309,10 +17319,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45587</v>
+        <v>45782</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17325,7 +17335,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17368,7 +17378,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17382,10 +17392,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45748</v>
+        <v>46273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17398,7 +17408,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17441,7 +17451,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17455,10 +17465,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45672</v>
+        <v>46274</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17470,13 +17480,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17519,7 +17524,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17533,10 +17538,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45672</v>
+        <v>46274</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17548,13 +17553,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17597,7 +17597,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45609</v>
+        <v>45187</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17670,7 +17670,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17684,10 +17684,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45118</v>
+        <v>45791</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17699,8 +17699,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17743,7 +17748,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17757,10 +17762,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45782</v>
+        <v>45791</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17772,8 +17777,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17816,7 +17826,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17830,10 +17840,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45782</v>
+        <v>45790</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17845,8 +17855,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17889,7 +17904,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17903,10 +17918,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45790</v>
+        <v>46280</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17918,13 +17933,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17967,7 +17977,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 23567-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17981,10 +17991,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17996,13 +18006,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18045,7 +18050,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18059,10 +18064,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45791</v>
+        <v>45793</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18074,13 +18079,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18123,7 +18123,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 23567-2025</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18140,7 +18140,7 @@
         <v>45792</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18152,8 +18152,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18196,7 +18201,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18210,10 +18215,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45187</v>
+        <v>45792</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18226,7 +18231,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18269,7 +18274,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18283,10 +18288,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45792</v>
+        <v>45797</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18298,13 +18303,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18347,7 +18347,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18361,10 +18361,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45792</v>
+        <v>45797</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18420,7 +18420,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18434,10 +18434,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45793</v>
+        <v>45799</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>8.1</v>
+        <v>3.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18493,7 +18493,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18507,10 +18507,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45797</v>
+        <v>45799</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18566,7 +18566,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18580,10 +18580,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45797</v>
+        <v>45799</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18653,10 +18653,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45800</v>
+        <v>45799</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18712,7 +18712,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18729,7 +18729,7 @@
         <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18802,7 +18802,7 @@
         <v>45800</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18872,10 +18872,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18931,7 +18931,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18941,14 +18941,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45799</v>
+        <v>45827</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19004,7 +19004,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19018,10 +19018,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45799</v>
+        <v>45835</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19077,7 +19077,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19091,10 +19091,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45799</v>
+        <v>45462</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19150,7 +19150,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19164,10 +19164,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44559</v>
+        <v>45250</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>60.7</v>
+        <v>31.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19228,7 +19228,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19242,10 +19242,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44645</v>
+        <v>44559</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19257,8 +19257,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>15.8</v>
+        <v>60.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19301,7 +19306,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19315,10 +19320,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45250</v>
+        <v>44645</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19330,13 +19335,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>31.7</v>
+        <v>15.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19396,7 +19396,7 @@
         <v>45775</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46070</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>46073</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46114</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>45799</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45698</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>46108</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45642</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>46007</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44651</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44524</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>44854</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>44565</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>44610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>45229</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45532</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45411</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45757</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>45055</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>44853</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45504</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44691</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45516</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>45146</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45103</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45246</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45680</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44854</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45177</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>45356</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45257</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45517</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45672</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45672</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>45730</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>45669</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>45357</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>45582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>45581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45884</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45807</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>45608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45175</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45587</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>46044</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>45908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>45909</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>45909</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>45799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45912</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45918</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45463</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44935</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>45939</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>45615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>46149</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>46149</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>46148</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>45950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>45951</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45951</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>45951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44581</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45218</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>45957</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45146</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45957</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>45957</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45965</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>45965</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45730</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45975</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45975</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>45978</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45978</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45978</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45978</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>45980</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45980</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>45139</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>45980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45986</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45275</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45992</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45549</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45748</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>46161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>46078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45106</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45995</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45996</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>46162</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>46000</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>46000</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>46000</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46000</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>46000</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>46000</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>46000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45103</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>44953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45737</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>46010</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>46013</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45439</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>44501</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>46030</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>46170</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>46034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>46036</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45609</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45609</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45098</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44747</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>46042</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>46042</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>46044</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>46044</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>46175</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>46175</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>46048</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45509</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>46175</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>46175</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>46176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>46175</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>46176</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45771</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>46065</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>46066</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>46070</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44987</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>46071</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45231</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45509</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45508</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>44509</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45106</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45118</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45118</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>44979</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>46121</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46126</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>46245</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44987</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>46133</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45580</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45440</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45390</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45713</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>46253</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>46253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46210</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45516</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45581</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45644</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>46255</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44747</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45775</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44816</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>46260</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45713</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>45356</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>45183</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45713</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>46140</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>44509</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46269</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46268</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45118</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45782</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>46273</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45782</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>46273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>46274</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>46274</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45187</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45791</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45791</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45790</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>46280</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45792</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45793</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45792</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45792</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45797</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>45797</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45799</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45799</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45799</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45799</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45800</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45800</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45827</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45835</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45462</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45250</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44559</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44645</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45775</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46070</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>46073</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46114</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE254"/>
+  <dimension ref="A1:AE248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,24 +948,24 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50033-2025</t>
+          <t>S 1760-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45943</v>
+        <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -978,162 +978,45 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16</v>
-      </c>
-      <c r="U5" t="n">
-        <v>16</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Rosenticka
-Tretåig hackspett
-Ullticka
-Jättesvampmal
-Vedticka
-Spillkråka
-Kungsfågel
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 50033-2025 artfynd.xlsx", "A 50033-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 50033-2025 karta.png", "A 50033-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 50033-2025 georefererad karta.tif", "A 50033-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 50033-2025 FSC-klagomål.docx", "A 50033-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 50033-2025 FSC-klagomål mail.docx", "A 50033-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 50033-2025 tillsynsbegäran.docx", "A 50033-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 50033-2025 tillsynsbegäran mail.docx", "A 50033-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/fåglar/A 50033-2025 prioriterade fågelarter.docx", "A 50033-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S 1760-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45435</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Brunklöver
 Nötkråka
@@ -1145,111 +1028,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/S 1760-2024 artfynd.xlsx", "S 1760-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/S 1760-2024 karta.png", "S 1760-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/S 1760-2024 georefererad karta.tif", "S 1760-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/S 1760-2024 FSC-klagomål.docx", "S 1760-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/S 1760-2024 FSC-klagomål mail.docx", "S 1760-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/S 1760-2024 tillsynsbegäran.docx", "S 1760-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/S 1760-2024 tillsynsbegäran mail.docx", "S 1760-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/fåglar/S 1760-2024 prioriterade fågelarter.docx", "S 1760-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 24846-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45799</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>2.8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S6" t="n">
         <v>6</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Talltita
@@ -1259,43 +1142,149 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 24846-2025 artfynd.xlsx", "A 24846-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 24846-2025 karta.png", "A 24846-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 24846-2025 georefererad karta.tif", "A 24846-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 24846-2025 FSC-klagomål.docx", "A 24846-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 24846-2025 FSC-klagomål mail.docx", "A 24846-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 24846-2025 tillsynsbegäran.docx", "A 24846-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 24846-2025 tillsynsbegäran mail.docx", "A 24846-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/fåglar/A 24846-2025 prioriterade fågelarter.docx", "A 24846-2025")</f>
         <v/>
       </c>
     </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 6179-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45698</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 6179-2025 artfynd.xlsx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 6179-2025 karta.png", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 6179-2025 georefererad karta.tif", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 6179-2025 FSC-klagomål.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 6179-2025 FSC-klagomål mail.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 6179-2025 tillsynsbegäran.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 6179-2025 tillsynsbegäran mail.docx", "A 6179-2025")</f>
+        <v/>
+      </c>
+    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 62416-2025</t>
+          <t>A 62418-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1312,7 +1301,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1325,88 +1314,82 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Vågbandad barkbock
-Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62416-2025 artfynd.xlsx", "A 62416-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62416-2025 karta.png", "A 62416-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62416-2025 georefererad karta.tif", "A 62416-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62416-2025 FSC-klagomål.docx", "A 62416-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62416-2025 FSC-klagomål mail.docx", "A 62416-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62416-2025 tillsynsbegäran.docx", "A 62416-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62416-2025 tillsynsbegäran mail.docx", "A 62416-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/fåglar/A 62416-2025 prioriterade fågelarter.docx", "A 62416-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6179-2025</t>
+          <t>A 60033-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1420,10 +1403,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45698</v>
+        <v>45642</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,13 +1419,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1466,53 +1449,52 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar
-Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 6179-2025 artfynd.xlsx", "A 6179-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 6179-2025 karta.png", "A 6179-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 6179-2025 georefererad karta.tif", "A 6179-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 6179-2025 FSC-klagomål.docx", "A 6179-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 6179-2025 FSC-klagomål mail.docx", "A 6179-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 6179-2025 tillsynsbegäran.docx", "A 6179-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 6179-2025 tillsynsbegäran mail.docx", "A 6179-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 16140-2026</t>
+          <t>A 55173-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1526,10 +1508,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46108</v>
+        <v>45237</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1542,100 +1524,99 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Bollvitmossa
-Utter</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 16140-2026 artfynd.xlsx", "A 16140-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 16140-2026 karta.png", "A 16140-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 16140-2026 georefererad karta.tif", "A 16140-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 16140-2026 FSC-klagomål.docx", "A 16140-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 16140-2026 FSC-klagomål mail.docx", "A 16140-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 16140-2026 tillsynsbegäran.docx", "A 16140-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 16140-2026 tillsynsbegäran mail.docx", "A 16140-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60033-2024</t>
+          <t>S 460-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45642</v>
+        <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1647,14 +1628,19 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>5.3</v>
+        <v>93</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1688,59 +1674,59 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/S 460-2025 artfynd.xlsx", "S 460-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/S 460-2025 karta.png", "S 460-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/S 460-2025 georefererad karta.tif", "S 460-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/S 460-2025 FSC-klagomål.docx", "S 460-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/S 460-2025 FSC-klagomål mail.docx", "S 460-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/S 460-2025 tillsynsbegäran.docx", "S 460-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/S 460-2025 tillsynsbegäran mail.docx", "S 460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 62418-2025</t>
+          <t>S 1810-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46007</v>
+        <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1753,7 +1739,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1762,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1777,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1793,42 +1779,46 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/S 1810-2026 artfynd.xlsx", "S 1810-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/S 1810-2026 karta.png", "S 1810-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/S 1810-2026 georefererad karta.tif", "S 1810-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/S 1810-2026 FSC-klagomål.docx", "S 1810-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/S 1810-2026 FSC-klagomål mail.docx", "S 1810-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/S 1810-2026 tillsynsbegäran.docx", "S 1810-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/S 1810-2026 tillsynsbegäran mail.docx", "S 1810-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/fåglar/S 1810-2026 prioriterade fågelarter.docx", "S 1810-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55173-2023</t>
+          <t>A 14222-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1842,10 +1832,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45237</v>
+        <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,7 +1848,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1867,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1882,75 +1872,43 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
+      <c r="V13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S 460-2025</t>
+          <t>A 427-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45701</v>
+        <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,16 +1920,11 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>93</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1998,69 +1951,37 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/S 460-2025 artfynd.xlsx", "S 460-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/S 460-2025 karta.png", "S 460-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/S 460-2025 georefererad karta.tif", "S 460-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/S 460-2025 FSC-klagomål.docx", "S 460-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/S 460-2025 FSC-klagomål mail.docx", "S 460-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/S 460-2025 tillsynsbegäran.docx", "S 460-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/S 460-2025 tillsynsbegäran mail.docx", "S 460-2025")</f>
-        <v/>
-      </c>
+      <c r="V14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S 1810-2026</t>
+          <t>A 67534-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46189</v>
+        <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,16 +1994,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2097,62 +2018,26 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/S 1810-2026 artfynd.xlsx", "S 1810-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/S 1810-2026 karta.png", "S 1810-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/S 1810-2026 georefererad karta.tif", "S 1810-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/S 1810-2026 FSC-klagomål.docx", "S 1810-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/S 1810-2026 FSC-klagomål mail.docx", "S 1810-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/S 1810-2026 tillsynsbegäran.docx", "S 1810-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/S 1810-2026 tillsynsbegäran mail.docx", "S 1810-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/fåglar/S 1810-2026 prioriterade fågelarter.docx", "S 1810-2026")</f>
-        <v/>
-      </c>
+      <c r="V15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14222-2022</t>
+          <t>A 47772-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2051,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44651</v>
+        <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2067,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2225,7 +2110,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 427-2022</t>
+          <t>A 429-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2242,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2255,7 +2140,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2298,7 +2183,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 67534-2021</t>
+          <t>A 8399-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2312,10 +2197,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44524</v>
+        <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2328,7 +2213,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2371,7 +2256,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 47772-2022</t>
+          <t>A 67514-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2385,10 +2270,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44854</v>
+        <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2401,7 +2286,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2444,7 +2329,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 429-2022</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2458,10 +2343,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44565</v>
+        <v>45229</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2474,7 +2359,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2517,7 +2402,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8399-2022</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2531,10 +2416,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44610</v>
+        <v>45411</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2547,7 +2432,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2590,7 +2475,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 67514-2021</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2604,10 +2489,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44524</v>
+        <v>45532</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2620,7 +2505,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2663,7 +2548,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2677,10 +2562,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45229</v>
+        <v>45532</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2693,7 +2578,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2736,7 +2621,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2746,14 +2631,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45532</v>
+        <v>44571</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2766,7 +2651,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2809,7 +2694,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2823,10 +2708,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45532</v>
+        <v>45127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2839,7 +2724,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2882,7 +2767,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2896,10 +2781,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45411</v>
+        <v>44747</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2955,7 +2840,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2969,10 +2854,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44571</v>
+        <v>45055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3028,7 +2913,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3042,10 +2927,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45127</v>
+        <v>45757</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3058,7 +2943,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3101,7 +2986,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3115,10 +3000,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44747</v>
+        <v>44853</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3131,7 +3016,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3174,7 +3059,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3188,10 +3073,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45757</v>
+        <v>44691</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3204,7 +3089,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3247,7 +3132,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3257,14 +3142,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45055</v>
+        <v>45503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3276,8 +3161,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3320,7 +3210,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3334,10 +3224,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44853</v>
+        <v>45504</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3349,8 +3239,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3393,7 +3288,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3407,10 +3302,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45503</v>
+        <v>45516</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3422,13 +3317,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3471,7 +3361,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3481,14 +3371,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45504</v>
+        <v>45146</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,13 +3390,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3549,7 +3434,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3563,10 +3448,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44691</v>
+        <v>45103</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3579,7 +3464,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3622,7 +3507,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3636,10 +3521,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45516</v>
+        <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3652,7 +3537,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3695,7 +3580,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3705,14 +3590,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45146</v>
+        <v>45680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3725,7 +3610,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3768,7 +3653,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3782,10 +3667,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45103</v>
+        <v>45099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3798,7 +3683,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3841,7 +3726,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3855,10 +3740,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45246</v>
+        <v>44854</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3871,7 +3756,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3914,7 +3799,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3928,10 +3813,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45680</v>
+        <v>45356</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3944,7 +3829,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3987,7 +3872,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3997,14 +3882,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45099</v>
+        <v>45177</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4017,7 +3902,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4060,7 +3945,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4074,10 +3959,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44854</v>
+        <v>45257</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4090,7 +3975,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4133,7 +4018,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4143,14 +4028,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45177</v>
+        <v>44846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4163,7 +4048,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4206,7 +4091,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4220,10 +4105,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45356</v>
+        <v>45462</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4236,7 +4121,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4279,7 +4164,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4293,10 +4178,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45257</v>
+        <v>45884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4309,7 +4194,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4352,7 +4237,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4366,10 +4251,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44846</v>
+        <v>45532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4382,7 +4267,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4425,7 +4310,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4439,10 +4324,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45532</v>
+        <v>45517</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4454,8 +4339,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4498,7 +4388,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4512,10 +4402,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45517</v>
+        <v>45672</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4529,11 +4419,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4576,7 +4466,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4593,7 +4483,7 @@
         <v>45672</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4611,7 +4501,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4654,7 +4544,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4668,10 +4558,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45672</v>
+        <v>45730</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4683,13 +4573,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4732,7 +4617,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4746,10 +4631,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45730</v>
+        <v>44565</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4762,7 +4647,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4805,7 +4690,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4819,10 +4704,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44929</v>
+        <v>45581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4835,7 +4720,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4878,7 +4763,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4892,10 +4777,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45669</v>
+        <v>44929</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4908,7 +4793,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4951,7 +4836,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4965,10 +4850,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45357</v>
+        <v>45807</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4981,7 +4866,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5024,7 +4909,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5038,10 +4923,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45582</v>
+        <v>45905</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5054,7 +4939,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5097,7 +4982,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5107,14 +4992,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45581</v>
+        <v>45908</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5127,7 +5012,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5170,7 +5055,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5184,10 +5069,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45884</v>
+        <v>45909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5200,7 +5085,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5243,7 +5128,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5257,10 +5142,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45807</v>
+        <v>45909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5272,8 +5157,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5316,7 +5206,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5330,10 +5220,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45608</v>
+        <v>45669</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5346,7 +5236,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5389,7 +5279,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5403,10 +5293,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44565</v>
+        <v>45175</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5419,7 +5309,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5462,7 +5352,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5476,10 +5366,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45713</v>
+        <v>45357</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5492,7 +5382,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5535,7 +5425,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5549,10 +5439,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45713</v>
+        <v>45582</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5608,7 +5498,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5622,10 +5512,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45175</v>
+        <v>45912</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5638,7 +5528,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5681,7 +5571,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5695,10 +5585,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45587</v>
+        <v>46044</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5711,7 +5601,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5754,7 +5644,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5768,10 +5658,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44970</v>
+        <v>45918</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5784,7 +5674,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5827,7 +5717,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5841,10 +5731,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46044</v>
+        <v>45918</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5857,7 +5747,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5900,7 +5790,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5914,10 +5804,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45905</v>
+        <v>45918</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5930,7 +5820,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5973,7 +5863,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5983,14 +5873,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45908</v>
+        <v>45608</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6003,7 +5893,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6046,7 +5936,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6060,10 +5950,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45909</v>
+        <v>45713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6076,7 +5966,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6119,7 +6009,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6133,10 +6023,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45909</v>
+        <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6148,13 +6038,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6197,7 +6082,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6211,10 +6096,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45799</v>
+        <v>45713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6227,7 +6112,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6270,7 +6155,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6284,10 +6169,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45912</v>
+        <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6300,7 +6185,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6343,7 +6228,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6357,10 +6242,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45918</v>
+        <v>45587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6373,7 +6258,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6416,7 +6301,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6430,10 +6315,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45918</v>
+        <v>44970</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6446,7 +6331,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6489,7 +6374,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6503,10 +6388,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6519,7 +6404,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6562,7 +6447,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6576,10 +6461,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45463</v>
+        <v>45939</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6592,7 +6477,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6635,7 +6520,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6649,10 +6534,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44935</v>
+        <v>46149</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6665,7 +6550,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6708,7 +6593,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6722,10 +6607,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45748</v>
+        <v>46149</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6738,7 +6623,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6781,7 +6666,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21204-2026</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6795,10 +6680,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6811,7 +6696,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6854,7 +6739,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6868,10 +6753,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45937</v>
+        <v>45950</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6884,7 +6769,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6927,7 +6812,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6941,10 +6826,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45937</v>
+        <v>45951</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6957,7 +6842,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7000,7 +6885,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7014,10 +6899,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7030,7 +6915,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7073,7 +6958,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7087,10 +6972,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45615</v>
+        <v>45951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7103,7 +6988,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7146,7 +7031,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7160,10 +7045,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46149</v>
+        <v>45957</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7176,7 +7061,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7219,7 +7104,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7233,10 +7118,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46149</v>
+        <v>45957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7249,7 +7134,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7292,7 +7177,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7306,10 +7191,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46148</v>
+        <v>45463</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7322,7 +7207,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7365,7 +7250,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7379,10 +7264,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45950</v>
+        <v>45957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7395,7 +7280,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7438,7 +7323,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7452,10 +7337,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45951</v>
+        <v>44935</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7468,7 +7353,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7511,7 +7396,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7525,10 +7410,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7541,7 +7426,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7584,7 +7469,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7598,10 +7483,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45951</v>
+        <v>46161</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7614,7 +7499,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7657,7 +7542,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7671,10 +7556,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44581</v>
+        <v>45965</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7687,7 +7572,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7730,7 +7615,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7744,10 +7629,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45218</v>
+        <v>45964</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7760,7 +7645,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.8</v>
+        <v>6.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7803,7 +7688,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7817,10 +7702,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45957</v>
+        <v>46078</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7833,7 +7718,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7876,7 +7761,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7890,10 +7775,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7906,7 +7791,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7949,7 +7834,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7963,10 +7848,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45146</v>
+        <v>45748</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7979,7 +7864,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>7.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8022,7 +7907,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8036,10 +7921,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45957</v>
+        <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8051,8 +7936,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8095,7 +7985,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8109,10 +7999,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45957</v>
+        <v>45974</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8125,7 +8015,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8168,7 +8058,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8182,10 +8072,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8198,7 +8088,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8241,7 +8131,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8255,10 +8145,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45964</v>
+        <v>45975</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8271,7 +8161,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8314,7 +8204,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8328,10 +8218,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8344,7 +8234,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8387,7 +8277,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8401,10 +8291,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45609</v>
+        <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8417,7 +8307,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8460,7 +8350,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8474,10 +8364,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45730</v>
+        <v>45978</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8490,7 +8380,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8533,7 +8423,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8547,10 +8437,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45974</v>
+        <v>45615</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8563,7 +8453,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8606,7 +8496,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8620,10 +8510,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8636,7 +8526,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8679,7 +8569,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8693,10 +8583,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8709,7 +8599,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8752,7 +8642,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8766,10 +8656,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8825,7 +8715,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8839,10 +8729,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8854,8 +8744,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8898,7 +8793,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8912,10 +8807,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8928,7 +8823,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8971,7 +8866,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8985,10 +8880,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9000,8 +8895,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9044,7 +8944,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9058,10 +8958,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9074,7 +8974,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9117,7 +9017,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9131,10 +9031,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45978</v>
+        <v>46170</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9147,7 +9047,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9190,7 +9090,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9204,10 +9104,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45980</v>
+        <v>44581</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9219,13 +9119,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9268,7 +9163,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9282,10 +9177,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45980</v>
+        <v>45218</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9298,7 +9193,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9341,7 +9236,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9351,14 +9246,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45139</v>
+        <v>45992</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9371,7 +9266,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9414,7 +9309,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9428,10 +9323,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45980</v>
+        <v>45146</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9443,13 +9338,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9492,7 +9382,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9506,10 +9396,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9522,7 +9412,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9565,7 +9455,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9579,10 +9469,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45275</v>
+        <v>45996</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9595,7 +9485,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9638,7 +9528,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9648,14 +9538,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9668,7 +9558,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9711,7 +9601,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9721,14 +9611,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45549</v>
+        <v>46000</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9741,7 +9631,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9784,7 +9674,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9798,10 +9688,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45748</v>
+        <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9814,7 +9704,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9857,7 +9747,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9871,10 +9761,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46161</v>
+        <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9887,7 +9777,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9930,7 +9820,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9944,10 +9834,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46078</v>
+        <v>46000</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9960,7 +9850,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10003,7 +9893,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10017,10 +9907,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45106</v>
+        <v>46000</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10033,7 +9923,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10076,7 +9966,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10090,10 +9980,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10106,7 +9996,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10149,7 +10039,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10163,10 +10053,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10179,7 +10069,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10222,7 +10112,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10236,10 +10126,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46162</v>
+        <v>46000</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10251,13 +10141,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10300,7 +10185,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10317,7 +10202,7 @@
         <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10330,7 +10215,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>8.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10373,7 +10258,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10383,14 +10268,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10402,8 +10287,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10446,7 +10336,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10460,10 +10350,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46000</v>
+        <v>45103</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10519,7 +10409,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10533,10 +10423,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10548,8 +10438,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10592,7 +10487,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10606,10 +10501,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46000</v>
+        <v>45146</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10622,7 +10517,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10665,7 +10560,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10679,10 +10574,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10694,8 +10589,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10738,7 +10638,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10752,10 +10652,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10767,8 +10667,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10811,7 +10716,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10825,10 +10730,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46000</v>
+        <v>46176</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10841,7 +10746,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10884,7 +10789,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10898,10 +10803,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46000</v>
+        <v>46175</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10913,8 +10818,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10957,7 +10867,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10971,10 +10881,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46000</v>
+        <v>46176</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10987,7 +10897,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11030,7 +10940,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11044,10 +10954,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45103</v>
+        <v>45609</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11060,7 +10970,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11103,7 +11013,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11117,10 +11027,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45146</v>
+        <v>45730</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11133,7 +11043,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11176,7 +11086,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11190,10 +11100,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44953</v>
+        <v>46010</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11206,7 +11116,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11249,7 +11159,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11263,10 +11173,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45737</v>
+        <v>46013</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11278,8 +11188,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>2.6</v>
+        <v>21.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11322,7 +11237,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11336,10 +11251,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46010</v>
+        <v>45139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11352,7 +11267,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11395,7 +11310,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11409,10 +11324,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46013</v>
+        <v>46030</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11424,13 +11339,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>21.4</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11473,7 +11383,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11487,10 +11397,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45439</v>
+        <v>46034</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11503,7 +11413,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11546,7 +11456,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11560,10 +11470,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44501</v>
+        <v>46034</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11576,7 +11486,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11619,7 +11529,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11633,10 +11543,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11649,7 +11559,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11692,7 +11602,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11706,10 +11616,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46170</v>
+        <v>45275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11722,7 +11632,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>6.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11765,7 +11675,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11779,10 +11689,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46034</v>
+        <v>45549</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11795,7 +11705,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11838,7 +11748,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11852,10 +11762,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45624</v>
+        <v>46042</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11868,7 +11778,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11911,7 +11821,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11925,10 +11835,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46034</v>
+        <v>45748</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11941,7 +11851,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>9.1</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11984,7 +11894,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11998,10 +11908,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46036</v>
+        <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12014,7 +11924,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12057,7 +11967,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12067,14 +11977,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45609</v>
+        <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12087,7 +11997,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12130,7 +12040,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12144,10 +12054,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45609</v>
+        <v>46044</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12160,7 +12070,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12203,7 +12113,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12213,14 +12123,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45098</v>
+        <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12233,7 +12143,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.3</v>
+        <v>0.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12276,7 +12186,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12290,10 +12200,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44747</v>
+        <v>46048</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12349,7 +12259,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12363,10 +12273,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12379,7 +12289,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12422,7 +12332,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12436,10 +12346,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46042</v>
+        <v>45106</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12452,7 +12362,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12495,7 +12405,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12505,14 +12415,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46044</v>
+        <v>46065</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12525,7 +12435,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12568,7 +12478,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12582,10 +12492,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46044</v>
+        <v>44953</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12598,7 +12508,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12641,7 +12551,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12651,14 +12561,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46044</v>
+        <v>45737</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12671,7 +12581,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12714,7 +12624,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12728,10 +12638,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46175</v>
+        <v>46066</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12743,13 +12653,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12792,7 +12697,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12806,10 +12711,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46175</v>
+        <v>46070</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12821,13 +12726,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12870,7 +12770,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12884,10 +12784,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46048</v>
+        <v>46071</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12943,7 +12843,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12957,10 +12857,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46048</v>
+        <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12973,7 +12873,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13016,7 +12916,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13030,10 +12930,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45509</v>
+        <v>45439</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13045,13 +12945,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13094,7 +12989,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13108,10 +13003,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46175</v>
+        <v>44501</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13123,13 +13018,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>10.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13172,7 +13062,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13186,10 +13076,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46175</v>
+        <v>45624</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13201,13 +13091,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13250,7 +13135,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13264,10 +13149,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46176</v>
+        <v>45609</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13280,7 +13165,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13323,7 +13208,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13337,10 +13222,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46175</v>
+        <v>45609</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13352,13 +13237,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13401,7 +13281,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13415,10 +13295,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46176</v>
+        <v>45098</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13431,7 +13311,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13474,7 +13354,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13488,10 +13368,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45771</v>
+        <v>44747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13501,11 +13381,6 @@
       <c r="G170" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -13552,7 +13427,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13566,10 +13441,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46065</v>
+        <v>45509</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13581,8 +13456,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13625,7 +13505,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13639,10 +13519,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46066</v>
+        <v>45771</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13652,6 +13532,11 @@
       <c r="G172" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I172" t="n">
@@ -13698,7 +13583,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13712,10 +13597,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46070</v>
+        <v>46121</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13728,7 +13613,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13771,7 +13656,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13785,10 +13670,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44987</v>
+        <v>46126</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13801,7 +13686,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13844,7 +13729,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13858,10 +13743,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46071</v>
+        <v>44987</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13874,7 +13759,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13917,7 +13802,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13927,14 +13812,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45231</v>
+        <v>46253</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13947,7 +13832,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13990,7 +13875,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14004,10 +13889,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45509</v>
+        <v>45231</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14020,7 +13905,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14063,7 +13948,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14077,10 +13962,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45508</v>
+        <v>46253</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14092,13 +13977,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14141,7 +14021,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14155,10 +14035,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44509</v>
+        <v>45509</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14171,7 +14051,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14214,7 +14094,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14224,14 +14104,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45106</v>
+        <v>46253</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14244,7 +14124,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14287,7 +14167,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14301,10 +14181,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45118</v>
+        <v>46210</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14317,7 +14197,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14360,7 +14240,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14374,10 +14254,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45118</v>
+        <v>45508</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14389,8 +14269,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14433,7 +14318,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14447,10 +14332,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44979</v>
+        <v>44509</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14463,7 +14348,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14506,7 +14391,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14520,10 +14405,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46198</v>
+        <v>46255</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14536,7 +14421,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14579,7 +14464,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14589,14 +14474,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45069</v>
+        <v>46260</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14609,7 +14494,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14652,7 +14537,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14666,10 +14551,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46121</v>
+        <v>45106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14682,7 +14567,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14725,7 +14610,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14739,10 +14624,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46126</v>
+        <v>45118</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14755,7 +14640,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14798,7 +14683,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14812,10 +14697,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46245</v>
+        <v>45118</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14828,7 +14713,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14871,7 +14756,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14885,10 +14770,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44987</v>
+        <v>44979</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14901,7 +14786,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14944,7 +14829,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 19357-2026</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14954,14 +14839,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46133</v>
+        <v>45069</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14974,7 +14859,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15017,7 +14902,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15031,10 +14916,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45580</v>
+        <v>46267</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15046,13 +14931,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15095,7 +14975,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15109,10 +14989,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45440</v>
+        <v>46140</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15124,13 +15004,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15173,7 +15048,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15187,10 +15062,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45390</v>
+        <v>44987</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15203,7 +15078,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15246,7 +15121,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15260,10 +15135,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45713</v>
+        <v>44509</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15276,7 +15151,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15319,7 +15194,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15329,14 +15204,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15349,7 +15224,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15392,7 +15267,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15406,10 +15281,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46253</v>
+        <v>45580</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15421,8 +15296,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15465,7 +15345,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15475,14 +15355,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46253</v>
+        <v>45440</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15494,8 +15374,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15538,7 +15423,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15552,10 +15437,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15568,7 +15453,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15611,7 +15496,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15625,10 +15510,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45516</v>
+        <v>45390</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15641,7 +15526,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15684,7 +15569,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15698,10 +15583,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45581</v>
+        <v>46273</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15714,7 +15599,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15757,7 +15642,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15767,14 +15652,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45644</v>
+        <v>46274</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15786,13 +15671,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15835,7 +15715,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15849,10 +15729,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45259</v>
+        <v>45713</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15865,7 +15745,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15908,7 +15788,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15922,10 +15802,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45474</v>
+        <v>46274</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15937,13 +15817,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15986,7 +15861,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16000,10 +15875,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46255</v>
+        <v>45516</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16016,7 +15891,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16059,7 +15934,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16073,10 +15948,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45188</v>
+        <v>46280</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16089,7 +15964,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16132,7 +16007,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16146,10 +16021,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44747</v>
+        <v>45581</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16162,7 +16037,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16205,7 +16080,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16215,14 +16090,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45775</v>
+        <v>45644</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16234,8 +16109,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16278,7 +16158,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16292,10 +16172,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44816</v>
+        <v>45259</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16308,7 +16188,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16351,7 +16231,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16365,10 +16245,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46260</v>
+        <v>45474</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16380,8 +16260,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16424,7 +16309,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16438,10 +16323,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45713</v>
+        <v>45188</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16497,7 +16382,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16511,10 +16396,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45356</v>
+        <v>44747</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16527,7 +16412,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16570,7 +16455,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16584,10 +16469,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45183</v>
+        <v>45775</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16600,7 +16485,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16643,7 +16528,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16657,10 +16542,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45713</v>
+        <v>44816</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16673,7 +16558,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16716,7 +16601,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16730,10 +16615,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46267</v>
+        <v>45713</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16746,7 +16631,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16789,7 +16674,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16803,10 +16688,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46140</v>
+        <v>46245</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16819,7 +16704,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16862,7 +16747,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16872,14 +16757,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44509</v>
+        <v>46269</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16891,8 +16776,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16935,7 +16825,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16945,14 +16835,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46269</v>
+        <v>45356</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16964,13 +16854,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17013,7 +16898,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17027,10 +16912,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46268</v>
+        <v>45183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17043,7 +16928,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17086,7 +16971,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17100,10 +16985,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45118</v>
+        <v>45713</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17116,7 +17001,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17159,7 +17044,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17173,10 +17058,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45782</v>
+        <v>45118</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17232,7 +17117,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17246,10 +17131,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46273</v>
+        <v>45782</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17262,7 +17147,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17322,7 +17207,7 @@
         <v>45782</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17378,7 +17263,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17392,10 +17277,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46273</v>
+        <v>45187</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17408,7 +17293,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17451,7 +17336,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17465,10 +17350,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46274</v>
+        <v>45791</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17480,8 +17365,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17524,7 +17414,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17538,10 +17428,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46274</v>
+        <v>45791</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17553,8 +17443,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17597,7 +17492,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17611,10 +17506,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45187</v>
+        <v>45790</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17626,8 +17521,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17670,7 +17570,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17684,10 +17584,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45791</v>
+        <v>45793</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17699,13 +17599,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17748,7 +17643,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17762,10 +17657,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17783,7 +17678,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17826,7 +17721,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17840,10 +17735,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45790</v>
+        <v>45792</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17855,13 +17750,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17904,7 +17794,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17918,10 +17808,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46280</v>
+        <v>45797</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17934,7 +17824,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17977,7 +17867,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 23567-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17991,10 +17881,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45792</v>
+        <v>45797</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18007,7 +17897,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18050,7 +17940,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18064,10 +17954,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45793</v>
+        <v>45799</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18080,7 +17970,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8.1</v>
+        <v>3.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18123,7 +18013,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18137,10 +18027,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45792</v>
+        <v>45799</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18152,13 +18042,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18201,7 +18086,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18215,10 +18100,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45792</v>
+        <v>45799</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18231,7 +18116,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18274,7 +18159,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18288,10 +18173,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45797</v>
+        <v>45799</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18304,7 +18189,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18347,7 +18232,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18361,10 +18246,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45797</v>
+        <v>45799</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18377,7 +18262,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18420,7 +18305,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18434,10 +18319,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18450,7 +18335,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18493,7 +18378,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18507,10 +18392,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18523,7 +18408,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18566,7 +18451,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18576,14 +18461,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45799</v>
+        <v>45827</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18596,7 +18481,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18639,7 +18524,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18653,10 +18538,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45799</v>
+        <v>45835</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18669,7 +18554,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18712,24 +18597,24 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45799</v>
+        <v>45250</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18741,8 +18626,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18785,24 +18675,24 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45800</v>
+        <v>44559</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18814,8 +18704,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>1.4</v>
+        <v>60.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18858,24 +18753,24 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45800</v>
+        <v>44645</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18888,7 +18783,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.2</v>
+        <v>15.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18931,24 +18826,24 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>S 1362-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45827</v>
+        <v>45775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18961,7 +18856,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.3</v>
+        <v>63.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19004,24 +18899,24 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>S 2703-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45835</v>
+        <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19034,7 +18929,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.8</v>
+        <v>61.2</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19077,24 +18972,24 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>S 425-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45462</v>
+        <v>46070</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19106,8 +19001,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>1.4</v>
+        <v>17.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19150,7 +19050,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 470-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19164,10 +19064,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45250</v>
+        <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19177,11 +19077,6 @@
       <c r="G247" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I247" t="n">
@@ -19225,10 +19120,10 @@
       </c>
       <c r="V247" s="2" t="inlineStr"/>
     </row>
-    <row r="248" ht="15" customHeight="1">
+    <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 964-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19238,14 +19133,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44559</v>
+        <v>46114</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19259,11 +19154,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I248" t="n">
-        <v>60.7</v>
+        <v>0.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19302,454 +19197,6 @@
         <v>0</v>
       </c>
       <c r="V248" s="2" t="inlineStr"/>
-    </row>
-    <row r="249" ht="15" customHeight="1">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>S 1611-2022</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D249" s="1" t="n">
-        <v>44645</v>
-      </c>
-      <c r="E249" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I249" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J249" t="n">
-        <v>0</v>
-      </c>
-      <c r="K249" t="n">
-        <v>0</v>
-      </c>
-      <c r="L249" t="n">
-        <v>0</v>
-      </c>
-      <c r="M249" t="n">
-        <v>0</v>
-      </c>
-      <c r="N249" t="n">
-        <v>0</v>
-      </c>
-      <c r="O249" t="n">
-        <v>0</v>
-      </c>
-      <c r="P249" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0</v>
-      </c>
-      <c r="S249" t="n">
-        <v>0</v>
-      </c>
-      <c r="T249" t="n">
-        <v>0</v>
-      </c>
-      <c r="U249" t="n">
-        <v>0</v>
-      </c>
-      <c r="V249" s="2" t="inlineStr"/>
-    </row>
-    <row r="250" ht="15" customHeight="1">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>S 1362-2025</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D250" s="1" t="n">
-        <v>45775</v>
-      </c>
-      <c r="E250" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I250" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J250" t="n">
-        <v>0</v>
-      </c>
-      <c r="K250" t="n">
-        <v>0</v>
-      </c>
-      <c r="L250" t="n">
-        <v>0</v>
-      </c>
-      <c r="M250" t="n">
-        <v>0</v>
-      </c>
-      <c r="N250" t="n">
-        <v>0</v>
-      </c>
-      <c r="O250" t="n">
-        <v>0</v>
-      </c>
-      <c r="P250" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0</v>
-      </c>
-      <c r="S250" t="n">
-        <v>0</v>
-      </c>
-      <c r="T250" t="n">
-        <v>0</v>
-      </c>
-      <c r="U250" t="n">
-        <v>0</v>
-      </c>
-      <c r="V250" s="2" t="inlineStr"/>
-    </row>
-    <row r="251" ht="15" customHeight="1">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>S 2703-2025</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D251" s="1" t="n">
-        <v>45929</v>
-      </c>
-      <c r="E251" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I251" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="J251" t="n">
-        <v>0</v>
-      </c>
-      <c r="K251" t="n">
-        <v>0</v>
-      </c>
-      <c r="L251" t="n">
-        <v>0</v>
-      </c>
-      <c r="M251" t="n">
-        <v>0</v>
-      </c>
-      <c r="N251" t="n">
-        <v>0</v>
-      </c>
-      <c r="O251" t="n">
-        <v>0</v>
-      </c>
-      <c r="P251" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0</v>
-      </c>
-      <c r="S251" t="n">
-        <v>0</v>
-      </c>
-      <c r="T251" t="n">
-        <v>0</v>
-      </c>
-      <c r="U251" t="n">
-        <v>0</v>
-      </c>
-      <c r="V251" s="2" t="inlineStr"/>
-    </row>
-    <row r="252" ht="15" customHeight="1">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>S 425-2026</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D252" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E252" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I252" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J252" t="n">
-        <v>0</v>
-      </c>
-      <c r="K252" t="n">
-        <v>0</v>
-      </c>
-      <c r="L252" t="n">
-        <v>0</v>
-      </c>
-      <c r="M252" t="n">
-        <v>0</v>
-      </c>
-      <c r="N252" t="n">
-        <v>0</v>
-      </c>
-      <c r="O252" t="n">
-        <v>0</v>
-      </c>
-      <c r="P252" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0</v>
-      </c>
-      <c r="S252" t="n">
-        <v>0</v>
-      </c>
-      <c r="T252" t="n">
-        <v>0</v>
-      </c>
-      <c r="U252" t="n">
-        <v>0</v>
-      </c>
-      <c r="V252" s="2" t="inlineStr"/>
-    </row>
-    <row r="253" ht="15" customHeight="1">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>S 470-2026</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D253" s="1" t="n">
-        <v>46073</v>
-      </c>
-      <c r="E253" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I253" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J253" t="n">
-        <v>0</v>
-      </c>
-      <c r="K253" t="n">
-        <v>0</v>
-      </c>
-      <c r="L253" t="n">
-        <v>0</v>
-      </c>
-      <c r="M253" t="n">
-        <v>0</v>
-      </c>
-      <c r="N253" t="n">
-        <v>0</v>
-      </c>
-      <c r="O253" t="n">
-        <v>0</v>
-      </c>
-      <c r="P253" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0</v>
-      </c>
-      <c r="S253" t="n">
-        <v>0</v>
-      </c>
-      <c r="T253" t="n">
-        <v>0</v>
-      </c>
-      <c r="U253" t="n">
-        <v>0</v>
-      </c>
-      <c r="V253" s="2" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>S 964-2026</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D254" s="1" t="n">
-        <v>46114</v>
-      </c>
-      <c r="E254" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I254" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J254" t="n">
-        <v>0</v>
-      </c>
-      <c r="K254" t="n">
-        <v>0</v>
-      </c>
-      <c r="L254" t="n">
-        <v>0</v>
-      </c>
-      <c r="M254" t="n">
-        <v>0</v>
-      </c>
-      <c r="N254" t="n">
-        <v>0</v>
-      </c>
-      <c r="O254" t="n">
-        <v>0</v>
-      </c>
-      <c r="P254" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0</v>
-      </c>
-      <c r="S254" t="n">
-        <v>0</v>
-      </c>
-      <c r="T254" t="n">
-        <v>0</v>
-      </c>
-      <c r="U254" t="n">
-        <v>0</v>
-      </c>
-      <c r="V254" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>45698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 62418-2025</t>
+          <t>A 55173-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46007</v>
+        <v>45237</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,17 +1314,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1354,248 +1354,248 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 62418-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 60033-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45642</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>5.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ögonpyrola</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55173-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45237</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8399-2022</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44610</v>
+        <v>45669</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 67514-2021</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44524</v>
+        <v>45713</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 8399-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45229</v>
+        <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 67514-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45411</v>
+        <v>44524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45532</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,8 +2504,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2548,7 +2553,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2562,10 +2567,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45532</v>
+        <v>44853</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2578,7 +2583,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2621,7 +2626,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2631,14 +2636,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44571</v>
+        <v>44509</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2651,7 +2656,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2694,7 +2699,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2708,10 +2713,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45127</v>
+        <v>45183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2724,7 +2729,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2767,7 +2772,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2781,10 +2786,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44747</v>
+        <v>45680</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2797,7 +2802,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2840,7 +2845,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2850,14 +2855,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45055</v>
+        <v>45218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2870,7 +2875,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2913,7 +2918,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2927,10 +2932,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45757</v>
+        <v>45790</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2942,8 +2947,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2986,7 +2996,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3000,10 +3010,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44853</v>
+        <v>45791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3015,8 +3025,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3059,7 +3074,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3073,10 +3088,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44691</v>
+        <v>45791</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3088,8 +3103,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3132,7 +3152,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3146,10 +3166,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45503</v>
+        <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3161,13 +3181,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3210,7 +3225,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3224,10 +3239,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45504</v>
+        <v>45792</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3245,7 +3260,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3288,7 +3303,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3302,10 +3317,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45516</v>
+        <v>44816</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3318,7 +3333,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3361,7 +3376,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3375,10 +3390,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45146</v>
+        <v>45055</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3391,7 +3406,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3434,7 +3449,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3448,10 +3463,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45103</v>
+        <v>45509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3463,8 +3478,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3507,7 +3527,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3521,10 +3541,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45246</v>
+        <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3537,7 +3557,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3580,7 +3600,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3594,10 +3614,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45680</v>
+        <v>45106</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3610,7 +3630,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3653,7 +3673,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3667,10 +3687,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45099</v>
+        <v>45106</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3683,7 +3703,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3726,7 +3746,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3740,10 +3760,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44854</v>
+        <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3756,7 +3776,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3799,7 +3819,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3813,10 +3833,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45356</v>
+        <v>45884</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3829,7 +3849,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3872,7 +3892,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3882,14 +3902,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45177</v>
+        <v>45793</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3902,7 +3922,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3945,7 +3965,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3959,10 +3979,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45257</v>
+        <v>45748</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3975,7 +3995,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4018,7 +4038,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4032,10 +4052,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44846</v>
+        <v>45356</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4048,7 +4068,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4091,7 +4111,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4105,10 +4125,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45462</v>
+        <v>45390</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4121,7 +4141,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4164,7 +4184,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4178,10 +4198,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45884</v>
+        <v>45797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4194,7 +4214,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4237,7 +4257,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4251,10 +4271,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45532</v>
+        <v>45797</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4267,7 +4287,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4310,7 +4330,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4324,10 +4344,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45517</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4339,13 +4359,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4388,7 +4403,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4402,10 +4417,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45672</v>
+        <v>44565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4417,13 +4432,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4466,7 +4476,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4480,10 +4490,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45672</v>
+        <v>45800</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4495,13 +4505,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4544,7 +4549,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4558,10 +4563,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45730</v>
+        <v>45799</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4574,7 +4579,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4617,7 +4622,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4631,10 +4636,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44565</v>
+        <v>45503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4646,8 +4651,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4690,7 +4700,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4704,10 +4714,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45581</v>
+        <v>45504</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4719,8 +4729,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4763,7 +4778,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4777,10 +4792,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44929</v>
+        <v>45800</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4793,7 +4808,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4836,7 +4851,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4846,14 +4861,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45807</v>
+        <v>45908</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4909,7 +4924,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4923,10 +4938,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45905</v>
+        <v>44929</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4939,7 +4954,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4982,7 +4997,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4992,14 +5007,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45908</v>
+        <v>45905</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5012,7 +5027,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5072,7 +5087,7 @@
         <v>45909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5145,7 +5160,7 @@
         <v>45909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5206,7 +5221,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5220,10 +5235,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45669</v>
+        <v>45799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5236,7 +5251,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5279,7 +5294,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5293,10 +5308,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45175</v>
+        <v>45912</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5309,7 +5324,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5352,7 +5367,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5366,10 +5381,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45357</v>
+        <v>45799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5382,7 +5397,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5425,7 +5440,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5439,10 +5454,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45582</v>
+        <v>45799</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5455,7 +5470,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5498,7 +5513,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5512,10 +5527,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45912</v>
+        <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5528,7 +5543,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5571,7 +5586,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5585,10 +5600,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46044</v>
+        <v>45918</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5601,7 +5616,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5661,7 +5676,7 @@
         <v>45918</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5717,7 +5732,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5734,7 +5749,7 @@
         <v>45918</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5747,7 +5762,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5790,7 +5805,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5804,10 +5819,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45918</v>
+        <v>45713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5820,7 +5835,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5863,7 +5878,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5877,10 +5892,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45608</v>
+        <v>45517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5892,8 +5907,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5936,7 +5956,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5950,10 +5970,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45713</v>
+        <v>45146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5966,7 +5986,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6029,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6023,10 +6043,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45799</v>
+        <v>45582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6039,7 +6059,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6082,7 +6102,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6096,10 +6116,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45713</v>
+        <v>45118</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6112,7 +6132,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6172,7 +6192,7 @@
         <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6228,7 +6248,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6242,10 +6262,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45587</v>
+        <v>45127</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6258,7 +6278,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6301,7 +6321,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6315,10 +6335,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44970</v>
+        <v>45937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6331,7 +6351,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6374,7 +6394,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6388,10 +6408,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45937</v>
+        <v>45580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6403,8 +6423,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6464,7 +6489,7 @@
         <v>45939</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6520,7 +6545,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6534,10 +6559,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46149</v>
+        <v>45509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6550,7 +6575,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6593,7 +6618,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6607,10 +6632,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46149</v>
+        <v>45609</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6623,7 +6648,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6666,7 +6691,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6680,10 +6705,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46148</v>
+        <v>45609</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6696,7 +6721,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6739,7 +6764,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6753,10 +6778,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45950</v>
+        <v>45713</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6769,7 +6794,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6812,7 +6837,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6826,10 +6851,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45951</v>
+        <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6842,7 +6867,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6885,7 +6910,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6899,10 +6924,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45951</v>
+        <v>44970</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6915,7 +6940,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6958,7 +6983,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6975,7 +7000,7 @@
         <v>45951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6988,7 +7013,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7031,7 +7056,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7045,10 +7070,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45957</v>
+        <v>45951</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7061,7 +7086,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7104,7 +7129,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7118,10 +7143,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45957</v>
+        <v>45951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7177,7 +7202,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7191,10 +7216,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45463</v>
+        <v>45950</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7207,7 +7232,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7267,7 +7292,7 @@
         <v>45957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7323,7 +7348,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7337,10 +7362,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44935</v>
+        <v>45957</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7353,7 +7378,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7396,7 +7421,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7413,7 +7438,7 @@
         <v>45957</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7426,7 +7451,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7469,7 +7494,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7483,10 +7508,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46161</v>
+        <v>45957</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7499,7 +7524,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7542,7 +7567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7556,10 +7581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45965</v>
+        <v>45737</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7572,7 +7597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7615,7 +7640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7629,10 +7654,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45964</v>
+        <v>45098</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7645,7 +7670,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7688,7 +7713,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7702,10 +7727,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46078</v>
+        <v>45964</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7718,7 +7743,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>6.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7778,7 +7803,7 @@
         <v>45965</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7834,7 +7859,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7848,10 +7873,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45748</v>
+        <v>45965</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7864,7 +7889,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7907,7 +7932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7921,10 +7946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46162</v>
+        <v>45440</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7942,7 +7967,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7985,7 +8010,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7999,10 +8024,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45974</v>
+        <v>45231</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8015,7 +8040,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8058,7 +8083,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8072,10 +8097,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45975</v>
+        <v>45356</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8088,7 +8113,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.5</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8131,7 +8156,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8145,10 +8170,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45975</v>
+        <v>45581</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8161,7 +8186,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8204,7 +8229,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8218,10 +8243,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45975</v>
+        <v>45246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8234,7 +8259,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8277,7 +8302,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8294,7 +8319,7 @@
         <v>45974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8307,7 +8332,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8350,7 +8375,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8364,10 +8389,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45978</v>
+        <v>45730</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8380,7 +8405,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8423,7 +8448,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8437,10 +8462,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45615</v>
+        <v>45974</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8453,7 +8478,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8496,7 +8521,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8510,10 +8535,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45978</v>
+        <v>45975</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8526,7 +8551,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8569,7 +8594,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8583,10 +8608,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45978</v>
+        <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8599,7 +8624,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8642,7 +8667,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8659,7 +8684,7 @@
         <v>45978</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8672,7 +8697,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8715,7 +8740,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8729,10 +8754,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45980</v>
+        <v>45978</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8744,13 +8769,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8793,7 +8813,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8807,10 +8827,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45980</v>
+        <v>45978</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8823,7 +8843,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8866,7 +8886,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8880,10 +8900,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45980</v>
+        <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8895,13 +8915,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8944,7 +8959,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8958,10 +8973,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45986</v>
+        <v>45978</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8974,7 +8989,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9017,7 +9032,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9031,10 +9046,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46170</v>
+        <v>44581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9047,7 +9062,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9090,7 +9105,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9104,10 +9119,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44581</v>
+        <v>45980</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9120,7 +9135,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9163,7 +9178,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9177,10 +9192,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45218</v>
+        <v>45980</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9192,8 +9207,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9236,7 +9256,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9246,14 +9266,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45992</v>
+        <v>45980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9265,8 +9285,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9309,7 +9334,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9323,10 +9348,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45146</v>
+        <v>45188</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9339,7 +9364,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9382,7 +9407,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9396,10 +9421,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45995</v>
+        <v>45986</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9412,7 +9437,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9455,7 +9480,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9469,10 +9494,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45996</v>
+        <v>45516</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9485,7 +9510,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9528,7 +9553,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9542,10 +9567,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46000</v>
+        <v>45516</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9558,7 +9583,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9601,7 +9626,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9611,14 +9636,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46000</v>
+        <v>45103</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9631,7 +9656,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9674,7 +9699,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9688,10 +9713,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46000</v>
+        <v>45099</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9704,7 +9729,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9747,7 +9772,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9757,14 +9782,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46000</v>
+        <v>45827</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9777,7 +9802,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9820,7 +9845,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9830,14 +9855,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46000</v>
+        <v>45177</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9850,7 +9875,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9893,7 +9918,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9907,10 +9932,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46000</v>
+        <v>45257</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9923,7 +9948,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9966,7 +9991,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9976,14 +10001,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46000</v>
+        <v>45992</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9996,7 +10021,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10039,7 +10064,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10053,10 +10078,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46000</v>
+        <v>45995</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10069,7 +10094,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10112,7 +10137,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10126,10 +10151,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46000</v>
+        <v>45996</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10142,7 +10167,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10185,7 +10210,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10202,7 +10227,7 @@
         <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10215,7 +10240,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10258,7 +10283,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10272,10 +10297,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46175</v>
+        <v>46000</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10287,13 +10312,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10336,7 +10356,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10350,10 +10370,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45103</v>
+        <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10366,7 +10386,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10409,7 +10429,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10423,10 +10443,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46175</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10438,13 +10458,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10487,7 +10502,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10501,10 +10516,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45146</v>
+        <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10517,7 +10532,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10560,7 +10575,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10574,10 +10589,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46175</v>
+        <v>44854</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10589,13 +10604,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10638,7 +10648,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10652,10 +10662,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46175</v>
+        <v>46000</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10667,13 +10677,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10716,7 +10721,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10730,10 +10735,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46176</v>
+        <v>46000</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10746,7 +10751,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10789,7 +10794,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10799,14 +10804,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46175</v>
+        <v>46000</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10818,13 +10823,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46176</v>
+        <v>46000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10940,7 +10940,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45609</v>
+        <v>46000</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11013,7 +11013,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45730</v>
+        <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11086,7 +11086,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11100,10 +11100,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46010</v>
+        <v>46034</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>9.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11159,7 +11159,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11173,10 +11173,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46013</v>
+        <v>45103</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11188,13 +11188,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>21.4</v>
+        <v>4.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11237,7 +11232,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11251,10 +11246,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45139</v>
+        <v>46000</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11267,7 +11262,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11310,7 +11305,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11324,10 +11319,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46030</v>
+        <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11340,7 +11335,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11383,7 +11378,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11397,10 +11392,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46034</v>
+        <v>45357</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11413,7 +11408,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11456,7 +11451,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11470,10 +11465,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46034</v>
+        <v>45771</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11485,8 +11480,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>9.1</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11546,7 +11546,7 @@
         <v>46036</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11616,10 +11616,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45275</v>
+        <v>44747</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.7</v>
+        <v>2.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11675,7 +11675,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11689,10 +11689,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45549</v>
+        <v>44747</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11762,10 +11762,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46042</v>
+        <v>45835</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11821,7 +11821,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11835,10 +11835,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45748</v>
+        <v>46042</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11977,14 +11977,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46044</v>
+        <v>46010</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12040,7 +12040,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12050,14 +12050,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
         <v>46044</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12113,7 +12113,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12123,14 +12123,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12186,7 +12186,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12196,14 +12196,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12276,7 +12276,7 @@
         <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45106</v>
+        <v>46013</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12361,8 +12361,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>5.5</v>
+        <v>21.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12405,7 +12410,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12419,10 +12424,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46065</v>
+        <v>46048</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12478,7 +12483,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12492,10 +12497,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44953</v>
+        <v>45259</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12508,7 +12513,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12551,7 +12556,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12565,10 +12570,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45737</v>
+        <v>45549</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12581,7 +12586,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12641,7 +12646,7 @@
         <v>46066</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12697,7 +12702,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12711,10 +12716,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46070</v>
+        <v>46065</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12727,7 +12732,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12770,7 +12775,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12784,10 +12789,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12800,7 +12805,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12843,7 +12848,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12857,10 +12862,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46198</v>
+        <v>46071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12873,7 +12878,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12916,7 +12921,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12926,14 +12931,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45439</v>
+        <v>46269</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12945,8 +12950,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12989,7 +12999,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13003,10 +13013,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44501</v>
+        <v>46245</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13019,7 +13029,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>10.2</v>
+        <v>5.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13062,7 +13072,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13076,10 +13086,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45624</v>
+        <v>44691</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13092,7 +13102,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13135,7 +13145,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13145,14 +13155,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45609</v>
+        <v>45069</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13165,7 +13175,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13208,7 +13218,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13218,14 +13228,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45609</v>
+        <v>44571</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13238,7 +13248,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13281,7 +13291,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13295,10 +13305,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45098</v>
+        <v>45411</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13311,7 +13321,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13354,7 +13364,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13368,10 +13378,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44747</v>
+        <v>44935</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13384,7 +13394,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13427,7 +13437,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13441,10 +13451,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45509</v>
+        <v>45118</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13456,13 +13466,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13505,7 +13510,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13519,10 +13524,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45771</v>
+        <v>46121</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13534,13 +13539,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13583,7 +13583,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46121</v>
+        <v>45508</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13612,8 +13612,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13656,7 +13661,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13670,10 +13675,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46126</v>
+        <v>45730</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13686,7 +13691,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13729,7 +13734,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13743,10 +13748,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44987</v>
+        <v>46126</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13759,7 +13764,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13802,7 +13807,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13812,14 +13817,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46253</v>
+        <v>45624</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13832,7 +13837,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13875,7 +13880,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13889,10 +13894,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45231</v>
+        <v>44501</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13905,7 +13910,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.4</v>
+        <v>10.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13948,7 +13953,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13962,10 +13967,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46253</v>
+        <v>45463</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13978,7 +13983,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14021,7 +14026,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14035,10 +14040,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45509</v>
+        <v>45608</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14051,7 +14056,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14094,7 +14099,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14104,14 +14109,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46253</v>
+        <v>45462</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14124,7 +14129,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14167,7 +14172,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14181,10 +14186,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46210</v>
+        <v>45275</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14197,7 +14202,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.6</v>
+        <v>6.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14240,7 +14245,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14254,10 +14259,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45508</v>
+        <v>45713</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14269,13 +14274,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14332,10 +14332,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44509</v>
+        <v>45713</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14391,7 +14391,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14401,14 +14401,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46255</v>
+        <v>45146</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14464,7 +14464,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14478,10 +14478,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46260</v>
+        <v>44987</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45106</v>
+        <v>45139</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14610,7 +14610,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14624,10 +14624,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45118</v>
+        <v>45615</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14683,7 +14683,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45118</v>
+        <v>44987</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44979</v>
+        <v>45757</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14829,7 +14829,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14839,14 +14839,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45069</v>
+        <v>45775</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14902,7 +14902,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46267</v>
+        <v>45532</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14975,7 +14975,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14989,10 +14989,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46140</v>
+        <v>45532</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15048,7 +15048,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15062,10 +15062,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44987</v>
+        <v>45532</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15121,7 +15121,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15135,10 +15135,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44509</v>
+        <v>45474</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15150,8 +15150,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15194,7 +15199,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15208,10 +15213,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46268</v>
+        <v>44979</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15224,7 +15229,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15267,7 +15272,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15281,10 +15286,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45580</v>
+        <v>45807</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15296,13 +15301,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15345,7 +15345,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45440</v>
+        <v>45799</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15374,13 +15374,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15423,7 +15418,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15437,10 +15432,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46273</v>
+        <v>46044</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15453,7 +15448,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15496,7 +15491,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15510,10 +15505,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45390</v>
+        <v>45175</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15526,7 +15521,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15569,7 +15564,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15583,10 +15578,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46273</v>
+        <v>45581</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15599,7 +15594,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>7.9</v>
+        <v>1.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15642,7 +15637,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15656,10 +15651,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46274</v>
+        <v>44953</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15672,7 +15667,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15715,7 +15710,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15729,10 +15724,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45713</v>
+        <v>44747</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15745,7 +15740,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15788,7 +15783,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15802,10 +15797,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46274</v>
+        <v>45587</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15818,7 +15813,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15861,7 +15856,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15875,10 +15870,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45516</v>
+        <v>45748</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15891,7 +15886,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15934,7 +15929,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15948,10 +15943,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46280</v>
+        <v>45672</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15963,8 +15958,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16007,7 +16007,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16021,10 +16021,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45581</v>
+        <v>45672</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16036,8 +16036,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16080,7 +16085,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16090,14 +16095,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45644</v>
+        <v>45609</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16109,13 +16114,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16158,7 +16158,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45259</v>
+        <v>46148</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16231,7 +16231,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16245,10 +16245,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45474</v>
+        <v>45118</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16260,13 +16260,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16309,7 +16304,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16323,10 +16318,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45188</v>
+        <v>46149</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16339,7 +16334,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16382,7 +16377,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16396,10 +16391,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44747</v>
+        <v>45782</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16412,7 +16407,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16455,7 +16450,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16469,10 +16464,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45775</v>
+        <v>45782</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16485,7 +16480,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16528,7 +16523,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16542,10 +16537,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44816</v>
+        <v>46149</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16558,7 +16553,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16601,7 +16596,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16615,10 +16610,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45713</v>
+        <v>46162</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16630,8 +16625,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16674,7 +16674,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16688,10 +16688,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46245</v>
+        <v>46078</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16747,7 +16747,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16757,14 +16757,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46269</v>
+        <v>46161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16776,13 +16776,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16825,7 +16820,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16839,10 +16834,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45356</v>
+        <v>46170</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16855,7 +16850,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16898,7 +16893,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16912,10 +16907,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45183</v>
+        <v>46175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16927,8 +16922,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16971,7 +16971,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16985,10 +16985,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45713</v>
+        <v>46175</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17000,8 +17000,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17044,7 +17049,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17058,10 +17063,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45118</v>
+        <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17073,8 +17078,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17117,7 +17127,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17131,10 +17141,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45782</v>
+        <v>46175</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17146,8 +17156,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17190,7 +17205,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17204,10 +17219,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45782</v>
+        <v>46175</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17219,8 +17234,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17263,7 +17283,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17277,10 +17297,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45187</v>
+        <v>46176</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17293,7 +17313,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17336,7 +17356,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17350,10 +17370,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45791</v>
+        <v>46176</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17365,13 +17385,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>8.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17414,7 +17429,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17428,10 +17443,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45791</v>
+        <v>46198</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17443,13 +17458,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17492,7 +17502,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17506,10 +17516,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45790</v>
+        <v>46253</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17521,13 +17531,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17570,7 +17575,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17584,10 +17589,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45793</v>
+        <v>46210</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17600,7 +17605,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17643,7 +17648,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17653,14 +17658,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45792</v>
+        <v>46253</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17672,13 +17677,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17721,7 +17721,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17731,14 +17731,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45792</v>
+        <v>46253</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17794,7 +17794,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17808,10 +17808,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45797</v>
+        <v>46255</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17867,7 +17867,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17881,10 +17881,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45797</v>
+        <v>46260</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17940,7 +17940,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17954,10 +17954,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45799</v>
+        <v>46140</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18013,7 +18013,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18027,10 +18027,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45799</v>
+        <v>44509</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18086,7 +18086,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18100,10 +18100,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45799</v>
+        <v>46267</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18159,7 +18159,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18173,10 +18173,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45799</v>
+        <v>46268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18232,7 +18232,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18246,10 +18246,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45799</v>
+        <v>46274</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18305,7 +18305,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18319,10 +18319,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45800</v>
+        <v>46274</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18392,10 +18392,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45800</v>
+        <v>46273</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18451,7 +18451,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18461,14 +18461,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45827</v>
+        <v>46273</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.3</v>
+        <v>7.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18524,7 +18524,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45835</v>
+        <v>46280</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18597,7 +18597,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18611,10 +18611,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45250</v>
+        <v>44559</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>31.7</v>
+        <v>60.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18675,7 +18675,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18689,10 +18689,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44559</v>
+        <v>44645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18704,13 +18704,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>60.7</v>
+        <v>15.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18753,7 +18748,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18767,10 +18762,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44645</v>
+        <v>45250</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18782,8 +18777,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>15.8</v>
+        <v>31.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18843,7 +18843,7 @@
         <v>45775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46070</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46114</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>45698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 55173-2023</t>
+          <t>A 62418-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45237</v>
+        <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1354,248 +1354,248 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 60033-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55173-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45237</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Brunklöver</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 62418-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 62418-2025 artfynd.xlsx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 62418-2025 karta.png", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 62418-2025 georefererad karta.tif", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 62418-2025 FSC-klagomål.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 62418-2025 FSC-klagomål mail.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 62418-2025 tillsynsbegäran.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 62418-2025 tillsynsbegäran mail.docx", "A 62418-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 60033-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 8399-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45669</v>
+        <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 67514-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45713</v>
+        <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8399-2022</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44610</v>
+        <v>45229</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 67514-2021</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44524</v>
+        <v>45532</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>45532</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2504,13 +2504,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2553,7 +2548,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44853</v>
+        <v>45411</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2583,7 +2578,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2626,7 +2621,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2636,14 +2631,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44509</v>
+        <v>44571</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2656,7 +2651,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2699,7 +2694,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2713,10 +2708,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45183</v>
+        <v>45127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2729,7 +2724,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2772,7 +2767,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2786,10 +2781,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45680</v>
+        <v>44747</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2802,7 +2797,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2845,7 +2840,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2855,14 +2850,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45218</v>
+        <v>45055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2875,7 +2870,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2918,7 +2913,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2932,10 +2927,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45790</v>
+        <v>45757</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2947,13 +2942,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2996,7 +2986,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3010,10 +3000,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45791</v>
+        <v>44853</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3025,13 +3015,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3074,7 +3059,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3088,10 +3073,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45791</v>
+        <v>45503</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3109,7 +3094,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3152,7 +3137,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3166,10 +3151,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45187</v>
+        <v>45504</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3181,8 +3166,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3225,7 +3215,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3239,10 +3229,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45792</v>
+        <v>44691</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3254,13 +3244,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3303,7 +3288,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3317,10 +3302,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44816</v>
+        <v>45516</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3333,7 +3318,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3376,7 +3361,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3390,10 +3375,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45055</v>
+        <v>45146</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3406,7 +3391,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3449,7 +3434,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3463,10 +3448,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45509</v>
+        <v>45103</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3478,13 +3463,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3527,7 +3507,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3541,10 +3521,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45792</v>
+        <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3557,7 +3537,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3600,7 +3580,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,10 +3594,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45106</v>
+        <v>45680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3630,7 +3610,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3673,7 +3653,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,10 +3667,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45106</v>
+        <v>44854</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3703,7 +3683,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3746,7 +3726,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,10 +3740,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44846</v>
+        <v>45099</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3819,7 +3799,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3829,14 +3809,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45884</v>
+        <v>45177</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3849,7 +3829,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3892,7 +3872,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,10 +3886,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45793</v>
+        <v>45356</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3922,7 +3902,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3965,7 +3945,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3979,10 +3959,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45748</v>
+        <v>44846</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3995,7 +3975,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4038,7 +4018,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4052,10 +4032,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45356</v>
+        <v>45257</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4068,7 +4048,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4111,7 +4091,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4125,10 +4105,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45390</v>
+        <v>45884</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4141,7 +4121,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4184,7 +4164,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,10 +4178,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45797</v>
+        <v>45462</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4214,7 +4194,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4257,7 +4237,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4271,10 +4251,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45797</v>
+        <v>45532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4287,7 +4267,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4330,7 +4310,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4344,10 +4324,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>45517</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4359,8 +4339,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4403,7 +4388,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4417,10 +4402,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44565</v>
+        <v>45672</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4432,8 +4417,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4476,7 +4466,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4490,10 +4480,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45800</v>
+        <v>45672</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4505,8 +4495,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4549,7 +4544,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4563,10 +4558,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45799</v>
+        <v>45730</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4579,7 +4574,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4622,7 +4617,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4636,10 +4631,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45503</v>
+        <v>44565</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4651,13 +4646,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4700,7 +4690,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4714,10 +4704,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45504</v>
+        <v>44929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4729,13 +4719,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4778,7 +4763,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4792,10 +4777,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45800</v>
+        <v>45905</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4808,7 +4793,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4868,7 +4853,7 @@
         <v>45908</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4924,7 +4909,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4938,10 +4923,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44929</v>
+        <v>45909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4954,7 +4939,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4997,7 +4982,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5011,10 +4996,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5026,8 +5011,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5070,7 +5060,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5084,10 +5074,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45909</v>
+        <v>45669</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5100,7 +5090,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5143,7 +5133,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5157,10 +5147,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45909</v>
+        <v>45357</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5172,13 +5162,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5221,7 +5206,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5235,10 +5220,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45799</v>
+        <v>45582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5251,7 +5236,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5311,7 +5296,7 @@
         <v>45912</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5367,7 +5352,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5381,10 +5366,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45799</v>
+        <v>45608</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5397,7 +5382,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5440,7 +5425,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5454,10 +5439,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45799</v>
+        <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5513,7 +5498,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5527,10 +5512,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45799</v>
+        <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5543,7 +5528,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5586,7 +5571,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5603,7 +5588,7 @@
         <v>45918</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5616,7 +5601,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5659,7 +5644,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,10 +5658,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45918</v>
+        <v>45581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5689,7 +5674,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5732,7 +5717,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5746,10 +5731,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45918</v>
+        <v>45807</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5762,7 +5747,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5805,7 +5790,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5822,7 +5807,7 @@
         <v>45713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5835,7 +5820,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5878,7 +5863,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5892,10 +5877,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45517</v>
+        <v>45713</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5907,13 +5892,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5956,7 +5936,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5970,10 +5950,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45146</v>
+        <v>45587</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5986,7 +5966,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6029,7 +6009,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6043,10 +6023,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45582</v>
+        <v>44970</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6059,7 +6039,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6102,7 +6082,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6116,10 +6096,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45118</v>
+        <v>45937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6175,7 +6155,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6192,7 +6172,7 @@
         <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6205,7 +6185,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6248,7 +6228,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6262,10 +6242,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45127</v>
+        <v>45939</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6278,7 +6258,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6321,7 +6301,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6335,10 +6315,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45937</v>
+        <v>45175</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6351,7 +6331,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6394,7 +6374,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6408,10 +6388,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45580</v>
+        <v>45950</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6423,13 +6403,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6472,7 +6447,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6486,10 +6461,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6502,7 +6477,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6545,7 +6520,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6559,10 +6534,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45509</v>
+        <v>45951</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6575,7 +6550,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6618,7 +6593,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6632,10 +6607,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45609</v>
+        <v>45951</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6648,7 +6623,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6691,7 +6666,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6705,10 +6680,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45609</v>
+        <v>45463</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6721,7 +6696,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6764,7 +6739,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6778,10 +6753,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45713</v>
+        <v>44935</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6794,7 +6769,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6837,7 +6812,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6851,10 +6826,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45439</v>
+        <v>45957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6867,7 +6842,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6910,7 +6885,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6924,10 +6899,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44970</v>
+        <v>45957</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6940,7 +6915,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6983,7 +6958,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6997,10 +6972,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45951</v>
+        <v>46044</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7013,7 +6988,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7056,7 +7031,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7070,10 +7045,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7086,7 +7061,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7129,7 +7104,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7143,10 +7118,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7159,7 +7134,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7202,7 +7177,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7216,10 +7191,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45950</v>
+        <v>45748</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7232,7 +7207,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7275,7 +7250,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7289,10 +7264,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7305,7 +7280,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7348,7 +7323,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7362,10 +7337,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7378,7 +7353,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7421,7 +7396,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7435,10 +7410,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45957</v>
+        <v>45799</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7451,7 +7426,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7494,7 +7469,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7508,10 +7483,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7567,7 +7542,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7581,10 +7556,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45737</v>
+        <v>45615</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7597,7 +7572,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7640,7 +7615,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7654,10 +7629,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45098</v>
+        <v>45974</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7670,7 +7645,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7713,7 +7688,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7727,10 +7702,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45964</v>
+        <v>45975</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7743,7 +7718,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7786,7 +7761,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7800,10 +7775,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7816,7 +7791,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7859,7 +7834,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7873,10 +7848,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7889,7 +7864,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7932,7 +7907,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7946,10 +7921,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45440</v>
+        <v>45974</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7961,13 +7936,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8010,7 +7980,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8024,10 +7994,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45231</v>
+        <v>45978</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8040,7 +8010,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8083,7 +8053,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8097,10 +8067,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45356</v>
+        <v>45978</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8113,7 +8083,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8156,7 +8126,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8170,10 +8140,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45581</v>
+        <v>45978</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8186,7 +8156,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8229,7 +8199,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8243,10 +8213,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45246</v>
+        <v>45978</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8259,7 +8229,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8302,7 +8272,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8316,10 +8286,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8331,8 +8301,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8375,7 +8350,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8389,10 +8364,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45730</v>
+        <v>45980</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8405,7 +8380,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8448,7 +8423,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8462,10 +8437,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8477,8 +8452,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8521,7 +8501,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8535,10 +8515,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45975</v>
+        <v>44581</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8551,7 +8531,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8594,7 +8574,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8608,10 +8588,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45975</v>
+        <v>45218</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8624,7 +8604,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8.5</v>
+        <v>3.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8667,7 +8647,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8681,10 +8661,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45978</v>
+        <v>45146</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8697,7 +8677,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8740,7 +8720,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8754,10 +8734,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8770,7 +8750,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8813,7 +8793,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8827,10 +8807,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45978</v>
+        <v>46149</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8843,7 +8823,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8886,7 +8866,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8900,10 +8880,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45975</v>
+        <v>46149</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8916,7 +8896,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8959,7 +8939,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8973,10 +8953,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45978</v>
+        <v>46148</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8989,7 +8969,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9032,7 +9012,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9042,14 +9022,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44581</v>
+        <v>45992</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9062,7 +9042,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9105,7 +9085,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9119,10 +9099,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45980</v>
+        <v>45995</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9135,7 +9115,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9178,7 +9158,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9192,10 +9172,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45980</v>
+        <v>45996</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,13 +9187,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9256,7 +9231,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9270,10 +9245,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45980</v>
+        <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9285,13 +9260,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>3.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9334,7 +9304,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9344,14 +9314,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45188</v>
+        <v>46000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9407,7 +9377,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9421,10 +9391,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45986</v>
+        <v>46000</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9437,7 +9407,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9480,7 +9450,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9494,10 +9464,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45516</v>
+        <v>46000</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9510,7 +9480,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9553,7 +9523,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9567,10 +9537,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45516</v>
+        <v>46000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9583,7 +9553,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9626,7 +9596,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9640,10 +9610,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45103</v>
+        <v>46000</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9656,7 +9626,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9699,7 +9669,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9713,10 +9683,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45099</v>
+        <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9729,7 +9699,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9772,7 +9742,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9782,14 +9752,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45827</v>
+        <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9802,7 +9772,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9845,7 +9815,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9855,14 +9825,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45177</v>
+        <v>46000</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9875,7 +9845,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9918,7 +9888,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9932,10 +9902,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45257</v>
+        <v>45609</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9948,7 +9918,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9991,7 +9961,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10001,14 +9971,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10021,7 +9991,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10064,7 +10034,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10078,10 +10048,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45995</v>
+        <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10094,7 +10064,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10137,7 +10107,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10151,10 +10121,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45996</v>
+        <v>45146</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10167,7 +10137,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10210,7 +10180,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10224,10 +10194,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46000</v>
+        <v>45730</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10240,7 +10210,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>8.300000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10283,7 +10253,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10297,10 +10267,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10313,7 +10283,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10356,7 +10326,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10370,10 +10340,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46000</v>
+        <v>46013</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10385,8 +10355,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>21.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10429,7 +10404,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10443,10 +10418,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>45139</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10459,7 +10434,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10502,7 +10477,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10516,10 +10491,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46030</v>
+        <v>46161</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10532,7 +10507,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10575,7 +10550,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10589,10 +10564,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44854</v>
+        <v>46078</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10605,7 +10580,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10648,7 +10623,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10662,10 +10637,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10678,7 +10653,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10721,7 +10696,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10735,10 +10710,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46000</v>
+        <v>45275</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10751,7 +10726,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10794,7 +10769,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10804,14 +10779,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46000</v>
+        <v>45549</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10824,7 +10799,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10867,7 +10842,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10881,10 +10856,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46000</v>
+        <v>46034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10940,7 +10915,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10954,10 +10929,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46000</v>
+        <v>45748</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10970,7 +10945,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11013,7 +10988,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11030,7 +11005,7 @@
         <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11043,7 +11018,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>9.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11086,7 +11061,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11100,10 +11075,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11116,7 +11091,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>9.1</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11159,7 +11134,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11173,10 +11148,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45103</v>
+        <v>46162</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11188,8 +11163,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11232,7 +11212,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11246,10 +11226,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46000</v>
+        <v>46042</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11262,7 +11242,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11305,7 +11285,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11319,10 +11299,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45146</v>
+        <v>45106</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11335,7 +11315,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11378,7 +11358,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11392,10 +11372,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45357</v>
+        <v>46042</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11408,7 +11388,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11451,7 +11431,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11461,14 +11441,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45771</v>
+        <v>46044</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11480,13 +11460,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11529,7 +11504,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11543,10 +11518,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11559,7 +11534,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11602,7 +11577,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11612,14 +11587,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44747</v>
+        <v>46044</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11632,7 +11607,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11675,7 +11650,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11689,10 +11664,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44747</v>
+        <v>46048</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11748,7 +11723,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11762,10 +11737,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45835</v>
+        <v>46048</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11778,7 +11753,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11821,7 +11796,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11835,10 +11810,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46042</v>
+        <v>44953</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11851,7 +11826,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11894,7 +11869,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11908,10 +11883,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46042</v>
+        <v>45737</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11924,7 +11899,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11967,7 +11942,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11981,10 +11956,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46010</v>
+        <v>45439</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11997,7 +11972,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12040,7 +12015,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12050,14 +12025,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46044</v>
+        <v>46065</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12070,7 +12045,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12113,7 +12088,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12127,10 +12102,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46044</v>
+        <v>46170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12143,7 +12118,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12186,7 +12161,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12196,14 +12171,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46044</v>
+        <v>46066</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12216,7 +12191,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12259,7 +12234,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12273,10 +12248,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46048</v>
+        <v>44501</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12289,7 +12264,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>10.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12332,7 +12307,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12346,10 +12321,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46013</v>
+        <v>46070</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12361,13 +12336,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>21.4</v>
+        <v>5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12410,7 +12380,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12424,10 +12394,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46048</v>
+        <v>46071</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12483,7 +12453,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12497,10 +12467,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45259</v>
+        <v>45624</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12513,7 +12483,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12556,7 +12526,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12570,10 +12540,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45549</v>
+        <v>45609</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12586,7 +12556,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12629,7 +12599,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12643,10 +12613,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46066</v>
+        <v>45609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12659,7 +12629,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12702,7 +12672,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12716,10 +12686,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46065</v>
+        <v>45098</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12732,7 +12702,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12775,7 +12745,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12789,10 +12759,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46070</v>
+        <v>46175</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12804,8 +12774,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12848,7 +12823,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12862,10 +12837,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46071</v>
+        <v>46175</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12877,8 +12852,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12921,7 +12901,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12931,14 +12911,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46269</v>
+        <v>46175</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12952,11 +12932,11 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12999,7 +12979,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13013,10 +12993,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46245</v>
+        <v>46175</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13028,8 +13008,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13072,7 +13057,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13086,10 +13071,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44691</v>
+        <v>46176</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13102,7 +13087,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13145,7 +13130,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13155,14 +13140,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45069</v>
+        <v>46175</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13174,8 +13159,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13218,7 +13208,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13228,14 +13218,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44571</v>
+        <v>46176</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13248,7 +13238,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13291,7 +13281,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13305,10 +13295,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45411</v>
+        <v>44747</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13321,7 +13311,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13364,7 +13354,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13378,10 +13368,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44935</v>
+        <v>45509</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13393,8 +13383,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13437,7 +13432,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13451,10 +13446,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45118</v>
+        <v>45771</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13466,8 +13461,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13527,7 +13527,7 @@
         <v>46121</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45508</v>
+        <v>46126</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13612,13 +13612,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13661,7 +13656,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13675,10 +13670,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45730</v>
+        <v>44987</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13691,7 +13686,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13734,7 +13729,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13748,10 +13743,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46126</v>
+        <v>45231</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13764,7 +13759,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13807,7 +13802,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13821,10 +13816,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45624</v>
+        <v>45509</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13837,7 +13832,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13880,7 +13875,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13894,10 +13889,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44501</v>
+        <v>46198</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13910,7 +13905,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13953,7 +13948,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13967,10 +13962,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45463</v>
+        <v>45508</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13982,8 +13977,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14026,7 +14026,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14040,10 +14040,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45608</v>
+        <v>44509</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14099,7 +14099,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14113,10 +14113,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45462</v>
+        <v>45106</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14172,7 +14172,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14186,10 +14186,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45275</v>
+        <v>45118</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>6.7</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14245,7 +14245,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14259,10 +14259,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45713</v>
+        <v>45118</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14332,10 +14332,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45713</v>
+        <v>44979</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14391,7 +14391,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45146</v>
+        <v>45069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14464,7 +14464,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14474,14 +14474,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44987</v>
+        <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45139</v>
+        <v>46253</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14610,7 +14610,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14620,14 +14620,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45615</v>
+        <v>46253</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14683,7 +14683,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44987</v>
+        <v>46210</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45757</v>
+        <v>44987</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14829,7 +14829,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45775</v>
+        <v>46255</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14902,7 +14902,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45532</v>
+        <v>45580</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14931,8 +14931,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14975,7 +14980,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14989,10 +14994,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45532</v>
+        <v>45440</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15004,8 +15009,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15048,7 +15058,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15062,10 +15072,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45532</v>
+        <v>45390</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15078,7 +15088,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15121,7 +15131,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15135,10 +15145,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45474</v>
+        <v>46260</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15150,13 +15160,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15199,7 +15204,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15213,10 +15218,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44979</v>
+        <v>45713</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15229,7 +15234,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15272,7 +15277,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15286,10 +15291,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45807</v>
+        <v>46267</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15302,7 +15307,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15345,7 +15350,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15359,10 +15364,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45799</v>
+        <v>46140</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15375,7 +15380,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15418,7 +15423,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15432,10 +15437,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46044</v>
+        <v>44509</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15448,7 +15453,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15491,7 +15496,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15505,10 +15510,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45175</v>
+        <v>46268</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15521,7 +15526,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15564,7 +15569,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15578,10 +15583,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45581</v>
+        <v>45516</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15594,7 +15599,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15637,7 +15642,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15651,10 +15656,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44953</v>
+        <v>45581</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15667,7 +15672,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15710,7 +15715,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15720,14 +15725,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44747</v>
+        <v>45644</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15739,8 +15744,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15783,7 +15793,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15797,10 +15807,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45587</v>
+        <v>45259</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15813,7 +15823,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15856,7 +15866,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15870,10 +15880,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45748</v>
+        <v>46273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15886,7 +15896,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>7.1</v>
+        <v>2.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15929,7 +15939,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15943,10 +15953,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45672</v>
+        <v>45474</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15960,11 +15970,11 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16007,7 +16017,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16021,10 +16031,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45672</v>
+        <v>46273</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16036,13 +16046,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16085,7 +16090,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16099,10 +16104,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45609</v>
+        <v>46274</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16158,7 +16163,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16172,10 +16177,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46148</v>
+        <v>45188</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16188,7 +16193,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16231,7 +16236,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16245,10 +16250,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45118</v>
+        <v>44747</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16261,7 +16266,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16304,7 +16309,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16318,10 +16323,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46149</v>
+        <v>45775</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16334,7 +16339,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16377,7 +16382,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16391,10 +16396,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45782</v>
+        <v>44816</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16407,7 +16412,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16450,7 +16455,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16464,10 +16469,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45782</v>
+        <v>46274</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16480,7 +16485,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16523,7 +16528,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16537,10 +16542,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46149</v>
+        <v>45713</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16596,7 +16601,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16610,10 +16615,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46162</v>
+        <v>45356</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16625,13 +16630,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16674,7 +16674,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16688,10 +16688,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46078</v>
+        <v>45183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16747,7 +16747,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16761,10 +16761,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46161</v>
+        <v>45713</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16820,7 +16820,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16834,10 +16834,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46170</v>
+        <v>46280</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.2</v>
+        <v>6.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16893,7 +16893,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16907,10 +16907,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46175</v>
+        <v>45118</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16922,13 +16922,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16971,7 +16966,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16985,10 +16980,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46175</v>
+        <v>45782</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17000,13 +16995,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17049,7 +17039,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17063,10 +17053,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46175</v>
+        <v>45782</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17078,13 +17068,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17127,7 +17112,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17137,14 +17122,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46175</v>
+        <v>46269</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17158,11 +17143,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17205,7 +17190,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17219,10 +17204,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46175</v>
+        <v>45187</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17234,13 +17219,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17283,7 +17263,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17297,10 +17277,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46176</v>
+        <v>45791</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17312,8 +17292,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17356,7 +17341,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17370,10 +17355,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46176</v>
+        <v>45791</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17385,8 +17370,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17429,7 +17419,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17443,10 +17433,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46198</v>
+        <v>45790</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17458,8 +17448,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17502,7 +17497,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17516,10 +17511,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46253</v>
+        <v>45793</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17532,7 +17527,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>5.3</v>
+        <v>8.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17575,7 +17570,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17589,10 +17584,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46210</v>
+        <v>45792</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17604,8 +17599,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17648,7 +17648,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17658,14 +17658,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46253</v>
+        <v>45792</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17721,7 +17721,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17731,14 +17731,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46253</v>
+        <v>45797</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17794,7 +17794,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17808,10 +17808,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46255</v>
+        <v>45797</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17867,7 +17867,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17881,10 +17881,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46260</v>
+        <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17940,7 +17940,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17954,10 +17954,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46140</v>
+        <v>45799</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18013,7 +18013,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18027,10 +18027,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44509</v>
+        <v>45799</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18086,7 +18086,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18100,10 +18100,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46267</v>
+        <v>45799</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18159,7 +18159,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18173,10 +18173,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46268</v>
+        <v>45799</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18232,7 +18232,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18246,10 +18246,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46274</v>
+        <v>45799</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18305,7 +18305,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18319,10 +18319,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46274</v>
+        <v>45800</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18392,10 +18392,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46273</v>
+        <v>45800</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18451,7 +18451,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18461,14 +18461,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46273</v>
+        <v>45827</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>7.9</v>
+        <v>0.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18524,7 +18524,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46280</v>
+        <v>45835</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18597,7 +18597,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18611,10 +18611,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44559</v>
+        <v>45250</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>60.7</v>
+        <v>31.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18675,7 +18675,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18689,10 +18689,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44645</v>
+        <v>44559</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18704,8 +18704,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>15.8</v>
+        <v>60.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18748,7 +18753,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18762,10 +18767,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45250</v>
+        <v>44645</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18777,13 +18782,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>31.7</v>
+        <v>15.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18843,7 +18843,7 @@
         <v>45775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46070</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46114</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>45698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60033-2024</t>
+          <t>A 55173-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45642</v>
+        <v>45237</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,17 +1419,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1459,143 +1459,143 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 60033-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55173-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45237</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45229</v>
+        <v>45218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45532</v>
+        <v>44816</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45532</v>
+        <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45411</v>
+        <v>45748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44571</v>
+        <v>45390</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45127</v>
+        <v>46013</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,8 +2723,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>21.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2767,7 +2772,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2781,10 +2786,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44747</v>
+        <v>45503</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,8 +2801,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2840,7 +2850,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2850,14 +2860,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45055</v>
+        <v>45504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2869,8 +2879,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2913,7 +2928,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2927,10 +2942,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45757</v>
+        <v>45884</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2943,7 +2958,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2986,7 +3001,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3000,10 +3015,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44853</v>
+        <v>46030</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3016,7 +3031,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3059,7 +3074,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3073,10 +3088,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45503</v>
+        <v>45793</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3088,13 +3103,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3137,7 +3147,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3151,10 +3161,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45504</v>
+        <v>44929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3166,13 +3176,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3215,7 +3220,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3229,10 +3234,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44691</v>
+        <v>45797</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3245,7 +3250,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3288,7 +3293,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45516</v>
+        <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3318,7 +3323,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3361,7 +3366,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3371,14 +3376,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45146</v>
+        <v>46034</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3391,7 +3396,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3434,7 +3439,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3448,10 +3453,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45103</v>
+        <v>46034</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3464,7 +3469,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>9.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3507,7 +3512,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3521,10 +3526,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45246</v>
+        <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3537,7 +3542,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3580,7 +3585,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3594,10 +3599,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45680</v>
+        <v>46036</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3653,7 +3658,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3667,10 +3672,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44854</v>
+        <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3683,7 +3688,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3726,7 +3731,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3740,10 +3745,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45099</v>
+        <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3799,7 +3804,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3809,14 +3814,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45177</v>
+        <v>46042</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3872,7 +3877,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3886,10 +3891,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45356</v>
+        <v>46042</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3902,7 +3907,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3945,7 +3950,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3959,10 +3964,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44846</v>
+        <v>45800</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4018,7 +4023,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4028,14 +4033,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45257</v>
+        <v>46044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4048,7 +4053,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4091,7 +4096,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45884</v>
+        <v>46044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4121,7 +4126,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4164,7 +4169,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4174,14 +4179,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45462</v>
+        <v>46044</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4237,7 +4242,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4251,10 +4256,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45532</v>
+        <v>46048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4267,7 +4272,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45517</v>
+        <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4339,13 +4344,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45672</v>
+        <v>45517</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4419,11 +4419,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45672</v>
+        <v>45799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4495,13 +4495,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4544,7 +4539,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4554,14 +4549,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45730</v>
+        <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4574,7 +4569,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4617,7 +4612,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44565</v>
+        <v>45799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4647,7 +4642,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4690,7 +4685,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4704,10 +4699,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44929</v>
+        <v>45799</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4720,7 +4715,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4780,7 +4775,7 @@
         <v>45905</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4836,7 +4831,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4846,14 +4841,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4866,7 +4861,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4909,7 +4904,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4923,10 +4918,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45909</v>
+        <v>45799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4939,7 +4934,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4999,7 +4994,7 @@
         <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5060,7 +5055,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5074,10 +5069,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45669</v>
+        <v>45912</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5090,7 +5085,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5133,7 +5128,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5147,10 +5142,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45357</v>
+        <v>45918</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5163,7 +5158,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5206,7 +5201,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5220,10 +5215,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45582</v>
+        <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5236,7 +5231,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5279,7 +5274,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5293,10 +5288,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45912</v>
+        <v>45918</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5309,7 +5304,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5352,7 +5347,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5366,10 +5361,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45608</v>
+        <v>46066</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5382,7 +5377,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5425,7 +5420,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5439,10 +5434,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45918</v>
+        <v>46065</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5498,7 +5493,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45918</v>
+        <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5528,7 +5523,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5571,7 +5566,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45918</v>
+        <v>46071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5601,7 +5596,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5644,7 +5639,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5658,10 +5653,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45581</v>
+        <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5717,7 +5712,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5731,10 +5726,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45807</v>
+        <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5747,7 +5742,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5790,7 +5785,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5804,10 +5799,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45713</v>
+        <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5820,7 +5815,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5863,7 +5858,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5877,10 +5872,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45713</v>
+        <v>45939</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5893,7 +5888,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5936,7 +5931,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5950,10 +5945,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45587</v>
+        <v>45951</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5966,7 +5961,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6004,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6023,10 +6018,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44970</v>
+        <v>45951</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6039,7 +6034,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6082,7 +6077,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6096,10 +6091,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45937</v>
+        <v>45951</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6112,7 +6107,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6150,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6169,10 +6164,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45937</v>
+        <v>45950</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6185,7 +6180,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6228,7 +6223,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6242,10 +6237,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45939</v>
+        <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6258,7 +6253,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6301,7 +6296,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6315,10 +6310,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45175</v>
+        <v>45957</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6331,7 +6326,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6374,7 +6369,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6388,10 +6383,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45950</v>
+        <v>45581</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6404,7 +6399,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6447,7 +6442,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6461,10 +6456,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45951</v>
+        <v>45246</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6477,7 +6472,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6520,7 +6515,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6534,10 +6529,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6550,7 +6545,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6593,7 +6588,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6607,10 +6602,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6623,7 +6618,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6666,7 +6661,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6680,10 +6675,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45463</v>
+        <v>45957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6696,7 +6691,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6739,7 +6734,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6753,10 +6748,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44935</v>
+        <v>45730</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6769,7 +6764,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6812,7 +6807,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6826,10 +6821,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45957</v>
+        <v>46121</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6842,7 +6837,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6885,7 +6880,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6899,10 +6894,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45957</v>
+        <v>45964</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6915,7 +6910,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>6.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6958,7 +6953,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6972,10 +6967,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46044</v>
+        <v>45965</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6988,7 +6983,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7031,7 +7026,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7045,10 +7040,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7061,7 +7056,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7104,7 +7099,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7118,10 +7113,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45957</v>
+        <v>46126</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7134,7 +7129,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7177,7 +7172,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7191,10 +7186,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45748</v>
+        <v>45974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7207,7 +7202,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7250,7 +7245,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7264,10 +7259,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45965</v>
+        <v>45974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7323,7 +7318,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7337,10 +7332,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45964</v>
+        <v>45975</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7353,7 +7348,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.7</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7396,7 +7391,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7410,10 +7405,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45799</v>
+        <v>45975</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7426,7 +7421,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7469,7 +7464,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7483,10 +7478,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45965</v>
+        <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7542,7 +7537,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7556,10 +7551,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45615</v>
+        <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7572,7 +7567,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7615,7 +7610,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7629,10 +7624,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7645,7 +7640,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7688,7 +7683,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7705,7 +7700,7 @@
         <v>45975</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7718,7 +7713,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7761,7 +7756,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7775,10 +7770,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7791,7 +7786,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7834,7 +7829,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7864,7 +7859,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7907,7 +7902,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7921,10 +7916,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7936,8 +7931,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7980,7 +7980,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,8 +8009,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8053,7 +8058,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8067,10 +8072,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45978</v>
+        <v>45516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8083,7 +8088,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8126,7 +8131,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8140,10 +8145,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45978</v>
+        <v>45516</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8156,7 +8161,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8199,7 +8204,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8213,10 +8218,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45978</v>
+        <v>45103</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8229,7 +8234,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8272,7 +8277,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8282,14 +8287,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45980</v>
+        <v>45177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8301,13 +8306,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45980</v>
+        <v>45669</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8452,13 +8452,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8501,7 +8496,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8511,14 +8506,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44581</v>
+        <v>45992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8531,7 +8526,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8574,7 +8569,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45218</v>
+        <v>45713</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8604,7 +8599,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8647,7 +8642,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8661,10 +8656,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45146</v>
+        <v>45995</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8677,7 +8672,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8720,7 +8715,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8734,10 +8729,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8750,7 +8745,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8793,7 +8788,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8807,10 +8802,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46149</v>
+        <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8823,7 +8818,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8866,7 +8861,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8880,10 +8875,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46149</v>
+        <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8896,7 +8891,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8939,7 +8934,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8953,10 +8948,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46148</v>
+        <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8969,7 +8964,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9012,7 +9007,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9022,14 +9017,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9042,7 +9037,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9085,7 +9080,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9099,10 +9094,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9115,7 +9110,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9158,7 +9153,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9172,10 +9167,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9188,7 +9183,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9231,7 +9226,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9241,14 +9236,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
         <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9261,7 +9256,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9304,7 +9299,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9314,14 +9309,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
         <v>46000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9334,7 +9329,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9377,7 +9372,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9394,7 +9389,7 @@
         <v>46000</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9407,7 +9402,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9450,7 +9445,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9464,10 +9459,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46000</v>
+        <v>45103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9480,7 +9475,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9523,7 +9518,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9540,7 +9535,7 @@
         <v>46000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9553,7 +9548,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9596,7 +9591,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9610,10 +9605,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46000</v>
+        <v>45146</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9626,7 +9621,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9669,7 +9664,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9679,14 +9674,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46000</v>
+        <v>45644</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9698,8 +9693,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9742,7 +9742,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46000</v>
+        <v>44853</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46000</v>
+        <v>44509</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9888,7 +9888,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45609</v>
+        <v>45807</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9975,10 +9975,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46000</v>
+        <v>45183</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10034,7 +10034,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45103</v>
+        <v>45799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45146</v>
+        <v>45680</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10180,7 +10180,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45730</v>
+        <v>46010</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10253,7 +10253,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46010</v>
+        <v>46044</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10340,10 +10340,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46013</v>
+        <v>45175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10355,13 +10355,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>21.4</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10404,7 +10399,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10414,14 +10409,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45139</v>
+        <v>45055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10434,7 +10429,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10477,7 +10472,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10491,10 +10486,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46161</v>
+        <v>45581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10507,7 +10502,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10550,7 +10545,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10564,10 +10559,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46078</v>
+        <v>45509</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10579,8 +10574,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10623,7 +10623,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46030</v>
+        <v>45106</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10696,7 +10696,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45275</v>
+        <v>45106</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10769,7 +10769,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10779,14 +10779,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45549</v>
+        <v>45827</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10842,7 +10842,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10856,10 +10856,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46034</v>
+        <v>46148</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45748</v>
+        <v>46149</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10988,7 +10988,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11002,10 +11002,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46034</v>
+        <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>9.1</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11061,7 +11061,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11075,10 +11075,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46036</v>
+        <v>45356</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11134,7 +11134,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11148,10 +11148,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46162</v>
+        <v>45835</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11163,13 +11163,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11212,7 +11207,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11226,10 +11221,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46042</v>
+        <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11241,8 +11236,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11285,7 +11285,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45106</v>
+        <v>45229</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11358,7 +11358,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11372,10 +11372,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46042</v>
+        <v>46078</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11431,7 +11431,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11441,14 +11441,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46044</v>
+        <v>46161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11518,10 +11518,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46044</v>
+        <v>46170</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11577,7 +11577,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11587,14 +11587,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46044</v>
+        <v>46175</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11606,8 +11606,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11650,7 +11655,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11664,10 +11669,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46048</v>
+        <v>46175</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11679,8 +11684,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11723,7 +11733,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11737,10 +11747,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46048</v>
+        <v>46175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11752,8 +11762,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11796,7 +11811,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11810,10 +11825,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44953</v>
+        <v>46175</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11825,8 +11840,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11869,7 +11889,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11883,10 +11903,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45737</v>
+        <v>46175</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11898,8 +11918,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11942,7 +11967,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11956,10 +11981,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45439</v>
+        <v>46176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11972,7 +11997,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12015,7 +12040,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12029,10 +12054,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46065</v>
+        <v>46176</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12045,7 +12070,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12088,7 +12113,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12102,10 +12127,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46170</v>
+        <v>45713</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12118,7 +12143,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12161,7 +12186,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12175,10 +12200,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46066</v>
+        <v>45146</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12191,7 +12216,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12234,7 +12259,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12248,10 +12273,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44501</v>
+        <v>45582</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12264,7 +12289,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>10.2</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12307,7 +12332,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12321,10 +12346,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46070</v>
+        <v>45118</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12337,7 +12362,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12380,7 +12405,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12394,10 +12419,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46071</v>
+        <v>45127</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12410,7 +12435,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12453,7 +12478,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12467,10 +12492,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45624</v>
+        <v>45580</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12482,8 +12507,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12526,7 +12556,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12540,10 +12570,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45609</v>
+        <v>45509</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12556,7 +12586,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12599,7 +12629,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12616,7 +12646,7 @@
         <v>45609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12629,7 +12659,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12672,7 +12702,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12686,10 +12716,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45098</v>
+        <v>45609</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12702,7 +12732,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12745,7 +12775,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12759,10 +12789,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46175</v>
+        <v>45713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12774,13 +12804,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12823,7 +12848,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12837,10 +12862,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46175</v>
+        <v>45439</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12850,11 +12875,6 @@
       <c r="G163" t="inlineStr">
         <is>
           <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -12901,7 +12921,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12915,10 +12935,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46175</v>
+        <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12930,13 +12950,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12979,7 +12994,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12993,10 +13008,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46175</v>
+        <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13008,13 +13023,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13057,7 +13067,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13071,10 +13081,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46176</v>
+        <v>45737</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13087,7 +13097,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13130,7 +13140,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13144,10 +13154,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46175</v>
+        <v>45098</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13159,13 +13169,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13208,7 +13213,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13222,10 +13227,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46176</v>
+        <v>46253</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13238,7 +13243,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13281,7 +13286,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13295,10 +13300,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44747</v>
+        <v>46210</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13311,7 +13316,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13354,7 +13359,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13368,10 +13373,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45509</v>
+        <v>45440</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13389,7 +13394,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13432,7 +13437,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13442,14 +13447,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45771</v>
+        <v>46253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13461,13 +13466,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13510,7 +13510,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13520,14 +13520,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46121</v>
+        <v>46253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13583,7 +13583,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46126</v>
+        <v>45231</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13656,7 +13656,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13670,10 +13670,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44987</v>
+        <v>46255</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13729,7 +13729,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45231</v>
+        <v>44581</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13802,7 +13802,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13816,10 +13816,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45509</v>
+        <v>46260</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13889,10 +13889,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46198</v>
+        <v>45188</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13948,7 +13948,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13962,10 +13962,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45508</v>
+        <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13977,13 +13977,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14026,7 +14021,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14040,10 +14035,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44509</v>
+        <v>45257</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14056,7 +14051,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14099,7 +14094,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14113,10 +14108,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45106</v>
+        <v>44854</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14129,7 +14124,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14172,7 +14167,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14186,10 +14181,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45118</v>
+        <v>45357</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14202,7 +14197,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14245,7 +14240,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14259,10 +14254,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45118</v>
+        <v>45771</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14274,8 +14269,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14332,10 +14332,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44979</v>
+        <v>46140</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14391,7 +14391,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14401,14 +14401,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45069</v>
+        <v>44509</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14464,7 +14464,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14474,14 +14474,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46253</v>
+        <v>46267</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14610,7 +14610,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14620,14 +14620,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46253</v>
+        <v>44747</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14683,7 +14683,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46210</v>
+        <v>44747</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44987</v>
+        <v>46274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14829,7 +14829,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46255</v>
+        <v>46274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14902,7 +14902,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45580</v>
+        <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14931,13 +14931,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14980,7 +14975,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14994,10 +14989,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45440</v>
+        <v>46273</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15009,13 +15004,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15058,7 +15048,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15072,10 +15062,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45390</v>
+        <v>45259</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15088,7 +15078,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15131,7 +15121,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15145,10 +15135,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46260</v>
+        <v>45549</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15161,7 +15151,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15204,7 +15194,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15218,10 +15208,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45713</v>
+        <v>46280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15234,7 +15224,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15277,7 +15267,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15287,14 +15277,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15306,8 +15296,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15350,7 +15345,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15364,10 +15359,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46140</v>
+        <v>46245</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15380,7 +15375,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15423,7 +15418,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15437,10 +15432,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44509</v>
+        <v>44691</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15453,7 +15448,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15496,7 +15491,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15506,14 +15501,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46268</v>
+        <v>45069</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15526,7 +15521,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15569,7 +15564,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15579,14 +15574,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45516</v>
+        <v>44571</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15599,7 +15594,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15642,7 +15637,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15656,10 +15651,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45581</v>
+        <v>45411</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15715,7 +15710,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15725,14 +15720,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45644</v>
+        <v>44935</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15744,13 +15739,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15793,7 +15783,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15807,10 +15797,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45259</v>
+        <v>45118</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15823,7 +15813,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15866,7 +15856,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15880,10 +15870,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46273</v>
+        <v>45508</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15895,8 +15885,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15939,7 +15934,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15953,10 +15948,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45474</v>
+        <v>45730</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15968,13 +15963,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16017,7 +16007,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16031,10 +16021,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46273</v>
+        <v>45624</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16047,7 +16037,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16090,7 +16080,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16104,10 +16094,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46274</v>
+        <v>44501</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16120,7 +16110,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.7</v>
+        <v>10.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16163,7 +16153,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16177,10 +16167,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45188</v>
+        <v>45463</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16193,7 +16183,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16236,7 +16226,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16250,10 +16240,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44747</v>
+        <v>45608</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16266,7 +16256,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16309,7 +16299,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16323,10 +16313,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45775</v>
+        <v>45275</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16339,7 +16329,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.8</v>
+        <v>6.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16382,7 +16372,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16396,10 +16386,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44816</v>
+        <v>45713</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16412,7 +16402,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16455,7 +16445,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16469,10 +16459,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46274</v>
+        <v>45713</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16485,7 +16475,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16528,7 +16518,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16538,14 +16528,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45713</v>
+        <v>45146</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16558,7 +16548,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16601,7 +16591,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16615,10 +16605,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45356</v>
+        <v>44987</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16631,7 +16621,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16674,7 +16664,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16688,10 +16678,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45183</v>
+        <v>45139</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16704,7 +16694,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16747,7 +16737,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16761,10 +16751,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45713</v>
+        <v>45615</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16777,7 +16767,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16820,7 +16810,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16834,10 +16824,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46280</v>
+        <v>44987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16850,7 +16840,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>6.9</v>
+        <v>3.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16893,7 +16883,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16907,10 +16897,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45118</v>
+        <v>45757</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16966,7 +16956,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16980,10 +16970,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45782</v>
+        <v>45775</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16996,7 +16986,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17039,7 +17029,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17053,10 +17043,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45782</v>
+        <v>45532</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17069,7 +17059,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17112,7 +17102,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17122,14 +17112,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46269</v>
+        <v>45532</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17141,13 +17131,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17190,7 +17175,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17204,10 +17189,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45187</v>
+        <v>45532</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17220,7 +17205,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17263,7 +17248,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17277,10 +17262,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45791</v>
+        <v>45474</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17298,7 +17283,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17341,7 +17326,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17355,10 +17340,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45791</v>
+        <v>44979</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17370,13 +17355,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17419,7 +17399,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17433,10 +17413,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45790</v>
+        <v>44953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17448,13 +17428,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17497,7 +17472,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17511,10 +17486,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45793</v>
+        <v>44747</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17527,7 +17502,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17570,7 +17545,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17584,10 +17559,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45792</v>
+        <v>45587</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17599,13 +17574,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17648,7 +17618,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17662,10 +17632,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45792</v>
+        <v>45748</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17678,7 +17648,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17721,7 +17691,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17735,10 +17705,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45797</v>
+        <v>45672</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17750,8 +17720,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17794,7 +17769,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17808,10 +17783,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45797</v>
+        <v>45672</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17823,8 +17798,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17867,7 +17847,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17881,10 +17861,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46245</v>
+        <v>45609</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17897,7 +17877,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17940,7 +17920,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17954,10 +17934,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45799</v>
+        <v>45118</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17970,7 +17950,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18013,7 +17993,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18027,10 +18007,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45799</v>
+        <v>45782</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18043,7 +18023,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18086,7 +18066,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18100,10 +18080,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45799</v>
+        <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18116,7 +18096,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18159,7 +18139,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18173,10 +18153,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45799</v>
+        <v>45790</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18188,8 +18168,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18232,7 +18217,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18246,10 +18231,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45799</v>
+        <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18261,8 +18246,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18305,7 +18295,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18319,10 +18309,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45800</v>
+        <v>45791</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18334,8 +18324,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18378,7 +18373,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18392,10 +18387,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45800</v>
+        <v>45187</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18408,7 +18403,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18451,7 +18446,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18461,14 +18456,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45827</v>
+        <v>45792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18480,8 +18475,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18524,7 +18524,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45835</v>
+        <v>45792</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18597,7 +18597,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18611,10 +18611,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45250</v>
+        <v>44559</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>31.7</v>
+        <v>60.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18675,7 +18675,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18689,10 +18689,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44559</v>
+        <v>44645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18704,13 +18704,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>60.7</v>
+        <v>15.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18753,7 +18748,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18767,10 +18762,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44645</v>
+        <v>45250</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18782,8 +18777,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>15.8</v>
+        <v>31.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18843,7 +18843,7 @@
         <v>45775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46070</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46114</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>45698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45237</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45642</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44816</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45390</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46013</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45503</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45884</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46030</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45793</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45797</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46034</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46034</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46036</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46042</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46042</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45800</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>46044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46044</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45517</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45799</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45905</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45909</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>45912</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>45918</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45918</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46066</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46065</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>46071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45939</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45951</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45951</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45951</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45950</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45957</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45581</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45246</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45730</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>46121</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45964</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45965</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46126</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45975</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45975</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45978</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45975</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45980</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45980</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45980</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45516</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>45103</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>45177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>45986</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45669</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>45713</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45995</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45996</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46000</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>46000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45146</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45644</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>44853</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44509</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45807</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>45183</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45680</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>46010</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>46044</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>45509</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45106</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45106</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45827</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>46148</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>46149</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45356</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45835</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45229</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>46078</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>46161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>46170</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>46175</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>46175</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>46175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>46175</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>46175</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>46176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>46176</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45713</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45146</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45582</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45118</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45127</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45580</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45509</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45609</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45439</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45737</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45098</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46253</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46210</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45440</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>46253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>46253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45231</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46255</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44581</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>46260</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45188</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45257</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>44854</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45357</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45771</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>46140</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>44509</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>46267</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>46268</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44747</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44747</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>46274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>46274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>46273</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45259</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45549</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>46280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>46269</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>46245</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44691</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45069</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44571</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45411</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44935</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45118</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45508</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45730</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45624</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>44501</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45463</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45608</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45275</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45713</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45713</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45146</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44987</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45139</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45615</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45757</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45775</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45532</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45532</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>45532</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45474</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>44979</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44747</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45587</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45748</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45672</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45672</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45609</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45118</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45782</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45790</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45791</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45187</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45792</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44559</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45250</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46070</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46114</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>45698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45237</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45642</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44816</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45390</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46013</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45503</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45884</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46030</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45793</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45797</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>46034</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46034</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46036</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46042</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>46042</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45800</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>46044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46044</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45517</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45799</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45905</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>45909</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>45912</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>45918</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45918</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46066</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46065</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>46071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45939</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45951</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45951</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45951</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45950</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45957</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45581</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45246</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45730</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>46121</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45964</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45965</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46126</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45975</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45975</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45978</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45975</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45980</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45980</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45980</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45516</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>45103</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>45177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>45986</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45669</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>45713</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45995</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45996</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46000</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>46000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45146</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45644</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>44853</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44509</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45807</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>45183</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45680</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>46010</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>46044</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>45509</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45106</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45106</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45827</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>46148</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>46149</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45356</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45835</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45229</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>46078</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>46161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>46170</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>46175</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>46175</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>46175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>46175</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>46175</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>46176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>46176</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45713</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45146</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45582</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45118</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45127</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45580</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45509</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45609</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45439</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45737</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45098</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46253</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46210</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45440</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>46253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>46253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45231</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46255</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44581</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>46260</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45188</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45257</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>44854</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45357</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45771</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>46140</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>44509</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>46267</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>46268</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44747</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44747</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>46274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>46274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>46273</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45259</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45549</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>46280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>46269</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>46245</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44691</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45069</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44571</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45411</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44935</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45118</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45508</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45730</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45624</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>44501</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45463</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45608</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45275</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45713</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45713</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45146</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44987</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45139</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45615</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45757</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45775</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45532</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45532</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>45532</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45474</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>44979</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44747</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45587</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45748</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45672</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45672</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45609</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45118</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45782</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45790</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45791</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45187</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45792</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44559</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45250</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46070</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46114</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>45698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 55173-2023</t>
+          <t>A 60033-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45237</v>
+        <v>45642</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1459,143 +1459,143 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55173-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45237</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Brunklöver</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 60033-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45642</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52536-2023</t>
+          <t>A 54793-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45218</v>
+        <v>45229</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38956-2022</t>
+          <t>A 16782-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44816</v>
+        <v>45411</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46434-2022</t>
+          <t>A 846-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44846</v>
+        <v>44571</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15674-2025</t>
+          <t>A 33319-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45748</v>
+        <v>45127</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13758-2024</t>
+          <t>A 28337-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45390</v>
+        <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 63447-2025</t>
+          <t>A 35737-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46013</v>
+        <v>45532</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,13 +2723,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>21.4</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2772,7 +2767,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31264-2024</t>
+          <t>A 35771-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2786,10 +2781,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45503</v>
+        <v>45532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2801,13 +2796,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2850,7 +2840,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31277-2024</t>
+          <t>A 20228-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2860,14 +2850,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45504</v>
+        <v>45055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2879,13 +2869,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2928,7 +2913,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38566-2025</t>
+          <t>A 31132-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2942,10 +2927,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45884</v>
+        <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2958,7 +2943,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3001,7 +2986,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 862-2026</t>
+          <t>A 35349-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3015,10 +3000,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46030</v>
+        <v>45146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3031,7 +3016,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3074,7 +3059,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23776-2025</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3088,10 +3073,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45793</v>
+        <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3104,7 +3089,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3147,7 +3132,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1058-2023</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3161,10 +3146,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44929</v>
+        <v>45791</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3176,8 +3161,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3220,7 +3210,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24346-2025</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3234,10 +3224,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45797</v>
+        <v>45791</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3249,8 +3239,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3293,7 +3288,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24342-2025</t>
+          <t>A 22900-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3307,10 +3302,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45797</v>
+        <v>45790</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3322,8 +3317,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1633-2026</t>
+          <t>A 23776-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46034</v>
+        <v>45793</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1614-2026</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46034</v>
+        <v>45792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3468,8 +3468,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>9.1</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3512,7 +3517,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25206-2025</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3526,10 +3531,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45800</v>
+        <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3542,7 +3547,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3585,7 +3590,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2072-2026</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3599,10 +3604,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46036</v>
+        <v>45884</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3615,7 +3620,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3658,7 +3663,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 426-2022</t>
+          <t>A 24342-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3672,10 +3677,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44565</v>
+        <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3688,7 +3693,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3731,7 +3736,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24756-2025</t>
+          <t>A 24346-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45799</v>
+        <v>45797</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3761,7 +3766,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3804,7 +3809,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3540-2026</t>
+          <t>A 17414-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3818,10 +3823,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46042</v>
+        <v>45757</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3877,7 +3882,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3538-2026</t>
+          <t>A 426-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3891,10 +3896,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46042</v>
+        <v>44565</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3907,7 +3912,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3950,7 +3955,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 25205-2025</t>
+          <t>A 24756-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3964,10 +3969,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45800</v>
+        <v>45799</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3980,7 +3985,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4023,7 +4028,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4081-2026</t>
+          <t>A 24812-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4033,14 +4038,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46044</v>
+        <v>45799</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4053,7 +4058,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4096,7 +4101,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4108-2026</t>
+          <t>A 24792-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4110,10 +4115,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46044</v>
+        <v>45799</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4126,7 +4131,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4169,7 +4174,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4090-2026</t>
+          <t>A 24868-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4179,14 +4184,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46044</v>
+        <v>45799</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4199,7 +4204,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4242,7 +4247,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4870-2026</t>
+          <t>A 24856-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4256,10 +4261,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46048</v>
+        <v>45799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4272,7 +4277,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4315,7 +4320,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4685-2026</t>
+          <t>A 47976-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4329,10 +4334,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46048</v>
+        <v>44853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4345,7 +4350,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4388,7 +4393,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32956-2024</t>
+          <t>A 31264-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4402,10 +4407,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45517</v>
+        <v>45503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4423,7 +4428,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4466,7 +4471,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24868-2025</t>
+          <t>A 31277-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4480,10 +4485,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45799</v>
+        <v>45504</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4495,8 +4500,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4539,7 +4549,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42902-2025</t>
+          <t>A 19100-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4549,14 +4559,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45908</v>
+        <v>44691</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4569,7 +4579,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4612,7 +4622,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24812-2025</t>
+          <t>A 25205-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4626,10 +4636,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4642,7 +4652,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4685,7 +4695,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24856-2025</t>
+          <t>A 25206-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4699,10 +4709,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4715,7 +4725,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4758,7 +4768,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42584-2025</t>
+          <t>A 63160-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4772,10 +4782,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45905</v>
+        <v>46010</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4788,7 +4798,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4831,7 +4841,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42990-2025</t>
+          <t>A 32809-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4845,10 +4855,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45909</v>
+        <v>45516</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4861,7 +4871,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4904,7 +4914,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24792-2025</t>
+          <t>A 42584-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4918,10 +4928,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45799</v>
+        <v>45905</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4934,7 +4944,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4977,7 +4987,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43030-2025</t>
+          <t>A 42902-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4987,14 +4997,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45909</v>
+        <v>45908</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5006,13 +5016,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5055,7 +5060,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43685-2025</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5069,10 +5074,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45912</v>
+        <v>46013</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5084,8 +5089,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>21.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5128,7 +5138,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44832-2025</t>
+          <t>A 43030-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5142,10 +5152,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45918</v>
+        <v>45909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5157,8 +5167,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5201,7 +5216,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44975-2025</t>
+          <t>A 35354-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5211,14 +5226,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45918</v>
+        <v>45146</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5231,7 +5246,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5274,7 +5289,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44895-2025</t>
+          <t>A 28615-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5288,10 +5303,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45918</v>
+        <v>45103</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5304,7 +5319,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5347,7 +5362,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8697-2026</t>
+          <t>A 43685-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5361,10 +5376,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46066</v>
+        <v>45912</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5377,7 +5392,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5420,7 +5435,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8516-2026</t>
+          <t>A 44975-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5434,10 +5449,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46065</v>
+        <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5450,7 +5465,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5493,7 +5508,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9250-2026</t>
+          <t>A 44832-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5507,10 +5522,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46070</v>
+        <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5523,7 +5538,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5566,7 +5581,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9525-2026</t>
+          <t>A 44895-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5580,10 +5595,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46071</v>
+        <v>45918</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5596,7 +5611,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5639,7 +5654,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7871-2023</t>
+          <t>A 30163-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5649,14 +5664,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44970</v>
+        <v>45827</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5669,7 +5684,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5712,7 +5727,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48859-2025</t>
+          <t>A 57777-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5726,10 +5741,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45937</v>
+        <v>45246</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5742,7 +5757,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5785,7 +5800,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48886-2025</t>
+          <t>A 31986-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5799,10 +5814,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45937</v>
+        <v>45835</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5815,7 +5830,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5858,7 +5873,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49520-2025</t>
+          <t>A 48859-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5872,10 +5887,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45939</v>
+        <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5888,7 +5903,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5931,7 +5946,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51605-2025</t>
+          <t>A 48886-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5945,10 +5960,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45951</v>
+        <v>45937</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5961,7 +5976,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6004,7 +6019,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51737-2025</t>
+          <t>A 49520-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6018,10 +6033,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45951</v>
+        <v>45939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6034,7 +6049,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6077,7 +6092,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 51722-2025</t>
+          <t>A 51553-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6091,10 +6106,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6107,7 +6122,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6150,7 +6165,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51553-2025</t>
+          <t>A 51722-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6164,10 +6179,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6180,7 +6195,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6223,7 +6238,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9026-2024</t>
+          <t>A 51605-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6237,10 +6252,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45356</v>
+        <v>45951</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6253,7 +6268,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6296,7 +6311,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52842-2025</t>
+          <t>A 51737-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6310,10 +6325,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45957</v>
+        <v>45951</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6326,7 +6341,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6369,7 +6384,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46212-2024</t>
+          <t>A 3584-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6383,10 +6398,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45581</v>
+        <v>45680</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6399,7 +6414,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6442,7 +6457,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 57777-2023</t>
+          <t>A 52835-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6456,10 +6471,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45246</v>
+        <v>45957</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6472,7 +6487,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6515,7 +6530,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52820-2025</t>
+          <t>A 52845-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6532,7 +6547,7 @@
         <v>45957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6545,7 +6560,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6588,7 +6603,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52845-2025</t>
+          <t>A 862-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6602,10 +6617,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45957</v>
+        <v>46030</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6618,7 +6633,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6661,7 +6676,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52835-2025</t>
+          <t>A 52842-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6678,7 +6693,7 @@
         <v>45957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6691,7 +6706,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6734,7 +6749,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12410-2025</t>
+          <t>A 30221-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6748,10 +6763,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45730</v>
+        <v>45099</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6764,7 +6779,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6807,7 +6822,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17687-2026</t>
+          <t>A 52820-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6821,10 +6836,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46121</v>
+        <v>45957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6837,7 +6852,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6880,7 +6895,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54243-2025</t>
+          <t>A 54570-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6894,10 +6909,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6910,7 +6925,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.7</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6953,7 +6968,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54562-2025</t>
+          <t>A 54243-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6967,10 +6982,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45965</v>
+        <v>45964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6983,7 +6998,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7026,7 +7041,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54570-2025</t>
+          <t>A 54562-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7043,7 +7058,7 @@
         <v>45965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7056,7 +7071,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7099,7 +7114,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18233-2026</t>
+          <t>A 47771-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7113,10 +7128,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46126</v>
+        <v>44854</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7129,7 +7144,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7172,7 +7187,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56320-2025</t>
+          <t>A 1633-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7186,10 +7201,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45974</v>
+        <v>46034</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7202,7 +7217,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7245,7 +7260,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56329-2025</t>
+          <t>A 25347-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7259,10 +7274,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45974</v>
+        <v>45462</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7275,7 +7290,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7318,7 +7333,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56553-2025</t>
+          <t>A 9026-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7332,10 +7347,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45975</v>
+        <v>45356</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7348,7 +7363,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7391,7 +7406,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56513-2025</t>
+          <t>A 1614-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7405,10 +7420,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45975</v>
+        <v>46034</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7421,7 +7436,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7464,7 +7479,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56835-2025</t>
+          <t>A 2072-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7478,10 +7493,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45978</v>
+        <v>46036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7494,7 +7509,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7537,7 +7552,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56966-2025</t>
+          <t>A 42141-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7547,14 +7562,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45978</v>
+        <v>45177</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7567,7 +7582,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7610,7 +7625,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56831-2025</t>
+          <t>A 56320-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7624,10 +7639,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45978</v>
+        <v>45974</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7640,7 +7655,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7683,7 +7698,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 56622-2025</t>
+          <t>A 56513-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7700,7 +7715,7 @@
         <v>45975</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7713,7 +7728,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7756,7 +7771,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56833-2025</t>
+          <t>A 56622-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7770,10 +7785,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45978</v>
+        <v>45975</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7786,7 +7801,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7829,7 +7844,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57347-2025</t>
+          <t>A 56553-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7843,10 +7858,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45980</v>
+        <v>45975</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7859,7 +7874,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7902,7 +7917,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 57448-2025</t>
+          <t>A 56329-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7916,10 +7931,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45980</v>
+        <v>45974</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7931,13 +7946,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7980,7 +7990,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57424-2025</t>
+          <t>A 59771-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7994,10 +8004,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45980</v>
+        <v>45257</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,13 +8019,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8058,7 +8063,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32792-2024</t>
+          <t>A 56831-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8072,10 +8077,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45516</v>
+        <v>45978</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8088,7 +8093,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8131,7 +8136,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32809-2024</t>
+          <t>A 3540-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8145,10 +8150,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45516</v>
+        <v>46042</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8161,7 +8166,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8204,7 +8209,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28615-2023</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8218,10 +8223,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45103</v>
+        <v>44846</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8234,7 +8239,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8277,7 +8282,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42141-2023</t>
+          <t>A 56833-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8287,14 +8292,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45177</v>
+        <v>45978</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8307,7 +8312,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8350,7 +8355,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58637-2025</t>
+          <t>A 56835-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8364,10 +8369,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45986</v>
+        <v>45978</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8380,7 +8385,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8423,7 +8428,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1438-2025</t>
+          <t>A 56966-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8437,10 +8442,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45669</v>
+        <v>45978</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8453,7 +8458,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8496,7 +8501,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59867-2025</t>
+          <t>A 3538-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8506,14 +8511,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45992</v>
+        <v>46042</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8526,7 +8531,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8569,7 +8574,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 8935-2025</t>
+          <t>A 57448-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8583,10 +8588,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45713</v>
+        <v>45980</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8598,8 +8603,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8642,7 +8652,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 60533-2025</t>
+          <t>A 57347-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8656,10 +8666,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45995</v>
+        <v>45980</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8672,7 +8682,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8715,7 +8725,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 60619-2025</t>
+          <t>A 57424-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8729,10 +8739,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45996</v>
+        <v>45980</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8744,8 +8754,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8788,7 +8803,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61176-2025</t>
+          <t>A 4081-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8798,14 +8813,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8818,7 +8833,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.300000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8861,7 +8876,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61182-2025</t>
+          <t>A 4108-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8875,10 +8890,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8891,7 +8906,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8934,7 +8949,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61204-2025</t>
+          <t>A 4090-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8944,14 +8959,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8964,7 +8979,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9007,7 +9022,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61118-2025</t>
+          <t>A 58637-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9021,10 +9036,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46000</v>
+        <v>45986</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9037,7 +9052,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9080,7 +9095,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61127-2025</t>
+          <t>A 4685-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9094,10 +9109,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46000</v>
+        <v>46048</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9110,7 +9125,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9153,7 +9168,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61216-2025</t>
+          <t>A 4870-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9167,10 +9182,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46000</v>
+        <v>46048</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9183,7 +9198,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9226,7 +9241,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61221-2025</t>
+          <t>A 35755-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9236,14 +9251,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46000</v>
+        <v>45532</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9256,7 +9271,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9299,7 +9314,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61142-2025</t>
+          <t>A 32956-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9313,10 +9328,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46000</v>
+        <v>45517</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9328,8 +9343,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9372,7 +9392,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61155-2025</t>
+          <t>A 2018-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9386,10 +9406,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46000</v>
+        <v>45672</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9401,8 +9421,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9445,7 +9470,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 2020-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9459,10 +9484,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45103</v>
+        <v>45672</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9474,8 +9499,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9518,7 +9548,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61158-2025</t>
+          <t>A 12425-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9532,10 +9562,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46000</v>
+        <v>45730</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9548,7 +9578,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9591,7 +9621,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 59867-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9601,14 +9631,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45146</v>
+        <v>45992</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9621,7 +9651,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.4</v>
+        <v>0.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9664,7 +9694,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 60640-2024</t>
+          <t>A 60533-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9674,14 +9704,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45644</v>
+        <v>45995</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9693,13 +9723,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9742,7 +9767,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 47976-2022</t>
+          <t>A 60619-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9756,10 +9781,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44853</v>
+        <v>45996</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9772,7 +9797,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9815,7 +9840,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 63981-2021</t>
+          <t>A 61176-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9829,10 +9854,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44509</v>
+        <v>46000</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9845,7 +9870,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9888,7 +9913,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26576-2025</t>
+          <t>A 61221-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9898,14 +9923,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45807</v>
+        <v>46000</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9918,7 +9943,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9961,7 +9986,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 44319-2023</t>
+          <t>A 61216-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9975,10 +10000,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45183</v>
+        <v>46000</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9991,7 +10016,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10034,7 +10059,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 24805-2025</t>
+          <t>A 61142-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10048,10 +10073,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45799</v>
+        <v>46000</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10064,7 +10089,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10107,7 +10132,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3584-2025</t>
+          <t>A 61155-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10121,10 +10146,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45680</v>
+        <v>46000</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10137,7 +10162,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10180,7 +10205,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 63160-2025</t>
+          <t>A 61158-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10194,10 +10219,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10210,7 +10235,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10253,7 +10278,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 4109-2026</t>
+          <t>A 61182-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10267,10 +10292,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46044</v>
+        <v>46000</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10283,7 +10308,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10326,7 +10351,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 42317-2023</t>
+          <t>A 61204-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10340,10 +10365,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45175</v>
+        <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10356,7 +10381,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10399,7 +10424,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 61127-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10409,14 +10434,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45055</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10472,7 +10497,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46195-2024</t>
+          <t>A 1058-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10486,10 +10511,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45581</v>
+        <v>44929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10502,7 +10527,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10545,7 +10570,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31839-2024</t>
+          <t>A 61118-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10559,10 +10584,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45509</v>
+        <v>46000</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10574,13 +10599,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10623,7 +10643,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 29476-2023</t>
+          <t>A 1438-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10637,10 +10657,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45106</v>
+        <v>45669</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10653,7 +10673,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10696,7 +10716,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 29485-2023</t>
+          <t>A 8993-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10710,10 +10730,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45106</v>
+        <v>45357</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10726,7 +10746,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10769,7 +10789,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30163-2025</t>
+          <t>A 46501-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10779,14 +10799,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45827</v>
+        <v>45582</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10799,7 +10819,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10842,7 +10862,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21567-2026</t>
+          <t>A 8516-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10856,10 +10876,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46148</v>
+        <v>46065</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10872,7 +10892,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10915,7 +10935,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21598-2026</t>
+          <t>A 52255-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10929,10 +10949,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46149</v>
+        <v>45608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10945,7 +10965,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10988,7 +11008,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21597-2026</t>
+          <t>A 8697-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11002,10 +11022,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46149</v>
+        <v>46066</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11018,7 +11038,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11061,7 +11081,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 9039-2024</t>
+          <t>A 9250-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11075,10 +11095,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45356</v>
+        <v>46070</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11091,7 +11111,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11134,7 +11154,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31986-2025</t>
+          <t>A 9525-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11148,10 +11168,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45835</v>
+        <v>46071</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11164,7 +11184,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11207,7 +11227,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23208-2026</t>
+          <t>A 8935-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11221,10 +11241,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46162</v>
+        <v>45713</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11236,13 +11256,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11285,7 +11300,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 8939-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11299,10 +11314,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45229</v>
+        <v>45713</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11315,7 +11330,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11358,7 +11373,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 10761-2026</t>
+          <t>A 47472-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11372,10 +11387,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46078</v>
+        <v>45587</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11388,7 +11403,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11431,7 +11446,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23019-2026</t>
+          <t>A 7871-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11445,10 +11460,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46161</v>
+        <v>44970</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11461,7 +11476,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11504,7 +11519,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24474-2026</t>
+          <t>A 25453-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11518,10 +11533,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46170</v>
+        <v>45463</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11534,7 +11549,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11577,7 +11592,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 25127-2026</t>
+          <t>A 1006-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11591,10 +11606,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46175</v>
+        <v>44935</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11606,13 +11621,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11655,7 +11665,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 25139-2026</t>
+          <t>A 15678-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11669,10 +11679,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46175</v>
+        <v>45748</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11684,13 +11694,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11733,7 +11738,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 25216-2026</t>
+          <t>A 53783-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11747,10 +11752,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46175</v>
+        <v>45615</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11762,13 +11767,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11811,7 +11811,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 25124-2026</t>
+          <t>A 17687-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46175</v>
+        <v>46121</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11840,13 +11840,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11889,7 +11884,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25112-2026</t>
+          <t>A 18233-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11903,10 +11898,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46175</v>
+        <v>46126</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11918,13 +11913,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11967,7 +11957,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 25274-2026</t>
+          <t>A 2933-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11981,10 +11971,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46176</v>
+        <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11997,7 +11987,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12040,7 +12030,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25273-2026</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12054,10 +12044,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46176</v>
+        <v>45218</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12070,7 +12060,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12113,7 +12103,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 8939-2025</t>
+          <t>A 35360-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12127,10 +12117,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45713</v>
+        <v>45146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12143,7 +12133,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12186,7 +12176,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35360-2023</t>
+          <t>A 52536-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12200,10 +12190,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45146</v>
+        <v>45609</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12216,7 +12206,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12259,7 +12249,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 46501-2024</t>
+          <t>A 12410-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12273,10 +12263,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45582</v>
+        <v>45730</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12289,7 +12279,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12332,7 +12322,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 31867-2023</t>
+          <t>A 46195-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12346,10 +12336,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45118</v>
+        <v>45581</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12405,7 +12395,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 26576-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12419,10 +12409,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45127</v>
+        <v>45807</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12435,7 +12425,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12478,7 +12468,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 45899-2024</t>
+          <t>A 42317-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12492,10 +12482,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45580</v>
+        <v>45175</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12507,13 +12497,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12556,7 +12541,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 31817-2024</t>
+          <t>A 34760-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12570,10 +12555,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45509</v>
+        <v>45139</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12586,7 +12571,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12629,7 +12614,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 52531-2024</t>
+          <t>A 4109-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12643,10 +12628,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45609</v>
+        <v>46044</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12659,7 +12644,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12702,7 +12687,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 52533-2024</t>
+          <t>A 24805-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12716,10 +12701,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45609</v>
+        <v>45799</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12732,7 +12717,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12775,7 +12760,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 8940-2025</t>
+          <t>A 63817-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12789,10 +12774,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45713</v>
+        <v>45275</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12805,7 +12790,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>6.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12848,7 +12833,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 21041-2024</t>
+          <t>A 39220-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12862,10 +12847,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45439</v>
+        <v>45549</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12878,7 +12863,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12921,7 +12906,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 25347-2024</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12935,10 +12920,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45462</v>
+        <v>45748</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12951,7 +12936,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12994,7 +12979,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28752-2026</t>
+          <t>A 29485-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13008,10 +12993,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46198</v>
+        <v>45106</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13024,7 +13009,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13067,7 +13052,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13762-2025</t>
+          <t>A 21597-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13081,10 +13066,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45737</v>
+        <v>46149</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13097,7 +13082,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13140,7 +13125,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 29573-2023</t>
+          <t>A 21598-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13154,10 +13139,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45098</v>
+        <v>46149</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13170,7 +13155,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13213,7 +13198,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 34204-2026</t>
+          <t>A 21567-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13227,10 +13212,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46253</v>
+        <v>46148</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13243,7 +13228,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13286,7 +13271,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 30607-2026</t>
+          <t>A 4676-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13300,10 +13285,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46210</v>
+        <v>44953</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13316,7 +13301,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13359,7 +13344,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21135-2024</t>
+          <t>A 13762-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13373,10 +13358,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45440</v>
+        <v>45737</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13388,13 +13373,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13437,7 +13417,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 34180-2026</t>
+          <t>A 21041-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13447,14 +13427,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46253</v>
+        <v>45439</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13467,7 +13447,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13510,7 +13490,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34196-2026</t>
+          <t>A 62553-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13520,14 +13500,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46253</v>
+        <v>44501</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13540,7 +13520,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13583,7 +13563,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 55444-2023</t>
+          <t>A 23019-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13597,10 +13577,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45231</v>
+        <v>46161</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13613,7 +13593,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13656,7 +13636,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 34499-2026</t>
+          <t>A 10761-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13670,10 +13650,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46255</v>
+        <v>46078</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13686,7 +13666,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13729,7 +13709,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 2933-2022</t>
+          <t>A 23208-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13743,10 +13723,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44581</v>
+        <v>46162</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13758,8 +13738,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13802,7 +13787,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35196-2026</t>
+          <t>A 56258-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13816,10 +13801,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46260</v>
+        <v>45624</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13832,7 +13817,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13875,7 +13860,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 44295-2023</t>
+          <t>A 52531-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13889,10 +13874,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45188</v>
+        <v>45609</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13905,7 +13890,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13948,7 +13933,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30221-2023</t>
+          <t>A 52533-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13962,10 +13947,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45099</v>
+        <v>45609</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13978,7 +13963,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14021,7 +14006,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 59771-2023</t>
+          <t>A 29573-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14035,10 +14020,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45257</v>
+        <v>45098</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14051,7 +14036,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14094,7 +14079,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 47771-2022</t>
+          <t>A 28347-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14108,10 +14093,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44854</v>
+        <v>44747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14124,7 +14109,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14167,7 +14152,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 8993-2024</t>
+          <t>A 24474-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14181,10 +14166,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45357</v>
+        <v>46170</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14197,7 +14182,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14240,7 +14225,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 19734-2025</t>
+          <t>A 31839-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14254,10 +14239,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45771</v>
+        <v>45509</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14275,7 +14260,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14318,7 +14303,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20577-2026</t>
+          <t>A 19734-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14332,10 +14317,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46140</v>
+        <v>45771</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14347,8 +14332,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14391,7 +14381,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 63980-2021</t>
+          <t>A 25124-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14405,10 +14395,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44509</v>
+        <v>46175</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14420,8 +14410,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14464,7 +14459,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36081-2026</t>
+          <t>A 25112-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14478,10 +14473,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46267</v>
+        <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14493,8 +14488,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 36317-2026</t>
+          <t>A 25127-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46268</v>
+        <v>46175</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14566,8 +14566,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14610,7 +14615,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28367-2022</t>
+          <t>A 25216-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14624,10 +14629,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44747</v>
+        <v>46175</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14639,8 +14644,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14683,7 +14693,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 28347-2022</t>
+          <t>A 25273-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14697,10 +14707,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44747</v>
+        <v>46176</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14713,7 +14723,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14756,7 +14766,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37118-2026</t>
+          <t>A 25139-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14770,10 +14780,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46274</v>
+        <v>46175</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14785,8 +14795,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14829,7 +14844,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37123-2026</t>
+          <t>A 25274-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14843,10 +14858,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46274</v>
+        <v>46176</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14859,7 +14874,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14902,7 +14917,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36921-2026</t>
+          <t>A 10533-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14916,10 +14931,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46273</v>
+        <v>44987</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14932,7 +14947,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14975,7 +14990,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36936-2026</t>
+          <t>A 55444-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14989,10 +15004,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46273</v>
+        <v>45231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15005,7 +15020,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15048,7 +15063,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 60557-2023</t>
+          <t>A 31817-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15062,10 +15077,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45259</v>
+        <v>45509</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15078,7 +15093,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15121,7 +15136,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 39220-2024</t>
+          <t>A 31699-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15135,10 +15150,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45549</v>
+        <v>45508</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15150,8 +15165,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15194,7 +15214,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 37983-2026</t>
+          <t>A 63981-2021</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15208,10 +15228,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46280</v>
+        <v>44509</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15224,7 +15244,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15267,7 +15287,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 36560-2026</t>
+          <t>A 28752-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15277,14 +15297,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46269</v>
+        <v>46198</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15296,13 +15316,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15345,7 +15360,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 33038-2026</t>
+          <t>A 29476-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15359,10 +15374,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46245</v>
+        <v>45106</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15375,7 +15390,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15418,7 +15433,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 19100-2022</t>
+          <t>A 31867-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15432,10 +15447,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44691</v>
+        <v>45118</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15491,7 +15506,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 22193-2023</t>
+          <t>A 31869-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15501,14 +15516,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45069</v>
+        <v>45118</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15521,7 +15536,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15564,7 +15579,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 9086-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15574,14 +15589,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44571</v>
+        <v>44979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15594,7 +15609,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15637,7 +15652,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 22193-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15647,14 +15662,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45411</v>
+        <v>45069</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15667,7 +15682,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15710,7 +15725,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 1006-2023</t>
+          <t>A 10440-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15724,10 +15739,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44935</v>
+        <v>44987</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15740,7 +15755,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15783,7 +15798,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 31869-2023</t>
+          <t>A 34180-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15793,14 +15808,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45118</v>
+        <v>46253</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15813,7 +15828,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15856,7 +15871,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31699-2024</t>
+          <t>A 34204-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15870,10 +15885,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45508</v>
+        <v>46253</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15885,13 +15900,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15934,7 +15944,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12425-2025</t>
+          <t>A 34196-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15944,14 +15954,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45730</v>
+        <v>46253</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15964,7 +15974,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16007,7 +16017,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 56258-2024</t>
+          <t>A 45899-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16021,10 +16031,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45624</v>
+        <v>45580</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16036,8 +16046,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16080,7 +16095,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 62553-2021</t>
+          <t>A 30607-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16094,10 +16109,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44501</v>
+        <v>46210</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16110,7 +16125,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>10.2</v>
+        <v>2.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16153,7 +16168,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25453-2024</t>
+          <t>A 21135-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16167,10 +16182,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45463</v>
+        <v>45440</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16182,8 +16197,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16226,7 +16246,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 52255-2024</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16240,10 +16260,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45608</v>
+        <v>45390</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16256,7 +16276,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16299,7 +16319,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 63817-2023</t>
+          <t>A 34499-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16313,10 +16333,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45275</v>
+        <v>46255</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16329,7 +16349,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16372,7 +16392,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 8937-2025</t>
+          <t>A 8938-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16389,7 +16409,7 @@
         <v>45713</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16402,7 +16422,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16445,7 +16465,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 8938-2025</t>
+          <t>A 35196-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16459,10 +16479,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45713</v>
+        <v>46260</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16475,7 +16495,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16518,7 +16538,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 35354-2023</t>
+          <t>A 32792-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16528,14 +16548,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45146</v>
+        <v>45516</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16548,7 +16568,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16591,7 +16611,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 10533-2023</t>
+          <t>A 36081-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16605,10 +16625,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44987</v>
+        <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16621,7 +16641,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16664,7 +16684,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 34760-2023</t>
+          <t>A 20577-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16678,10 +16698,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45139</v>
+        <v>46140</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16694,7 +16714,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16737,7 +16757,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 53783-2024</t>
+          <t>A 46212-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16751,10 +16771,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45615</v>
+        <v>45581</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16767,7 +16787,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16810,7 +16830,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10440-2023</t>
+          <t>A 60640-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16820,14 +16840,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44987</v>
+        <v>45644</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16839,8 +16859,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16883,7 +16908,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 17414-2025</t>
+          <t>A 60557-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16897,10 +16922,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45757</v>
+        <v>45259</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16913,7 +16938,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16956,7 +16981,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 20432-2025</t>
+          <t>A 63980-2021</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16970,10 +16995,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45775</v>
+        <v>44509</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16986,7 +17011,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17029,7 +17054,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 36317-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17043,10 +17068,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45532</v>
+        <v>46268</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17059,7 +17084,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17102,7 +17127,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 35755-2024</t>
+          <t>A 27530-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17116,10 +17141,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45532</v>
+        <v>45474</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17131,8 +17156,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17175,7 +17205,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 44295-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17189,10 +17219,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45532</v>
+        <v>45188</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17205,7 +17235,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17248,7 +17278,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 27530-2024</t>
+          <t>A 28367-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17262,10 +17292,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45474</v>
+        <v>44747</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17277,13 +17307,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17326,7 +17351,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 9086-2023</t>
+          <t>A 36921-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17340,10 +17365,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44979</v>
+        <v>46273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17356,7 +17381,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17399,7 +17424,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 4676-2023</t>
+          <t>A 20432-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17413,10 +17438,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44953</v>
+        <v>45775</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17429,7 +17454,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17472,7 +17497,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17486,10 +17511,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44747</v>
+        <v>44816</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17502,7 +17527,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17545,7 +17570,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 47472-2024</t>
+          <t>A 36936-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17559,10 +17584,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45587</v>
+        <v>46273</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17575,7 +17600,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17618,7 +17643,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 15678-2025</t>
+          <t>A 37118-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17632,10 +17657,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45748</v>
+        <v>46274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17648,7 +17673,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17691,7 +17716,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 2018-2025</t>
+          <t>A 8940-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17705,10 +17730,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45672</v>
+        <v>45713</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17720,13 +17745,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17769,7 +17789,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 2020-2025</t>
+          <t>A 9039-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17783,10 +17803,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45672</v>
+        <v>45356</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17798,13 +17818,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17847,7 +17862,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 52536-2024</t>
+          <t>A 44319-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17861,10 +17876,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45609</v>
+        <v>45183</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17877,7 +17892,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17920,7 +17935,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31865-2023</t>
+          <t>A 37123-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17934,10 +17949,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45118</v>
+        <v>46274</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -17950,7 +17965,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -17993,7 +18008,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 21437-2025</t>
+          <t>A 8937-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18007,10 +18022,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45782</v>
+        <v>45713</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18023,7 +18038,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18066,7 +18081,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21361-2025</t>
+          <t>A 37983-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18080,10 +18095,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45782</v>
+        <v>46280</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18096,7 +18111,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18139,7 +18154,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 22900-2025</t>
+          <t>A 31865-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18153,10 +18168,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45790</v>
+        <v>45118</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18168,13 +18183,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18217,7 +18227,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 23205-2025</t>
+          <t>A 21437-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18231,10 +18241,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45791</v>
+        <v>45782</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18246,13 +18256,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18295,7 +18300,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 21361-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18309,10 +18314,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45791</v>
+        <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18324,13 +18329,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18373,7 +18373,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 36560-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18383,14 +18383,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45187</v>
+        <v>46269</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18402,8 +18402,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18446,7 +18451,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 23453-2025</t>
+          <t>A 33038-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18460,10 +18465,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45792</v>
+        <v>46245</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18475,13 +18480,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18524,7 +18524,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 23465-2025</t>
+          <t>A 42990-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45792</v>
+        <v>45909</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18597,7 +18597,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 25-2022</t>
+          <t>S 4180-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18611,10 +18611,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44559</v>
+        <v>45250</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>60.7</v>
+        <v>31.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18675,7 +18675,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 1611-2022</t>
+          <t>S 25-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18689,10 +18689,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44645</v>
+        <v>44559</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18704,8 +18704,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>15.8</v>
+        <v>60.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18748,7 +18753,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 4180-2023</t>
+          <t>S 1611-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18762,10 +18767,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45250</v>
+        <v>44645</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18777,13 +18782,8 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>31.7</v>
+        <v>15.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18843,7 +18843,7 @@
         <v>45775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46070</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46073</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46114</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>

--- a/Översikt VÄNNÄS.xlsx
+++ b/Översikt VÄNNÄS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE248"/>
+  <dimension ref="A1:AE251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45796</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>46146</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45435</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45799</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>45698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60033-2024</t>
+          <t>A 55173-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45642</v>
+        <v>45237</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1419,17 +1419,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1459,143 +1459,143 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 60033-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VÄNNÄS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Ögonpyrola</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 60033-2024 artfynd.xlsx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 60033-2024 karta.png", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 60033-2024 georefererad karta.tif", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 60033-2024 FSC-klagomål.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 60033-2024 FSC-klagomål mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 60033-2024 tillsynsbegäran.docx", "A 60033-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 60033-2024 tillsynsbegäran mail.docx", "A 60033-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55173-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45237</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VÄNNÄS</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/artfynd/A 55173-2023 artfynd.xlsx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor/A 55173-2023 karta.png", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/kartor_geotiff/A 55173-2023 georefererad karta.tif", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomål/A 55173-2023 FSC-klagomål.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/klagomålsmail/A 55173-2023 FSC-klagomål mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsyn/A 55173-2023 tillsynsbegäran.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2460/tillsynsmail/A 55173-2023 tillsynsbegäran mail.docx", "A 55173-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45701</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>46189</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44565</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44565</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54793-2023</t>
+          <t>A 52536-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45229</v>
+        <v>45218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16782-2024</t>
+          <t>A 38956-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45411</v>
+        <v>44816</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 846-2022</t>
+          <t>A 46434-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44571</v>
+        <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33319-2023</t>
+          <t>A 15674-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45127</v>
+        <v>45748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28337-2022</t>
+          <t>A 13758-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44747</v>
+        <v>45390</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35737-2024</t>
+          <t>A 23205-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45532</v>
+        <v>45791</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2723,8 +2723,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2767,7 +2772,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35771-2024</t>
+          <t>A 23101-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2781,10 +2786,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45532</v>
+        <v>45791</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2796,8 +2801,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2840,7 +2850,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20228-2023</t>
+          <t>A 45126-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2850,14 +2860,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45055</v>
+        <v>45187</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2870,7 +2880,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2913,7 +2923,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31132-2023</t>
+          <t>A 23453-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2927,10 +2937,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45103</v>
+        <v>45792</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2942,8 +2952,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2986,7 +3001,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35349-2023</t>
+          <t>A 23465-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3000,10 +3015,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45146</v>
+        <v>45792</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3016,7 +3031,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3059,7 +3074,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45126-2023</t>
+          <t>A 63447-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3073,10 +3088,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45187</v>
+        <v>46013</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3088,8 +3103,13 @@
           <t>VÄNNÄS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>21.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3132,7 +3152,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23101-2025</t>
+          <t>A 38566-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3146,10 +3166,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45791</v>
+        <v>45884</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>4629